--- a/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="253">
   <si>
     <t>pathway</t>
   </si>
@@ -40,13 +40,13 @@
     <t>D4&amp;E4-neuroprostanes formation</t>
   </si>
   <si>
-    <t>E2895,E567,E2995,E568,E2897,E1408,E569</t>
-  </si>
-  <si>
-    <t>CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,C02670/C00072/glac,CE6466/CE6467/CE6465/CE6462/CE6463/CE6460/CE6461/CE6459/CE6458/CE6457/CE6455/CE6454/CE6453/CE6452/CE6456/CE6464,C02670/C00072/glac,CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,CE6429/CE6423/CE6420/CE6426/CE6438/CE6432/CE6435,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>///////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$///////////////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$///////$//////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
+    <t>E2895,E567,E2995,E568,E2897,E569,E1408</t>
+  </si>
+  <si>
+    <t>CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,C02670/C00072/glac,CE6466/CE6467/CE6465/CE6462/CE6463/CE6460/CE6461/CE6459/CE6458/CE6457/CE6455/CE6454/CE6453/CE6452/CE6456/CE6464,C02670/C00072/glac,CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,C02670/C00072/glac,CE6429/CE6423/CE6420/CE6426/CE6438/CE6432/CE6435</t>
+  </si>
+  <si>
+    <t>///////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$///////////////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$///////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$//////</t>
   </si>
   <si>
     <t>Porphyrin metabolism</t>
@@ -280,13 +280,7 @@
     <t>Hyaluronan Metabolism</t>
   </si>
   <si>
-    <t>E57,E33</t>
-  </si>
-  <si>
-    <t>C00618/C06472/C00191,</t>
-  </si>
-  <si>
-    <t>3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate$</t>
+    <t>E33,E57</t>
   </si>
   <si>
     <t>Heparan sulfate degradation</t>
@@ -1147,7 +1141,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>0.0004201610056973832</v>
+        <v>0.0005714189677484412</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1170,7 +1164,7 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>0.004890674106317541</v>
+        <v>0.004588158182215425</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1193,7 +1187,7 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>0.007025092015260248</v>
+        <v>0.006420060167056016</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1216,7 +1210,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>0.01709214971176955</v>
+        <v>0.01626863414060268</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1239,7 +1233,7 @@
         <v>120</v>
       </c>
       <c r="D6">
-        <v>0.02156266281238971</v>
+        <v>0.02043663131712072</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1262,7 +1256,7 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>0.03283978420530748</v>
+        <v>0.03085662425841583</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1285,7 +1279,7 @@
         <v>3</v>
       </c>
       <c r="D8">
-        <v>0.04374716391321154</v>
+        <v>0.04120939143879935</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1308,7 +1302,7 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0.05588141375775197</v>
+        <v>0.05322599620174451</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1331,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>0.06988117846758878</v>
+        <v>0.06690643854725131</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1354,7 +1348,7 @@
         <v>11</v>
       </c>
       <c r="D11">
-        <v>0.07959530091931229</v>
+        <v>0.07541049730256634</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1377,7 +1371,7 @@
         <v>19</v>
       </c>
       <c r="D12">
-        <v>0.08737668274482782</v>
+        <v>0.08317507268785398</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1400,7 +1394,7 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>0.09016655182265844</v>
+        <v>0.08574645804272198</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1423,7 +1417,7 @@
         <v>12</v>
       </c>
       <c r="D14">
-        <v>0.109191442160636</v>
+        <v>0.1048049612611553</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1446,7 +1440,7 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <v>0.1335439740508563</v>
+        <v>0.1266365271171913</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
@@ -1469,7 +1463,7 @@
         <v>9</v>
       </c>
       <c r="D16">
-        <v>0.1335439740508563</v>
+        <v>0.1266365271171913</v>
       </c>
       <c r="E16" t="s">
         <v>60</v>
@@ -1492,7 +1486,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.1341321994588326</v>
+        <v>0.1273592040469908</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
@@ -1515,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>0.1587368279524714</v>
+        <v>0.1520814776222248</v>
       </c>
       <c r="E18" t="s">
         <v>66</v>
@@ -1538,7 +1532,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.1593418598006756</v>
+        <v>0.1526192837095175</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
@@ -1561,7 +1555,7 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <v>0.1593418598006756</v>
+        <v>0.1526192837095175</v>
       </c>
       <c r="E20" t="s">
         <v>72</v>
@@ -1578,7 +1572,7 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>0.1620308902371389</v>
+        <v>0.1549049595805113</v>
       </c>
       <c r="E21" t="s">
         <v>74</v>
@@ -1601,7 +1595,7 @@
         <v>62</v>
       </c>
       <c r="D22">
-        <v>0.169392111056957</v>
+        <v>0.1620308902371389</v>
       </c>
       <c r="E22" t="s">
         <v>78</v>
@@ -1624,7 +1618,7 @@
         <v>11</v>
       </c>
       <c r="D23">
-        <v>0.1974252533570864</v>
+        <v>0.191879128081881</v>
       </c>
       <c r="E23" t="s">
         <v>82</v>
@@ -1647,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="D24">
-        <v>0.1974252533570864</v>
+        <v>0.191879128081881</v>
       </c>
       <c r="E24" t="s">
         <v>86</v>
@@ -1670,21 +1664,21 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>0.2135930488563217</v>
+        <v>0.2085175039074973</v>
       </c>
       <c r="E25" t="s">
         <v>88</v>
       </c>
       <c r="F25" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -1693,21 +1687,21 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>0.2135930488563217</v>
+        <v>0.2085175039074973</v>
       </c>
       <c r="E26" t="s">
         <v>88</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1716,15 +1710,15 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>0.2388195156383926</v>
+        <v>0.2345674862607351</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1733,15 +1727,15 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>0.2388195156383926</v>
+        <v>0.2345674862607351</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1750,15 +1744,15 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>0.2388195156383926</v>
+        <v>0.2345674862607351</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -1767,15 +1761,15 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>0.2388195156383926</v>
+        <v>0.2345674862607351</v>
       </c>
       <c r="E30" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1784,15 +1778,15 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>0.2388195156383926</v>
+        <v>0.2345674862607351</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1801,15 +1795,15 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>0.2388195156383926</v>
+        <v>0.2345674862607351</v>
       </c>
       <c r="E32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B33">
         <v>4</v>
@@ -1818,21 +1812,21 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>0.2518277003747836</v>
+        <v>0.2455757046100066</v>
       </c>
       <c r="E33" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" t="s">
         <v>103</v>
-      </c>
-      <c r="F33" t="s">
-        <v>104</v>
-      </c>
-      <c r="G33" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -1841,21 +1835,21 @@
         <v>8</v>
       </c>
       <c r="D34">
-        <v>0.2610544360598981</v>
+        <v>0.2564494714374548</v>
       </c>
       <c r="E34" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" t="s">
+        <v>106</v>
+      </c>
+      <c r="G34" t="s">
         <v>107</v>
-      </c>
-      <c r="F34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G34" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B35">
         <v>6</v>
@@ -1864,21 +1858,21 @@
         <v>27</v>
       </c>
       <c r="D35">
-        <v>0.2798104233542293</v>
+        <v>0.2766171997109292</v>
       </c>
       <c r="E35" t="s">
+        <v>109</v>
+      </c>
+      <c r="F35" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" t="s">
         <v>111</v>
-      </c>
-      <c r="F35" t="s">
-        <v>112</v>
-      </c>
-      <c r="G35" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1887,21 +1881,21 @@
         <v>18</v>
       </c>
       <c r="D36">
-        <v>0.2921295440412766</v>
+        <v>0.2898102552898271</v>
       </c>
       <c r="E36" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" t="s">
+        <v>114</v>
+      </c>
+      <c r="G36" t="s">
         <v>115</v>
-      </c>
-      <c r="F36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G36" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -1910,21 +1904,21 @@
         <v>9</v>
       </c>
       <c r="D37">
-        <v>0.3171711399808407</v>
+        <v>0.3123476916354347</v>
       </c>
       <c r="E37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F37" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -1933,15 +1927,15 @@
         <v>4</v>
       </c>
       <c r="D38">
-        <v>0.3187341389220349</v>
+        <v>0.3139779163375405</v>
       </c>
       <c r="E38" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -1950,21 +1944,21 @@
         <v>14</v>
       </c>
       <c r="D39">
-        <v>0.3199610090586713</v>
+        <v>0.3151711735937211</v>
       </c>
       <c r="E39" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" t="s">
+        <v>122</v>
+      </c>
+      <c r="G39" t="s">
         <v>123</v>
-      </c>
-      <c r="F39" t="s">
-        <v>124</v>
-      </c>
-      <c r="G39" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -1973,10 +1967,10 @@
         <v>14</v>
       </c>
       <c r="D40">
-        <v>0.3199610090586713</v>
+        <v>0.3151711735937211</v>
       </c>
       <c r="E40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F40" t="s">
         <v>41</v>
@@ -1987,7 +1981,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -1996,21 +1990,21 @@
         <v>10</v>
       </c>
       <c r="D41">
-        <v>0.346817700542848</v>
+        <v>0.3431034772524831</v>
       </c>
       <c r="E41" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B42">
         <v>8</v>
@@ -2019,21 +2013,21 @@
         <v>40</v>
       </c>
       <c r="D42">
-        <v>0.3551873077763399</v>
+        <v>0.3511705685618729</v>
       </c>
       <c r="E42" t="s">
+        <v>129</v>
+      </c>
+      <c r="F42" t="s">
+        <v>130</v>
+      </c>
+      <c r="G42" t="s">
         <v>131</v>
-      </c>
-      <c r="F42" t="s">
-        <v>132</v>
-      </c>
-      <c r="G42" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B43">
         <v>32</v>
@@ -2042,21 +2036,21 @@
         <v>152</v>
       </c>
       <c r="D43">
-        <v>0.3569183711198131</v>
+        <v>0.3527671803835229</v>
       </c>
       <c r="E43" t="s">
+        <v>133</v>
+      </c>
+      <c r="F43" t="s">
+        <v>134</v>
+      </c>
+      <c r="G43" t="s">
         <v>135</v>
-      </c>
-      <c r="F43" t="s">
-        <v>136</v>
-      </c>
-      <c r="G43" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -2065,15 +2059,15 @@
         <v>5</v>
       </c>
       <c r="D44">
-        <v>0.3625149157157023</v>
+        <v>0.3572040806036874</v>
       </c>
       <c r="E44" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -2082,15 +2076,15 @@
         <v>5</v>
       </c>
       <c r="D45">
-        <v>0.3625149157157023</v>
+        <v>0.3572040806036874</v>
       </c>
       <c r="E45" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -2099,21 +2093,21 @@
         <v>5</v>
       </c>
       <c r="D46">
-        <v>0.3625149157157023</v>
+        <v>0.3572040806036874</v>
       </c>
       <c r="E46" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46" t="s">
+        <v>141</v>
+      </c>
+      <c r="G46" t="s">
         <v>142</v>
-      </c>
-      <c r="F46" t="s">
-        <v>143</v>
-      </c>
-      <c r="G46" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B47">
         <v>2</v>
@@ -2122,21 +2116,21 @@
         <v>11</v>
       </c>
       <c r="D47">
-        <v>0.3793885817045092</v>
+        <v>0.3755231004520933</v>
       </c>
       <c r="E47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F47" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -2145,15 +2139,15 @@
         <v>6</v>
       </c>
       <c r="D48">
-        <v>0.4095561419135813</v>
+        <v>0.4063629182702811</v>
       </c>
       <c r="E48" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -2162,21 +2156,21 @@
         <v>6</v>
       </c>
       <c r="D49">
-        <v>0.4095561419135813</v>
+        <v>0.4063629182702811</v>
       </c>
       <c r="E49" t="s">
+        <v>140</v>
+      </c>
+      <c r="F49" t="s">
+        <v>141</v>
+      </c>
+      <c r="G49" t="s">
         <v>142</v>
-      </c>
-      <c r="F49" t="s">
-        <v>143</v>
-      </c>
-      <c r="G49" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -2185,15 +2179,15 @@
         <v>6</v>
       </c>
       <c r="D50">
-        <v>0.4095561419135813</v>
+        <v>0.4063629182702811</v>
       </c>
       <c r="E50" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -2202,15 +2196,15 @@
         <v>6</v>
       </c>
       <c r="D51">
-        <v>0.4095561419135813</v>
+        <v>0.4063629182702811</v>
       </c>
       <c r="E51" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B52">
         <v>3</v>
@@ -2219,10 +2213,10 @@
         <v>18</v>
       </c>
       <c r="D52">
-        <v>0.4302448698341204</v>
+        <v>0.4276062587183408</v>
       </c>
       <c r="E52" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F52" t="s">
         <v>41</v>
@@ -2233,7 +2227,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B53">
         <v>5</v>
@@ -2242,21 +2236,21 @@
         <v>29</v>
       </c>
       <c r="D53">
-        <v>0.4380598645400918</v>
+        <v>0.4361943496747954</v>
       </c>
       <c r="E53" t="s">
+        <v>155</v>
+      </c>
+      <c r="F53" t="s">
+        <v>156</v>
+      </c>
+      <c r="G53" t="s">
         <v>157</v>
-      </c>
-      <c r="F53" t="s">
-        <v>158</v>
-      </c>
-      <c r="G53" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -2265,15 +2259,15 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>0.4520596292499286</v>
+        <v>0.450715114031697</v>
       </c>
       <c r="E54" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -2282,15 +2276,15 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>0.4520596292499286</v>
+        <v>0.450715114031697</v>
       </c>
       <c r="E55" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -2299,15 +2293,15 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>0.4520596292499286</v>
+        <v>0.450715114031697</v>
       </c>
       <c r="E56" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -2316,21 +2310,21 @@
         <v>14</v>
       </c>
       <c r="D57">
-        <v>0.4761768709769584</v>
+        <v>0.4749668072805499</v>
       </c>
       <c r="E57" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G57" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -2339,21 +2333,21 @@
         <v>14</v>
       </c>
       <c r="D58">
-        <v>0.4761768709769584</v>
+        <v>0.4749668072805499</v>
       </c>
       <c r="E58" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F58" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G58" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -2362,21 +2356,21 @@
         <v>14</v>
       </c>
       <c r="D59">
-        <v>0.4761768709769584</v>
+        <v>0.4749668072805499</v>
       </c>
       <c r="E59" t="s">
+        <v>169</v>
+      </c>
+      <c r="F59" t="s">
+        <v>170</v>
+      </c>
+      <c r="G59" t="s">
         <v>171</v>
-      </c>
-      <c r="F59" t="s">
-        <v>172</v>
-      </c>
-      <c r="G59" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -2385,15 +2379,15 @@
         <v>8</v>
       </c>
       <c r="D60">
-        <v>0.486832154081444</v>
+        <v>0.4858069612275424</v>
       </c>
       <c r="E60" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B61">
         <v>6</v>
@@ -2402,21 +2396,21 @@
         <v>37</v>
       </c>
       <c r="D61">
-        <v>0.4895884102788188</v>
+        <v>0.4889497655501588</v>
       </c>
       <c r="E61" t="s">
+        <v>174</v>
+      </c>
+      <c r="F61" t="s">
+        <v>175</v>
+      </c>
+      <c r="G61" t="s">
         <v>176</v>
-      </c>
-      <c r="F61" t="s">
-        <v>177</v>
-      </c>
-      <c r="G61" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B62">
         <v>8</v>
@@ -2425,21 +2419,21 @@
         <v>51</v>
       </c>
       <c r="D62">
-        <v>0.5304616729130602</v>
+        <v>0.5313188013646829</v>
       </c>
       <c r="E62" t="s">
+        <v>178</v>
+      </c>
+      <c r="F62" t="s">
+        <v>179</v>
+      </c>
+      <c r="G62" t="s">
         <v>180</v>
-      </c>
-      <c r="F62" t="s">
-        <v>181</v>
-      </c>
-      <c r="G62" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -2448,15 +2442,15 @@
         <v>10</v>
       </c>
       <c r="D63">
-        <v>0.5333859935127141</v>
+        <v>0.5340750575620578</v>
       </c>
       <c r="E63" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -2465,15 +2459,15 @@
         <v>10</v>
       </c>
       <c r="D64">
-        <v>0.5333859935127141</v>
+        <v>0.5340750575620578</v>
       </c>
       <c r="E64" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -2482,21 +2476,21 @@
         <v>10</v>
       </c>
       <c r="D65">
-        <v>0.5333859935127141</v>
+        <v>0.5340750575620578</v>
       </c>
       <c r="E65" t="s">
+        <v>185</v>
+      </c>
+      <c r="F65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G65" t="s">
         <v>187</v>
-      </c>
-      <c r="F65" t="s">
-        <v>188</v>
-      </c>
-      <c r="G65" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -2505,21 +2499,21 @@
         <v>17</v>
       </c>
       <c r="D66">
-        <v>0.5343271541654762</v>
+        <v>0.5348817666929968</v>
       </c>
       <c r="E66" t="s">
+        <v>189</v>
+      </c>
+      <c r="F66" t="s">
+        <v>190</v>
+      </c>
+      <c r="G66" t="s">
         <v>191</v>
-      </c>
-      <c r="F66" t="s">
-        <v>192</v>
-      </c>
-      <c r="G66" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -2528,15 +2522,15 @@
         <v>12</v>
       </c>
       <c r="D67">
-        <v>0.5644442950538646</v>
+        <v>0.5655199072284499</v>
       </c>
       <c r="E67" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B68">
         <v>3</v>
@@ -2545,10 +2539,10 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>0.5748642879951598</v>
+        <v>0.5754525134031361</v>
       </c>
       <c r="E68" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F68" t="s">
         <v>41</v>
@@ -2559,7 +2553,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B69">
         <v>5</v>
@@ -2568,21 +2562,21 @@
         <v>41</v>
       </c>
       <c r="D69">
-        <v>0.5842086687618695</v>
+        <v>0.5841582494411859</v>
       </c>
       <c r="E69" t="s">
+        <v>197</v>
+      </c>
+      <c r="F69" t="s">
+        <v>198</v>
+      </c>
+      <c r="G69" t="s">
         <v>199</v>
-      </c>
-      <c r="F69" t="s">
-        <v>200</v>
-      </c>
-      <c r="G69" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -2591,21 +2585,21 @@
         <v>22</v>
       </c>
       <c r="D70">
-        <v>0.585906119224887</v>
+        <v>0.5861750222685334</v>
       </c>
       <c r="E70" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F70" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G70" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -2614,21 +2608,21 @@
         <v>24</v>
       </c>
       <c r="D71">
-        <v>0.5941412749365557</v>
+        <v>0.5945950488227089</v>
       </c>
       <c r="E71" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F71" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G71" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2637,12 +2631,12 @@
         <v>6</v>
       </c>
       <c r="D72">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2651,12 +2645,12 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2665,12 +2659,12 @@
         <v>2</v>
       </c>
       <c r="D74">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2679,12 +2673,12 @@
         <v>1</v>
       </c>
       <c r="D75">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2693,12 +2687,12 @@
         <v>4</v>
       </c>
       <c r="D76">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2707,12 +2701,12 @@
         <v>6</v>
       </c>
       <c r="D77">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2721,12 +2715,12 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2735,12 +2729,12 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2749,12 +2743,12 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2763,12 +2757,12 @@
         <v>3</v>
       </c>
       <c r="D81">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2777,12 +2771,12 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2791,12 +2785,12 @@
         <v>3</v>
       </c>
       <c r="D83">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2805,12 +2799,12 @@
         <v>5</v>
       </c>
       <c r="D84">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2819,12 +2813,12 @@
         <v>5</v>
       </c>
       <c r="D85">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2833,12 +2827,12 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2847,12 +2841,12 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2861,12 +2855,12 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2875,12 +2869,12 @@
         <v>4</v>
       </c>
       <c r="D89">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2889,12 +2883,12 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2903,12 +2897,12 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2917,12 +2911,12 @@
         <v>11</v>
       </c>
       <c r="D92">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2931,12 +2925,12 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2945,12 +2939,12 @@
         <v>10</v>
       </c>
       <c r="D94">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2959,12 +2953,12 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2973,12 +2967,12 @@
         <v>3</v>
       </c>
       <c r="D96">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2987,12 +2981,12 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -3001,12 +2995,12 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -3015,12 +3009,12 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -3029,12 +3023,12 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3043,12 +3037,12 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3057,12 +3051,12 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3071,12 +3065,12 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3085,12 +3079,12 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3099,12 +3093,12 @@
         <v>1</v>
       </c>
       <c r="D105">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3113,12 +3107,12 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3127,12 +3121,12 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3141,12 +3135,12 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3155,12 +3149,12 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3169,12 +3163,12 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3183,12 +3177,12 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3197,12 +3191,12 @@
         <v>1</v>
       </c>
       <c r="D112">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3211,12 +3205,12 @@
         <v>8</v>
       </c>
       <c r="D113">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3225,12 +3219,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3239,12 +3233,12 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3253,12 +3247,12 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3267,12 +3261,12 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3281,12 +3275,12 @@
         <v>5</v>
       </c>
       <c r="D118">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3295,12 +3289,12 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3309,7 +3303,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>0.6123090368229105</v>
+        <v>0.612880455790659</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="253">
   <si>
     <t>pathway</t>
   </si>
@@ -37,739 +37,739 @@
     <t>overlap_features (name)</t>
   </si>
   <si>
+    <t>Hyaluronan Metabolism</t>
+  </si>
+  <si>
+    <t>E2845,E35,E33,E57</t>
+  </si>
+  <si>
+    <t>C00518,C01074/C00645/C00140,C01074/C00645/C00140,C00618/C06472/C00191</t>
+  </si>
+  <si>
+    <t>Hyaluronate; Hyaluronic acid; [beta-N-Acetyl-D-glucosaminyl(1,4)beta-D-glucuronosyl(1,3)]n$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
+  </si>
+  <si>
+    <t>Tryptophan metabolism</t>
+  </si>
+  <si>
+    <t>E2752,E796,E823,E1154,E877,E123,E1438,E640,E760,E691,E2796,E647,E1186,E527,E1138,E1187,E693,E737,E846,E738,E601,E2748,E1735,E634,E651,E696,E705,E2750,E1439,E767,E1142,E706,E1436</t>
+  </si>
+  <si>
+    <t>CE3140,C05635/C16596,CE6205,C00978,CE5860,C05645,C04148/C05642,C00637,C05638,C05639,C00021,C05660,CE2119/C05643,C00954/C05634,C00643,CE2119/C05643,C05639,CE2122,C02406/C02700,CE2122,C00780,CE3140,C15522/thbpt4acam,CE1918/CE5629,C05660,C05639,C01252,CE3140,C00268/C02953/C04244,C00328/C05647,C00643,C01252,C04148/C05642</t>
+  </si>
+  <si>
+    <t>$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$5-methoxytryptophol$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$$4-(2-Amino-3-hydroxyphenyl)-2,4-dioxobutanoate$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$Indole-3-acetaldehyde$5-Hydroxykynurenamine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$S-Adenosyl-L-homocysteine$5-Methoxyindoleacetate$/6-Hydroxymelatonin$Indole-3-acetate/5-Hydroxyindoleacetaldehyde$5-Hydroxy-L-tryptophan$/6-Hydroxymelatonin$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$methyl indole-3-acetate$Formylkynurenine/L-Formylkynurenine$methyl indole-3-acetate$Serotonin$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$5-hydroxytryptophol/1,2-dehydrosalsolinol$5-Methoxyindoleacetate$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$4-(2-Aminophenyl)-2,4-dioxobutanoate$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$L-Kynurenine/Formyl-5-hydroxykynurenamine$5-Hydroxy-L-tryptophan$4-(2-Aminophenyl)-2,4-dioxobutanoate$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine</t>
+  </si>
+  <si>
     <t>D4&amp;E4-neuroprostanes formation</t>
   </si>
   <si>
-    <t>E2895,E567,E2995,E568,E2897,E569,E1408</t>
-  </si>
-  <si>
-    <t>CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,C02670/C00072/glac,CE6466/CE6467/CE6465/CE6462/CE6463/CE6460/CE6461/CE6459/CE6458/CE6457/CE6455/CE6454/CE6453/CE6452/CE6456/CE6464,C02670/C00072/glac,CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,C02670/C00072/glac,CE6429/CE6423/CE6420/CE6426/CE6438/CE6432/CE6435</t>
-  </si>
-  <si>
-    <t>///////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$///////////////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$///////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$//////</t>
+    <t>E2895,E1408,E567,E569</t>
+  </si>
+  <si>
+    <t>CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,CE6429/CE6423/CE6420/CE6426/CE6438/CE6432/CE6435,C02670/C00072/glac,C02670/C00072/glac</t>
+  </si>
+  <si>
+    <t>///////$//////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
   </si>
   <si>
     <t>Porphyrin metabolism</t>
   </si>
   <si>
-    <t>E567,E57,E568,E354,E1520,E569,E2463</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,C00618/C06472/C00191,C02670/C00072/glac,C00931,C05791,C02670/C00072/glac,C01079</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$Porphobilinogen$D-Urobilinogen$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$Protoporphyrinogen IX</t>
+    <t>E567,E57,E354,E1520,E569</t>
+  </si>
+  <si>
+    <t>C02670/C00072/glac,C00618/C06472/C00191,C00931,C05791,C02670/C00072/glac</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate$Porphobilinogen$D-Urobilinogen$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
+  </si>
+  <si>
+    <t>Limonene and pinene degradation</t>
+  </si>
+  <si>
+    <t>E262,E257,E261,E264</t>
+  </si>
+  <si>
+    <t>C02452/C11409/C02759/C00964,C02452/C11409/C02759/C00964,C02452/C11409/C02759/C00964,C02452/C11409/C02759/C00964</t>
+  </si>
+  <si>
+    <t>Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol$Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol$Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol$Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1844,E26,E29,E1345</t>
+  </si>
+  <si>
+    <t>C00021,C00212/C00330,,,</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$Adenosine/Deoxyguanosine$$$</t>
+  </si>
+  <si>
+    <t>Heparan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E35,E33,E57</t>
+  </si>
+  <si>
+    <t>C01074/C00645/C00140,C01074/C00645/C00140,C00618/C06472/C00191</t>
+  </si>
+  <si>
+    <t>N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
   </si>
   <si>
     <t>Urea cycle/amino group metabolism</t>
   </si>
   <si>
-    <t>E143,E273,E26,E1908,E1634,E1528,E1411,E1208,E377,E412,E149,E1529,E175,E1535,E471,E145</t>
-  </si>
-  <si>
-    <t>CE5536/C01586,C00624,C00170,C00143,C01449,C04692,CE2934,C00559/C05198,C01250,C05589/C00788,CE5536/C01586,C04692,C02442/C03711,C04692,C00437,CE5536/C01586</t>
-  </si>
-  <si>
-    <t>adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$N-Acetyl-L-glutamate; N-Acetyl-L-glutamic acid$5-Methylthioadenosine$5,10-Methylenetetrahydrofolate$Queuine; Base Q$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$o-methylhippurate$Deoxyadenosine/5'-Deoxyadenosine$N-Acetyl-L-glutamate 5-semialdehyde; 2-Acetamido-5-oxopentanoate$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$N-Methyltyramine/N-Methylphenylethanolamine$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$N2-Acetyl-L-ornithine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid</t>
-  </si>
-  <si>
-    <t>Limonene and pinene degradation</t>
-  </si>
-  <si>
-    <t>E257,E265,E93,E261,E262</t>
-  </si>
-  <si>
-    <t>C02452/C11409/C02759/C00964,C02452/C11409/C02759/C00964,C02576,C02452/C11409/C02759/C00964,C02452/C11409/C02759/C00964</t>
-  </si>
-  <si>
-    <t>Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol$Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol$Perillyl aldehyde; Perillaldehyde$Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol$Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol</t>
-  </si>
-  <si>
-    <t>Tryptophan metabolism</t>
-  </si>
-  <si>
-    <t>E2752,E666,E123,E124,E760,E691,E641,E879,E597,E598,E1186,E610,E527,E778,E1138,E1187,E693,E649,E737,E846,E738,E601,E2748,E1735,E588,E457,E635,E705,E2750,E1439,E767,E697,E1435,E706</t>
-  </si>
-  <si>
-    <t>CE3140,C01598,C05645,C05645,C05638,C05639,C00637,CE5860,C00780,C00780,CE2119/C05643,C02470,C00954/C05634,C06212,C00643,CE2119/C05643,C05639,C05660,CE2122,C02406/C02700,CE2122,C00780,CE3140,C15522/thbpt4acam,C00078/C00525,C02693,CE1918/CE5629,C01252,CE3140,C00268/C02953/C04244,C00328/C05647,C05639,C04148/C05642,C01252</t>
-  </si>
-  <si>
-    <t>$Melatonin; N-Acetyl-5-methoxytryptamine$4-(2-Amino-3-hydroxyphenyl)-2,4-dioxobutanoate$4-(2-Amino-3-hydroxyphenyl)-2,4-dioxobutanoate$5-Hydroxykynurenamine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$Indole-3-acetaldehyde$$Serotonin$Serotonin$/6-Hydroxymelatonin$Xanthurenic acid$Indole-3-acetate/5-Hydroxyindoleacetaldehyde$N-Methylserotonin$5-Hydroxy-L-tryptophan$/6-Hydroxymelatonin$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Methoxyindoleacetate$methyl indole-3-acetate$Formylkynurenine/L-Formylkynurenine$methyl indole-3-acetate$Serotonin$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tryptophan/D-Tryptophan$Indole-3-acetamide$5-hydroxytryptophol/1,2-dehydrosalsolinol$4-(2-Aminophenyl)-2,4-dioxobutanoate$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$L-Kynurenine/Formyl-5-hydroxykynurenamine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$4-(2-Aminophenyl)-2,4-dioxobutanoate</t>
+    <t>E143,E148,E1634,E2796,E1411,E26,E412,E29,E1535,E471,E145,E413</t>
+  </si>
+  <si>
+    <t>CE5536/C01586,CE5536/C01586,,C00021,CE2934,,C05589/C00788,,C04692,,CE5536/C01586,C05589/C00788</t>
+  </si>
+  <si>
+    <t>adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$S-Adenosyl-L-homocysteine$o-methylhippurate$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
+  </si>
+  <si>
+    <t>Biopterin metabolism</t>
+  </si>
+  <si>
+    <t>E912,E1459,E1455,E1439,E1735,E288</t>
+  </si>
+  <si>
+    <t>C00079,CE2705/CE5236,CE2705/CE5236,C00268/C02953/C04244,C15522/thbpt4acam,C00082</t>
+  </si>
+  <si>
+    <t>L-Phenylalanine$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tyrosine</t>
+  </si>
+  <si>
+    <t>Saturated fatty acids beta-oxidation</t>
+  </si>
+  <si>
+    <t>E2345</t>
+  </si>
+  <si>
+    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2796</t>
+  </si>
+  <si>
+    <t>C00021</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>E2839,E35,E33,E2970</t>
+  </si>
+  <si>
+    <t>,C01074/C00645/C00140,C01074/C00645/C00140,</t>
+  </si>
+  <si>
+    <t>$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$</t>
+  </si>
+  <si>
+    <t>Linoleate metabolism</t>
+  </si>
+  <si>
+    <t>E567,E92,E2348,E113,E2350,E2738,E2084,E2639,E569,E479</t>
+  </si>
+  <si>
+    <t>C02670/C00072/glac,,,,,,,,C02670/C00072/glac,</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$$$$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>E1514,E1512,E1071,E445,E1039</t>
+  </si>
+  <si>
+    <t>C00475,C00475,C00299,C00526,C00214</t>
+  </si>
+  <si>
+    <t>Cytidine$Cytidine$Uridine$Deoxyuridine$Thymidine</t>
+  </si>
+  <si>
+    <t>C21-steroid hormone biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2503,E2263,E2398,E1116,E1550,E1176,E1163,E1164,E2269,E2399,E1768,E1771,E1691,E2457,E2669</t>
+  </si>
+  <si>
+    <t>,C05139,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C00951,,C05487/C05475/C05478,C05487/C05475/C05478,andrstndn/C00280,17ahprgstrn/C03205/C05498/C01176,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,,,C05489</t>
+  </si>
+  <si>
+    <t>$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Estradiol-17beta; beta-Estradiol; Estradiol$$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$$$11beta,17alpha,21-Trihydroxypregnenolone</t>
+  </si>
+  <si>
+    <t>De novo fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E2345,E92,E2166</t>
+  </si>
+  <si>
+    <t>,,</t>
+  </si>
+  <si>
+    <t>$$</t>
+  </si>
+  <si>
+    <t>Keratan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E35,E33</t>
+  </si>
+  <si>
+    <t>C01074/C00645/C00140,C01074/C00645/C00140</t>
+  </si>
+  <si>
+    <t>N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine</t>
+  </si>
+  <si>
+    <t>Phosphatidylinositol phosphate metabolism</t>
+  </si>
+  <si>
+    <t>E2345,E57</t>
+  </si>
+  <si>
+    <t>,C00618/C06472/C00191</t>
+  </si>
+  <si>
+    <t>$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
+  </si>
+  <si>
+    <t>Chondroitin sulfate degradation</t>
+  </si>
+  <si>
+    <t>E57</t>
+  </si>
+  <si>
+    <t>C00618/C06472/C00191</t>
+  </si>
+  <si>
+    <t>3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E1074</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
+  </si>
+  <si>
+    <t>E2345,E2119,E2409</t>
+  </si>
+  <si>
+    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
+  </si>
+  <si>
+    <t>E975,E2549</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Drug metabolism - cytochrome P450</t>
+  </si>
+  <si>
+    <t>E521,E179,E796,E522,E1274,E2308,E803,E801,E940</t>
+  </si>
+  <si>
+    <t>C16595/C16587,C16586/CE2173,C05635/C16596,C16595/C16587,,,C16591,C16591,</t>
+  </si>
+  <si>
+    <t>4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$2-Phenyl-1,3-propanediol monocarbamate/$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$$$3-Carbamoyl-2-phenylpropionic acid$3-Carbamoyl-2-phenylpropionic acid$</t>
+  </si>
+  <si>
+    <t>Pentose and Glucuronate Interconversions</t>
+  </si>
+  <si>
+    <t>Tyrosine metabolism</t>
+  </si>
+  <si>
+    <t>E918,E143,E1598,E412,E1438,E190,E430,E1599,E158,E618,E145,E413,E192,E680,E2796,E1222,E288,E160,E220,E912,E148,E634,E914,E1735,E337,E831,E567,E179,E1439,E66,E569,E1436,E170</t>
+  </si>
+  <si>
+    <t>CE2176,CE5536/C01586,,C05589/C00788,C04148/C05642,C09642,C05580,,C00355,,CE5536/C01586,C05589/C00788,C09642,,C00021,,C00082,C00355,C05576,C00079,CE5536/C01586,CE1918/CE5629,CE2176,C15522/thbpt4acam,C05583/C05582,C02763/C00166,C02670/C00072/glac,C16586/CE2173,C00268/C02953/C04244,C05587/C07453,C02670/C00072/glac,C04148/C05642,C05588</t>
+  </si>
+  <si>
+    <t>3-O-methyldopa$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3,4-Dihydroxymandelate$$3,4-Dihydroxy-L-phenylalanine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$$S-Adenosyl-L-homocysteine$$L-Tyrosine$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxyphenylethyleneglycol$L-Phenylalanine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$5-hydroxytryptophol/1,2-dehydrosalsolinol$3-O-methyldopa$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$enol-Phenylpyruvate/Phenylpyruvate$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$2-Phenyl-1,3-propanediol monocarbamate/$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$3-Methoxytyramine/Epinine; Deoxyepinephrine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$L-Metanephrine</t>
+  </si>
+  <si>
+    <t>Vitamin B2 (riboflavin) metabolism</t>
+  </si>
+  <si>
+    <t>E276,E3036</t>
+  </si>
+  <si>
+    <t>Fatty acid activation</t>
+  </si>
+  <si>
+    <t>E2345,E92</t>
+  </si>
+  <si>
+    <t>Glycerophospholipid metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2383,E2796,E1351,E2985,E2513</t>
+  </si>
+  <si>
+    <t>,,C00021,,,</t>
+  </si>
+  <si>
+    <t>$$S-Adenosyl-L-homocysteine$$$</t>
+  </si>
+  <si>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>E2839,E35,E33</t>
+  </si>
+  <si>
+    <t>,C01074/C00645/C00140,C01074/C00645/C00140</t>
+  </si>
+  <si>
+    <t>$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine</t>
+  </si>
+  <si>
+    <t>Vitamin A (retinol) metabolism</t>
+  </si>
+  <si>
+    <t>E2485,E2166,E2012,E2513</t>
+  </si>
+  <si>
+    <t>,,,</t>
+  </si>
+  <si>
+    <t>$$$</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>E2345,E3164,E2383</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>E855,E853</t>
+  </si>
+  <si>
+    <t>Fatty Acid Metabolism</t>
+  </si>
+  <si>
+    <t>Selenoamino acid metabolism</t>
+  </si>
+  <si>
+    <t>E1844</t>
+  </si>
+  <si>
+    <t>C00212/C00330</t>
+  </si>
+  <si>
+    <t>Adenosine/Deoxyguanosine</t>
+  </si>
+  <si>
+    <t>Purine metabolism</t>
+  </si>
+  <si>
+    <t>E567,E933,E572,E116,E1844,E569,E1995</t>
+  </si>
+  <si>
+    <t>C02670/C00072/glac,,C00262,,C00212/C00330,C02670/C00072/glac,C01762</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$Hypoxanthine$$Adenosine/Deoxyguanosine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$Xanthosine</t>
   </si>
   <si>
     <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
   </si>
   <si>
-    <t>E744,E567,E57,E47,E568,E569</t>
-  </si>
-  <si>
-    <t>C04593/C00725,C02670/C00072/glac,C00618/C06472/C00191,C00257/C00800,C02670/C00072/glac,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>(2S,3R)-3-Hydroxybutane-1,2,3-tricarboxylate; Methylisocitrate; Methylisocitric acid/Lipoate; Lipoic acid; alpha-Lipoic acid; Thioctic acid$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate$D-Gluconate/L-Gulonate$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Pentose and Glucuronate Interconversions</t>
-  </si>
-  <si>
-    <t>E47,E57</t>
-  </si>
-  <si>
-    <t>C00257/C00800,C00618/C06472/C00191</t>
-  </si>
-  <si>
-    <t>D-Gluconate/L-Gulonate$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>E446,E1908,E1512,E2089,E445,E1039</t>
-  </si>
-  <si>
-    <t>,C00143,,,,</t>
-  </si>
-  <si>
-    <t>$5,10-Methylenetetrahydrofolate$$$$</t>
+    <t>E567,E57,E569</t>
+  </si>
+  <si>
+    <t>C02670/C00072/glac,C00618/C06472/C00191,C02670/C00072/glac</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
+  </si>
+  <si>
+    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
+  </si>
+  <si>
+    <t>E2570,E2796</t>
+  </si>
+  <si>
+    <t>C01185,C00021</t>
+  </si>
+  <si>
+    <t>Nicotinate D-ribonucleotide$S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Arginine and Proline Metabolism</t>
+  </si>
+  <si>
+    <t>E26,E29</t>
+  </si>
+  <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2505</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
+  </si>
+  <si>
+    <t>E2183</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
+    <t>E2192,E3007</t>
+  </si>
+  <si>
+    <t>Aminosugars metabolism</t>
+  </si>
+  <si>
+    <t>Lysine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1926</t>
+  </si>
+  <si>
+    <t>C00021,</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E471,E1473,E1074</t>
+  </si>
+  <si>
+    <t>Omega-3 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E92</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E1403</t>
+  </si>
+  <si>
+    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
+  </si>
+  <si>
+    <t>E1990</t>
+  </si>
+  <si>
+    <t>CoA Catabolism</t>
+  </si>
+  <si>
+    <t>E2192</t>
+  </si>
+  <si>
+    <t>Histidine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1403</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1714</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E2442,E1452</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>E2859,E3025,E3062,E3005</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E975,E989,E1301,E1286,E2899,E1899</t>
+  </si>
+  <si>
+    <t>,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E2796,E831</t>
+  </si>
+  <si>
+    <t>C00021,C02763/C00166</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$enol-Phenylpyruvate/Phenylpyruvate</t>
+  </si>
+  <si>
+    <t>Butanoate metabolism</t>
+  </si>
+  <si>
+    <t>E1044</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E975,E92,E2513</t>
+  </si>
+  <si>
+    <t>Hexose phosphorylation</t>
+  </si>
+  <si>
+    <t>E831,E784</t>
+  </si>
+  <si>
+    <t>C02763/C00166,</t>
+  </si>
+  <si>
+    <t>enol-Phenylpyruvate/Phenylpyruvate$</t>
+  </si>
+  <si>
+    <t>Vitamin B9 (folate) metabolism</t>
+  </si>
+  <si>
+    <t>E1823</t>
+  </si>
+  <si>
+    <t>Vitamin B6 (pyridoxine) metabolism</t>
+  </si>
+  <si>
+    <t>E383</t>
+  </si>
+  <si>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2263,E1550,E1176,E2796,E2269,E1768,E1771</t>
+  </si>
+  <si>
+    <t>C05139,C00951,,C00021,andrstndn/C00280,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179</t>
+  </si>
+  <si>
+    <t>16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Estradiol-17beta; beta-Estradiol; Estradiol$$S-Adenosyl-L-homocysteine$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E975,E567,E569</t>
+  </si>
+  <si>
+    <t>,C02670/C00072/glac,C02670/C00072/glac</t>
+  </si>
+  <si>
+    <t>$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
+  </si>
+  <si>
+    <t>Bile acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E2942,E2940</t>
+  </si>
+  <si>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycolysis and Gluconeogenesis</t>
   </si>
   <si>
     <t>Glycosphingolipid biosynthesis - ganglioseries</t>
   </si>
   <si>
-    <t>E2769,E2765,E2770</t>
-  </si>
-  <si>
-    <t>,,</t>
-  </si>
-  <si>
-    <t>$$</t>
-  </si>
-  <si>
-    <t>Lysine metabolism</t>
-  </si>
-  <si>
-    <t>E544,E2108,E727,E1926</t>
-  </si>
-  <si>
-    <t>,,,</t>
-  </si>
-  <si>
-    <t>$$$</t>
-  </si>
-  <si>
-    <t>Biopterin metabolism</t>
-  </si>
-  <si>
-    <t>E1459,E1908,E1455,E1439,E1735,E288</t>
-  </si>
-  <si>
-    <t>CE2705/CE5236,C00143,CE2705/CE5236,C00268/C02953/C04244,C15522/thbpt4acam,C00082</t>
-  </si>
-  <si>
-    <t>quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$5,10-Methylenetetrahydrofolate$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tyrosine</t>
-  </si>
-  <si>
-    <t>Purine metabolism</t>
-  </si>
-  <si>
-    <t>E567,E572,E116,E1495,E1844,E568,E569,E571,E1208,E1995</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,,,,,C02670/C00072/glac,C02670/C00072/glac,,C00559/C05198,</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$Deoxyadenosine/5'-Deoxyadenosine$</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E740,E2839,E33,E2970</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>E740,E33,E2580</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
-  </si>
-  <si>
-    <t>E47,E855,E740</t>
-  </si>
-  <si>
-    <t>C00257/C00800,,</t>
-  </si>
-  <si>
-    <t>D-Gluconate/L-Gulonate$$</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>E740,E2839,E33,E2580</t>
-  </si>
-  <si>
-    <t>De novo fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E2166,E256,E270</t>
-  </si>
-  <si>
-    <t>Chondroitin sulfate degradation</t>
-  </si>
-  <si>
-    <t>E57</t>
-  </si>
-  <si>
-    <t>C00618/C06472/C00191</t>
-  </si>
-  <si>
-    <t>3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>E1074</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol phosphate metabolism</t>
-  </si>
-  <si>
-    <t>E740,E57</t>
-  </si>
-  <si>
-    <t>,C00618/C06472/C00191</t>
-  </si>
-  <si>
-    <t>$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
-  </si>
-  <si>
-    <t>C21-steroid hormone biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2268,E2503,E2263,E1036,E1116,E1163,E423,E1767,E1164,E2269,E2399,E1771,E1691,E2457,E2669</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Vitamin B9 (folate) metabolism</t>
-  </si>
-  <si>
-    <t>E1897,E509,E1908</t>
-  </si>
-  <si>
-    <t>C00445,,C00143</t>
-  </si>
-  <si>
-    <t>5,10-Methenyltetrahydrofolate$$5,10-Methylenetetrahydrofolate</t>
-  </si>
-  <si>
-    <t>Aminosugars metabolism</t>
-  </si>
-  <si>
-    <t>E729,E33,E2580</t>
-  </si>
-  <si>
-    <t>Hyaluronan Metabolism</t>
-  </si>
-  <si>
-    <t>E33,E57</t>
-  </si>
-  <si>
-    <t>Heparan sulfate degradation</t>
+    <t>R Group Synthesis</t>
+  </si>
+  <si>
+    <t>C5-Branched dibasic acid metabolism</t>
+  </si>
+  <si>
+    <t>Pyruvate Metabolism</t>
+  </si>
+  <si>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycerolipid metabolism</t>
+  </si>
+  <si>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - globoseries</t>
+  </si>
+  <si>
+    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - lactoseries</t>
+  </si>
+  <si>
+    <t>Parathio degradation</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>Blood Group Biosynthesis</t>
   </si>
   <si>
     <t>Electron transport chain</t>
   </si>
   <si>
-    <t>E2089</t>
+    <t>Vitamin H (biotin) metabolism</t>
   </si>
   <si>
     <t>Caffeine metabolism</t>
   </si>
   <si>
-    <t>E740</t>
+    <t>Lipoate metabolism</t>
+  </si>
+  <si>
+    <t>Heparan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>Glyoxylate and Dicarboxylate Metabolism</t>
+  </si>
+  <si>
+    <t>Valine, leucine and isoleucine degradation</t>
+  </si>
+  <si>
+    <t>Glycosaminoglycan degradation</t>
   </si>
   <si>
     <t>Fatty acid oxidation</t>
   </si>
   <si>
+    <t>ROS Detoxification</t>
+  </si>
+  <si>
+    <t>Mono-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
+  </si>
+  <si>
+    <t>Geraniol degradation</t>
+  </si>
+  <si>
+    <t>Vitamin D</t>
+  </si>
+  <si>
+    <t>Dynorphin metabolism</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation, peroxisome</t>
+  </si>
+  <si>
+    <t>Polyunsaturated fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>Alanine and Aspartate Metabolism</t>
+  </si>
+  <si>
+    <t>Keratan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>TCA cycle</t>
+  </si>
+  <si>
+    <t>3-Chloroacrylic acid degradation</t>
+  </si>
+  <si>
+    <t>Sphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>O-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Proteoglycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin K metabolism</t>
+  </si>
+  <si>
+    <t>Glutamate metabolism</t>
+  </si>
+  <si>
+    <t>Benzoate degradation via CoA ligation</t>
+  </si>
+  <si>
+    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
+  </si>
+  <si>
+    <t>Atrazine degradation</t>
+  </si>
+  <si>
+    <t>Carbon fixation</t>
+  </si>
+  <si>
+    <t>Nucleotide Sugar Metabolism</t>
+  </si>
+  <si>
+    <t>1- and 2-Methylnaphthalene degradation</t>
+  </si>
+  <si>
+    <t>Nitrogen metabolism</t>
+  </si>
+  <si>
+    <t>Drug metabolism - other enzymes</t>
+  </si>
+  <si>
     <t>Prostaglandin formation from dihomo gama-linoleic acid</t>
   </si>
   <si>
-    <t>E2779</t>
-  </si>
-  <si>
     <t>Starch and Sucrose Metabolism</t>
   </si>
   <si>
+    <t>Trihydroxycoprostanoyl-CoA beta-oxidation</t>
+  </si>
+  <si>
     <t>Omega-6 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E256</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E1353,E471,E1473,E1074</t>
-  </si>
-  <si>
-    <t>,C00437,,</t>
-  </si>
-  <si>
-    <t>$N2-Acetyl-L-ornithine$$</t>
-  </si>
-  <si>
-    <t>Vitamin B2 (riboflavin) metabolism</t>
-  </si>
-  <si>
-    <t>E1372,E3036</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>Glycerophospholipid metabolism</t>
-  </si>
-  <si>
-    <t>E2383,E740,E1349,E1351,E256,E2513</t>
-  </si>
-  <si>
-    <t>,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$</t>
-  </si>
-  <si>
-    <t>Hexose phosphorylation</t>
-  </si>
-  <si>
-    <t>E729,E740,E831,E784</t>
-  </si>
-  <si>
-    <t>,,C02763/C00166,</t>
-  </si>
-  <si>
-    <t>$$enol-Phenylpyruvate/Phenylpyruvate$</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>E310,E313</t>
-  </si>
-  <si>
-    <t>Selenoamino acid metabolism</t>
-  </si>
-  <si>
-    <t>E1844</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>E1714,E1239,E1908</t>
-  </si>
-  <si>
-    <t>alpam,,C00143</t>
-  </si>
-  <si>
-    <t>S-aminomethyldihydrolipoamide$$5,10-Methylenetetrahydrofolate</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>E740,E2383,E3164</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>E740,E2817</t>
-  </si>
-  <si>
-    <t>Drug metabolism - cytochrome P450</t>
-  </si>
-  <si>
-    <t>E179,E522,E2005,E2308,E2568,E178,E801,E940</t>
-  </si>
-  <si>
-    <t>CE2173,,,,C07572,CE2173,,</t>
-  </si>
-  <si>
-    <t>$$$$Citalopram$$$</t>
-  </si>
-  <si>
-    <t>Tyrosine metabolism</t>
-  </si>
-  <si>
-    <t>E132,E918,E143,E66,E412,E190,E1975,E158,E145,E192,E175,E288,E160,E220,E149,E166,E931,E1735,E914,E178,E337,E831,E62,E635,E179,E567,E186,E1439,E568,E1435,E569,E214</t>
-  </si>
-  <si>
-    <t>,CE2176,CE5536/C01586,C05587,C05589/C00788,,,C00355,CE5536/C01586,,C02442/C03711,C00082,C00355,,CE5536/C01586,C05588,,C15522/thbpt4acam,CE2176,CE2173,C05583,C02763/C00166,C05587,CE1918/CE5629,CE2173,C02670/C00072/glac,,C00268/C02953/C04244,C02670/C00072/glac,C04148/C05642,C02670/C00072/glac,C04043/C05852</t>
-  </si>
-  <si>
-    <t>$3-O-methyldopa$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$3-Methoxytyramine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$$3,4-Dihydroxy-L-phenylalanine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$N-Methyltyramine/N-Methylphenylethanolamine$L-Tyrosine$3,4-Dihydroxy-L-phenylalanine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Metanephrine$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$3-O-methyldopa$$3-Methoxy-4-hydroxyphenylglycolaldehyde$enol-Phenylpyruvate/Phenylpyruvate$3-Methoxytyramine$5-hydroxytryptophol/1,2-dehydrosalsolinol$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde/2-Hydroxyphenylacetate</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>E2108</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - globoseries</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>E744</t>
-  </si>
-  <si>
-    <t>C04593/C00725</t>
-  </si>
-  <si>
-    <t>(2S,3R)-3-Hydroxybutane-1,2,3-tricarboxylate; Methylisocitrate; Methylisocitric acid/Lipoate; Lipoic acid; alpha-Lipoic acid; Thioctic acid</t>
-  </si>
-  <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>E2192,E3007</t>
-  </si>
-  <si>
-    <t>Keratan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E33</t>
-  </si>
-  <si>
-    <t>Lipoate metabolism</t>
-  </si>
-  <si>
-    <t>Omega-3 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E2325</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E1403</t>
-  </si>
-  <si>
-    <t>Vitamin A (retinol) metabolism</t>
-  </si>
-  <si>
-    <t>E2166,E2278,E2513</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E567,E568,E256,E569,E2779</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,C02670/C00072/glac,,C02670/C00072/glac,</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$</t>
-  </si>
-  <si>
-    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
-  </si>
-  <si>
-    <t>E2549</t>
-  </si>
-  <si>
-    <t>CoA Catabolism</t>
-  </si>
-  <si>
-    <t>E2192</t>
-  </si>
-  <si>
-    <t>Alanine and Aspartate Metabolism</t>
-  </si>
-  <si>
-    <t>E509</t>
-  </si>
-  <si>
-    <t>Histidine metabolism</t>
-  </si>
-  <si>
-    <t>E1488,E1403</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E2442,E740</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E1844,E26</t>
-  </si>
-  <si>
-    <t>,C00170</t>
-  </si>
-  <si>
-    <t>$5-Methylthioadenosine</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>Linoleate metabolism</t>
-  </si>
-  <si>
-    <t>E567,E2348,E2738,E568,E2639,E569</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,,,C02670/C00072/glac,,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2268,E2263,E1036,E423,E1767,E2269,E1771,E3019</t>
-  </si>
-  <si>
-    <t>,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$</t>
-  </si>
-  <si>
-    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
-  </si>
-  <si>
-    <t>E1738</t>
-  </si>
-  <si>
-    <t>TCA cycle</t>
-  </si>
-  <si>
-    <t>Arginine and Proline Metabolism</t>
-  </si>
-  <si>
-    <t>E26</t>
-  </si>
-  <si>
-    <t>C00170</t>
-  </si>
-  <si>
-    <t>5-Methylthioadenosine</t>
-  </si>
-  <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E831,E2089</t>
-  </si>
-  <si>
-    <t>C02763/C00166,</t>
-  </si>
-  <si>
-    <t>enol-Phenylpyruvate/Phenylpyruvate$</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (pyridoxine) metabolism</t>
-  </si>
-  <si>
-    <t>E382</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E1119,E1129,E3005</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E1301,E2899,E1901,E256,E2779</t>
-  </si>
-  <si>
-    <t>,,,,</t>
-  </si>
-  <si>
-    <t>$$$$</t>
-  </si>
-  <si>
-    <t>Bile acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E3075,E2940</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E2513,E256</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>R Group Synthesis</t>
-  </si>
-  <si>
-    <t>C5-Branched dibasic acid metabolism</t>
-  </si>
-  <si>
-    <t>Pyruvate Metabolism</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycerolipid metabolism</t>
-  </si>
-  <si>
-    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - lactoseries</t>
-  </si>
-  <si>
-    <t>Parathio degradation</t>
-  </si>
-  <si>
-    <t>Blood Group Biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
-  </si>
-  <si>
-    <t>Heparan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>Glyoxylate and Dicarboxylate Metabolism</t>
-  </si>
-  <si>
-    <t>Valine, leucine and isoleucine degradation</t>
-  </si>
-  <si>
-    <t>Fatty Acid Metabolism</t>
-  </si>
-  <si>
-    <t>Glycosaminoglycan degradation</t>
-  </si>
-  <si>
-    <t>ROS Detoxification</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>Saturated fatty acids beta-oxidation</t>
-  </si>
-  <si>
-    <t>Butanoate metabolism</t>
-  </si>
-  <si>
-    <t>Mono-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
-  </si>
-  <si>
-    <t>Geraniol degradation</t>
-  </si>
-  <si>
-    <t>Vitamin D</t>
-  </si>
-  <si>
-    <t>Dynorphin metabolism</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation, peroxisome</t>
-  </si>
-  <si>
-    <t>Polyunsaturated fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>Keratan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>3-Chloroacrylic acid degradation</t>
-  </si>
-  <si>
-    <t>Sphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>O-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Proteoglycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin K metabolism</t>
-  </si>
-  <si>
-    <t>Glutamate metabolism</t>
-  </si>
-  <si>
-    <t>Benzoate degradation via CoA ligation</t>
-  </si>
-  <si>
-    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
-  </si>
-  <si>
-    <t>Atrazine degradation</t>
-  </si>
-  <si>
-    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
-  </si>
-  <si>
-    <t>Fatty acid activation</t>
-  </si>
-  <si>
-    <t>Carbon fixation</t>
-  </si>
-  <si>
-    <t>Nucleotide Sugar Metabolism</t>
-  </si>
-  <si>
-    <t>1- and 2-Methylnaphthalene degradation</t>
-  </si>
-  <si>
-    <t>Nitrogen metabolism</t>
-  </si>
-  <si>
-    <t>Drug metabolism - other enzymes</t>
-  </si>
-  <si>
-    <t>Trihydroxycoprostanoyl-CoA beta-oxidation</t>
   </si>
   <si>
     <t>Phytanic acid peroxisomal oxidation</t>
@@ -1135,13 +1135,13 @@
         <v>7</v>
       </c>
       <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
         <v>7</v>
       </c>
-      <c r="C2">
-        <v>9</v>
-      </c>
       <c r="D2">
-        <v>0.0005714189677484412</v>
+        <v>0.01356279726391153</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,13 +1158,13 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="D3">
-        <v>0.004588158182215425</v>
+        <v>0.01830221340817801</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1181,13 +1181,13 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>0.006420060167056016</v>
+        <v>0.03374733197761382</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1207,10 +1207,10 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>0.01626863414060268</v>
+        <v>0.03979765045965614</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1227,13 +1227,13 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>0.02043663131712072</v>
+        <v>0.04682274247491638</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1250,13 +1250,13 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>0.03085662425841583</v>
+        <v>0.05399909245222769</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1273,13 +1273,13 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>0.04120939143879935</v>
+        <v>0.0600830238147258</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1296,13 +1296,13 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>0.05322599620174451</v>
+        <v>0.06890640493437085</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1319,13 +1319,13 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>0.06690643854725131</v>
+        <v>0.073057595670661</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1342,91 +1342,85 @@
         <v>43</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0.07541049730256634</v>
+        <v>0.07499033629686896</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
       </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0.07499033629686896</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" t="s">
         <v>47</v>
       </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>19</v>
-      </c>
-      <c r="D12">
-        <v>0.08317507268785398</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>48</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13">
+        <v>0.08899010100670576</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
         <v>51</v>
       </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>35</v>
-      </c>
-      <c r="D13">
-        <v>0.08574645804272198</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>52</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>37</v>
+      </c>
+      <c r="D14">
+        <v>0.09833448177341557</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" t="s">
         <v>55</v>
       </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
-      <c r="C14">
-        <v>12</v>
-      </c>
-      <c r="D14">
-        <v>0.1048049612611553</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>56</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1434,119 +1428,119 @@
         <v>57</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D15">
-        <v>0.1266365271171913</v>
+        <v>0.1173929849918489</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="D16">
-        <v>0.1266365271171913</v>
+        <v>0.1361657787264079</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>0.1273592040469908</v>
+        <v>0.1428547419371103</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>0.1520814776222248</v>
+        <v>0.1483336414514042</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="G18" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>0.1526192837095175</v>
+        <v>0.1483336414514042</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -1555,582 +1549,612 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <v>0.1526192837095175</v>
+        <v>0.1493756407455337</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>78</v>
+      </c>
+      <c r="F20" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
         <v>2</v>
       </c>
-      <c r="C21">
-        <v>6</v>
-      </c>
       <c r="D21">
-        <v>0.1549049595805113</v>
+        <v>0.1493756407455337</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>0.1620308902371389</v>
+        <v>0.1722492058956992</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23">
-        <v>0.191879128081881</v>
+        <v>0.1943328683551537</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D24">
-        <v>0.191879128081881</v>
+        <v>0.2194416900556293</v>
       </c>
       <c r="E24" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>0.2085175039074973</v>
+        <v>0.2261474597065596</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="D26">
-        <v>0.2085175039074973</v>
+        <v>0.2261978790272432</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G26" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D27">
-        <v>0.2345674862607351</v>
+        <v>0.2395085796877363</v>
       </c>
       <c r="E27" t="s">
-        <v>91</v>
+        <v>99</v>
+      </c>
+      <c r="F27" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>0.2345674862607351</v>
+        <v>0.2395085796877363</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>101</v>
+      </c>
+      <c r="F28" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D29">
-        <v>0.2345674862607351</v>
+        <v>0.2404161274600427</v>
       </c>
       <c r="E29" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="F29" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D30">
-        <v>0.2345674862607351</v>
+        <v>0.2469202198282382</v>
       </c>
       <c r="E30" t="s">
-        <v>96</v>
+        <v>107</v>
+      </c>
+      <c r="F30" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D31">
-        <v>0.2345674862607351</v>
+        <v>0.2558444395892506</v>
       </c>
       <c r="E31" t="s">
-        <v>93</v>
+        <v>111</v>
+      </c>
+      <c r="F31" t="s">
+        <v>112</v>
+      </c>
+      <c r="G31" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D32">
-        <v>0.2345674862607351</v>
+        <v>0.2938438009445219</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>115</v>
+      </c>
+      <c r="F32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D33">
-        <v>0.2455757046100066</v>
+        <v>0.2939278331456614</v>
       </c>
       <c r="E33" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="F33" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="G33" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34">
-        <v>0.2564494714374548</v>
+        <v>0.2939278331456614</v>
       </c>
       <c r="E34" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F34" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>0.2766171997109292</v>
+        <v>0.3027512142653065</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
-      </c>
-      <c r="F35" t="s">
-        <v>110</v>
-      </c>
-      <c r="G35" t="s">
-        <v>111</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
         <v>4</v>
       </c>
-      <c r="C36">
-        <v>18</v>
-      </c>
       <c r="D36">
-        <v>0.2898102552898271</v>
+        <v>0.3027512142653065</v>
       </c>
       <c r="E36" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F36" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G36" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D37">
-        <v>0.3123476916354347</v>
+        <v>0.320969395472345</v>
       </c>
       <c r="E37" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F37" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="G37" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D38">
-        <v>0.3139779163375405</v>
+        <v>0.3218601368044234</v>
       </c>
       <c r="E38" t="s">
-        <v>119</v>
+        <v>129</v>
+      </c>
+      <c r="F38" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D39">
-        <v>0.3151711735937211</v>
+        <v>0.3270029075141594</v>
       </c>
       <c r="E39" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F39" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G39" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>0.3151711735937211</v>
+        <v>0.3270029075141594</v>
       </c>
       <c r="E40" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F40" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D41">
-        <v>0.3431034772524831</v>
+        <v>0.3454731853246164</v>
       </c>
       <c r="E41" t="s">
-        <v>127</v>
-      </c>
-      <c r="F41" t="s">
-        <v>106</v>
-      </c>
-      <c r="G41" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B42">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>0.3511705685618729</v>
+        <v>0.3454731853246164</v>
       </c>
       <c r="E42" t="s">
-        <v>129</v>
-      </c>
-      <c r="F42" t="s">
-        <v>130</v>
-      </c>
-      <c r="G42" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B43">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="D43">
-        <v>0.3527671803835229</v>
+        <v>0.3575065965277894</v>
       </c>
       <c r="E43" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F43" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D44">
-        <v>0.3572040806036874</v>
+        <v>0.3575065965277894</v>
       </c>
       <c r="E44" t="s">
-        <v>137</v>
+        <v>70</v>
+      </c>
+      <c r="F44" t="s">
+        <v>71</v>
+      </c>
+      <c r="G44" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D45">
-        <v>0.3572040806036874</v>
+        <v>0.3575065965277894</v>
       </c>
       <c r="E45" t="s">
-        <v>93</v>
+        <v>146</v>
+      </c>
+      <c r="F45" t="s">
+        <v>147</v>
+      </c>
+      <c r="G45" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D46">
-        <v>0.3572040806036874</v>
+        <v>0.372346683249021</v>
       </c>
       <c r="E46" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F46" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="G46" t="s">
-        <v>142</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D47">
-        <v>0.3755231004520933</v>
+        <v>0.391455605788138</v>
       </c>
       <c r="E47" t="s">
-        <v>144</v>
-      </c>
-      <c r="F47" t="s">
-        <v>106</v>
-      </c>
-      <c r="G47" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -2139,488 +2163,449 @@
         <v>6</v>
       </c>
       <c r="D48">
-        <v>0.4063629182702811</v>
+        <v>0.391455605788138</v>
       </c>
       <c r="E48" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>0.4063629182702811</v>
+        <v>0.4359254466311491</v>
       </c>
       <c r="E49" t="s">
-        <v>140</v>
-      </c>
-      <c r="F49" t="s">
-        <v>141</v>
-      </c>
-      <c r="G49" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>0.4063629182702811</v>
+        <v>0.4359254466311491</v>
       </c>
       <c r="E50" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D51">
-        <v>0.4063629182702811</v>
+        <v>0.4567318196332835</v>
       </c>
       <c r="E51" t="s">
-        <v>151</v>
+        <v>160</v>
+      </c>
+      <c r="F51" t="s">
+        <v>147</v>
+      </c>
+      <c r="G51" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D52">
-        <v>0.4276062587183408</v>
+        <v>0.4567318196332835</v>
       </c>
       <c r="E52" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F52" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="G52" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D53">
-        <v>0.4361943496747954</v>
+        <v>0.4567318196332835</v>
       </c>
       <c r="E53" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F53" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D54">
-        <v>0.450715114031697</v>
+        <v>0.4817061898119359</v>
       </c>
       <c r="E54" t="s">
-        <v>159</v>
+        <v>166</v>
+      </c>
+      <c r="F54" t="s">
+        <v>112</v>
+      </c>
+      <c r="G54" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D55">
-        <v>0.450715114031697</v>
+        <v>0.5183946488294314</v>
       </c>
       <c r="E55" t="s">
-        <v>161</v>
+        <v>168</v>
+      </c>
+      <c r="F55" t="s">
+        <v>169</v>
+      </c>
+      <c r="G55" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D56">
-        <v>0.450715114031697</v>
+        <v>0.5204618409774625</v>
       </c>
       <c r="E56" t="s">
-        <v>163</v>
+        <v>172</v>
+      </c>
+      <c r="F56" t="s">
+        <v>173</v>
+      </c>
+      <c r="G56" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D57">
-        <v>0.4749668072805499</v>
+        <v>0.5222097107611636</v>
       </c>
       <c r="E57" t="s">
-        <v>165</v>
-      </c>
-      <c r="F57" t="s">
-        <v>106</v>
-      </c>
-      <c r="G57" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D58">
-        <v>0.4749668072805499</v>
+        <v>0.5272852557099881</v>
       </c>
       <c r="E58" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F58" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="G58" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D59">
-        <v>0.4749668072805499</v>
+        <v>0.5329658325070167</v>
       </c>
       <c r="E59" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F59" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G59" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D60">
-        <v>0.4858069612275424</v>
+        <v>0.5374363456076369</v>
       </c>
       <c r="E60" t="s">
-        <v>93</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B61">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D61">
-        <v>0.4889497655501588</v>
+        <v>0.5527133997747937</v>
       </c>
       <c r="E61" t="s">
-        <v>174</v>
-      </c>
-      <c r="F61" t="s">
-        <v>175</v>
-      </c>
-      <c r="G61" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B62">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C62">
         <v>51</v>
       </c>
       <c r="D62">
-        <v>0.5313188013646829</v>
+        <v>0.555234365808978</v>
       </c>
       <c r="E62" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="F62" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G62" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D63">
-        <v>0.5340750575620578</v>
+        <v>0.577233996067293</v>
       </c>
       <c r="E63" t="s">
-        <v>182</v>
+        <v>192</v>
+      </c>
+      <c r="F63" t="s">
+        <v>193</v>
+      </c>
+      <c r="G63" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>22</v>
+      </c>
+      <c r="D64">
+        <v>0.5776037377523067</v>
+      </c>
+      <c r="E64" t="s">
+        <v>196</v>
+      </c>
+      <c r="F64" t="s">
+        <v>87</v>
+      </c>
+      <c r="G64" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>6</v>
+      </c>
+      <c r="D65">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>198</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>10</v>
+      </c>
+      <c r="D66">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>8</v>
+      </c>
+      <c r="D67">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>200</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>7</v>
+      </c>
+      <c r="D68">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>202</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="D70">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
         <v>1</v>
       </c>
-      <c r="C64">
-        <v>10</v>
-      </c>
-      <c r="D64">
-        <v>0.5340750575620578</v>
-      </c>
-      <c r="E64" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" t="s">
-        <v>184</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
-      </c>
-      <c r="C65">
-        <v>10</v>
-      </c>
-      <c r="D65">
-        <v>0.5340750575620578</v>
-      </c>
-      <c r="E65" t="s">
-        <v>185</v>
-      </c>
-      <c r="F65" t="s">
-        <v>186</v>
-      </c>
-      <c r="G65" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" t="s">
-        <v>188</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66">
-        <v>17</v>
-      </c>
-      <c r="D66">
-        <v>0.5348817666929968</v>
-      </c>
-      <c r="E66" t="s">
-        <v>189</v>
-      </c>
-      <c r="F66" t="s">
-        <v>190</v>
-      </c>
-      <c r="G66" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" t="s">
-        <v>192</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="C67">
-        <v>12</v>
-      </c>
-      <c r="D67">
-        <v>0.5655199072284499</v>
-      </c>
-      <c r="E67" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" t="s">
-        <v>194</v>
-      </c>
-      <c r="B68">
-        <v>3</v>
-      </c>
-      <c r="C68">
-        <v>27</v>
-      </c>
-      <c r="D68">
-        <v>0.5754525134031361</v>
-      </c>
-      <c r="E68" t="s">
-        <v>195</v>
-      </c>
-      <c r="F68" t="s">
-        <v>41</v>
-      </c>
-      <c r="G68" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" t="s">
-        <v>196</v>
-      </c>
-      <c r="B69">
-        <v>5</v>
-      </c>
-      <c r="C69">
-        <v>41</v>
-      </c>
-      <c r="D69">
-        <v>0.5841582494411859</v>
-      </c>
-      <c r="E69" t="s">
-        <v>197</v>
-      </c>
-      <c r="F69" t="s">
-        <v>198</v>
-      </c>
-      <c r="G69" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" t="s">
-        <v>200</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
-      </c>
-      <c r="C70">
-        <v>22</v>
-      </c>
-      <c r="D70">
-        <v>0.5861750222685334</v>
-      </c>
-      <c r="E70" t="s">
-        <v>201</v>
-      </c>
-      <c r="F70" t="s">
-        <v>106</v>
-      </c>
-      <c r="G70" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" t="s">
-        <v>202</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
-      </c>
-      <c r="C71">
-        <v>24</v>
-      </c>
       <c r="D71">
-        <v>0.5945950488227089</v>
-      </c>
-      <c r="E71" t="s">
-        <v>203</v>
-      </c>
-      <c r="F71" t="s">
-        <v>106</v>
-      </c>
-      <c r="G71" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>204</v>
       </c>
@@ -2628,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="C72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D72">
-        <v>0.612880455790659</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>205</v>
       </c>
@@ -2642,13 +2627,13 @@
         <v>0</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D73">
-        <v>0.612880455790659</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>206</v>
       </c>
@@ -2656,13 +2641,13 @@
         <v>0</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>0.612880455790659</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>207</v>
       </c>
@@ -2670,13 +2655,13 @@
         <v>0</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D75">
-        <v>0.612880455790659</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>208</v>
       </c>
@@ -2684,13 +2669,13 @@
         <v>0</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D76">
-        <v>0.612880455790659</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>209</v>
       </c>
@@ -2698,13 +2683,13 @@
         <v>0</v>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>0.612880455790659</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>210</v>
       </c>
@@ -2712,13 +2697,13 @@
         <v>0</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D78">
-        <v>0.612880455790659</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>211</v>
       </c>
@@ -2726,13 +2711,13 @@
         <v>0</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>0.612880455790659</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>0.6092670711416615</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>212</v>
       </c>
@@ -2740,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D80">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2757,7 +2742,7 @@
         <v>3</v>
       </c>
       <c r="D81">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2768,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D82">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2782,10 +2767,10 @@
         <v>0</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D83">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2796,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D84">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2810,10 +2795,10 @@
         <v>0</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D85">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2827,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2841,7 +2826,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2855,7 +2840,7 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2866,10 +2851,10 @@
         <v>0</v>
       </c>
       <c r="C89">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2880,10 +2865,10 @@
         <v>0</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D90">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2897,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2908,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="C92">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D92">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2922,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D93">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2936,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="C94">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2950,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2964,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2981,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2995,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3006,10 +2991,10 @@
         <v>0</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D99">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3020,10 +3005,10 @@
         <v>0</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3034,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D101">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3048,10 +3033,10 @@
         <v>0</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3065,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3076,10 +3061,10 @@
         <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3090,10 +3075,10 @@
         <v>0</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3104,10 +3089,10 @@
         <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3121,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3132,10 +3117,10 @@
         <v>0</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3149,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3163,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3177,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3188,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3202,10 +3187,10 @@
         <v>0</v>
       </c>
       <c r="C113">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3219,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3230,10 +3215,10 @@
         <v>0</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D115">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3244,10 +3229,10 @@
         <v>0</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D116">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3258,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D117">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3272,10 +3257,10 @@
         <v>0</v>
       </c>
       <c r="C118">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3286,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D119">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3303,7 +3288,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>0.612880455790659</v>
+        <v>0.6092670711416615</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="247">
   <si>
     <t>pathway</t>
   </si>
@@ -103,10 +103,10 @@
     <t>E2796,E1844,E26,E29,E1345</t>
   </si>
   <si>
-    <t>C00021,C00212/C00330,,,</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$Adenosine/Deoxyguanosine$$$</t>
+    <t>C00021,,,,</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$$$$</t>
   </si>
   <si>
     <t>Heparan sulfate degradation</t>
@@ -127,10 +127,10 @@
     <t>E143,E148,E1634,E2796,E1411,E26,E412,E29,E1535,E471,E145,E413</t>
   </si>
   <si>
-    <t>CE5536/C01586,CE5536/C01586,,C00021,CE2934,,C05589/C00788,,C04692,,CE5536/C01586,C05589/C00788</t>
-  </si>
-  <si>
-    <t>adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$S-Adenosyl-L-homocysteine$o-methylhippurate$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
+    <t>,,,C00021,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$S-Adenosyl-L-homocysteine$$$$$$$$</t>
   </si>
   <si>
     <t>Biopterin metabolism</t>
@@ -139,10 +139,10 @@
     <t>E912,E1459,E1455,E1439,E1735,E288</t>
   </si>
   <si>
-    <t>C00079,CE2705/CE5236,CE2705/CE5236,C00268/C02953/C04244,C15522/thbpt4acam,C00082</t>
-  </si>
-  <si>
-    <t>L-Phenylalanine$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tyrosine</t>
+    <t>,,,C00268/C02953/C04244,C15522/thbpt4acam,</t>
+  </si>
+  <si>
+    <t>$$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$</t>
   </si>
   <si>
     <t>Saturated fatty acids beta-oxidation</t>
@@ -193,10 +193,10 @@
     <t>E1514,E1512,E1071,E445,E1039</t>
   </si>
   <si>
-    <t>C00475,C00475,C00299,C00526,C00214</t>
-  </si>
-  <si>
-    <t>Cytidine$Cytidine$Uridine$Deoxyuridine$Thymidine</t>
+    <t>,,,,</t>
+  </si>
+  <si>
+    <t>$$$$</t>
   </si>
   <si>
     <t>C21-steroid hormone biosynthesis and metabolism</t>
@@ -205,10 +205,10 @@
     <t>E2503,E2263,E2398,E1116,E1550,E1176,E1163,E1164,E2269,E2399,E1768,E1771,E1691,E2457,E2669</t>
   </si>
   <si>
-    <t>,C05139,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C00951,,C05487/C05475/C05478,C05487/C05475/C05478,andrstndn/C00280,17ahprgstrn/C03205/C05498/C01176,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,,,C05489</t>
-  </si>
-  <si>
-    <t>$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Estradiol-17beta; beta-Estradiol; Estradiol$$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$$$11beta,17alpha,21-Trihydroxypregnenolone</t>
+    <t>,,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$$</t>
   </si>
   <si>
     <t>De novo fatty acid biosynthesis</t>
@@ -289,10 +289,10 @@
     <t>E521,E179,E796,E522,E1274,E2308,E803,E801,E940</t>
   </si>
   <si>
-    <t>C16595/C16587,C16586/CE2173,C05635/C16596,C16595/C16587,,,C16591,C16591,</t>
-  </si>
-  <si>
-    <t>4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$2-Phenyl-1,3-propanediol monocarbamate/$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$$$3-Carbamoyl-2-phenylpropionic acid$3-Carbamoyl-2-phenylpropionic acid$</t>
+    <t>,,C05635/C16596,,,,,,</t>
+  </si>
+  <si>
+    <t>$$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$$$$$$</t>
   </si>
   <si>
     <t>Pentose and Glucuronate Interconversions</t>
@@ -304,10 +304,10 @@
     <t>E918,E143,E1598,E412,E1438,E190,E430,E1599,E158,E618,E145,E413,E192,E680,E2796,E1222,E288,E160,E220,E912,E148,E634,E914,E1735,E337,E831,E567,E179,E1439,E66,E569,E1436,E170</t>
   </si>
   <si>
-    <t>CE2176,CE5536/C01586,,C05589/C00788,C04148/C05642,C09642,C05580,,C00355,,CE5536/C01586,C05589/C00788,C09642,,C00021,,C00082,C00355,C05576,C00079,CE5536/C01586,CE1918/CE5629,CE2176,C15522/thbpt4acam,C05583/C05582,C02763/C00166,C02670/C00072/glac,C16586/CE2173,C00268/C02953/C04244,C05587/C07453,C02670/C00072/glac,C04148/C05642,C05588</t>
-  </si>
-  <si>
-    <t>3-O-methyldopa$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3,4-Dihydroxymandelate$$3,4-Dihydroxy-L-phenylalanine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$$S-Adenosyl-L-homocysteine$$L-Tyrosine$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxyphenylethyleneglycol$L-Phenylalanine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$5-hydroxytryptophol/1,2-dehydrosalsolinol$3-O-methyldopa$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$enol-Phenylpyruvate/Phenylpyruvate$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$2-Phenyl-1,3-propanediol monocarbamate/$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$3-Methoxytyramine/Epinine; Deoxyepinephrine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$L-Metanephrine</t>
+    <t>,,,,C04148/C05642,,,,,,,,,,C00021,,,,,,,CE1918/CE5629,,C15522/thbpt4acam,,,C02670/C00072/glac,,C00268/C02953/C04244,,C02670/C00072/glac,C04148/C05642,</t>
+  </si>
+  <si>
+    <t>$$$$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$$$$$$$$$$S-Adenosyl-L-homocysteine$$$$$$$5-hydroxytryptophol/1,2-dehydrosalsolinol$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$</t>
   </si>
   <si>
     <t>Vitamin B2 (riboflavin) metabolism</t>
@@ -382,22 +382,16 @@
     <t>E1844</t>
   </si>
   <si>
-    <t>C00212/C00330</t>
-  </si>
-  <si>
-    <t>Adenosine/Deoxyguanosine</t>
-  </si>
-  <si>
     <t>Purine metabolism</t>
   </si>
   <si>
     <t>E567,E933,E572,E116,E1844,E569,E1995</t>
   </si>
   <si>
-    <t>C02670/C00072/glac,,C00262,,C00212/C00330,C02670/C00072/glac,C01762</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$Hypoxanthine$$Adenosine/Deoxyguanosine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$Xanthosine</t>
+    <t>C02670/C00072/glac,,,,,C02670/C00072/glac,</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$</t>
   </si>
   <si>
     <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
@@ -418,10 +412,10 @@
     <t>E2570,E2796</t>
   </si>
   <si>
-    <t>C01185,C00021</t>
-  </si>
-  <si>
-    <t>Nicotinate D-ribonucleotide$S-Adenosyl-L-homocysteine</t>
+    <t>,C00021</t>
+  </si>
+  <si>
+    <t>$S-Adenosyl-L-homocysteine</t>
   </si>
   <si>
     <t>Arginine and Proline Metabolism</t>
@@ -535,12 +529,6 @@
     <t>E2796,E831</t>
   </si>
   <si>
-    <t>C00021,C02763/C00166</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$enol-Phenylpyruvate/Phenylpyruvate</t>
-  </si>
-  <si>
     <t>Butanoate metabolism</t>
   </si>
   <si>
@@ -559,12 +547,6 @@
     <t>E831,E784</t>
   </si>
   <si>
-    <t>C02763/C00166,</t>
-  </si>
-  <si>
-    <t>enol-Phenylpyruvate/Phenylpyruvate$</t>
-  </si>
-  <si>
     <t>Vitamin B9 (folate) metabolism</t>
   </si>
   <si>
@@ -583,10 +565,10 @@
     <t>E2263,E1550,E1176,E2796,E2269,E1768,E1771</t>
   </si>
   <si>
-    <t>C05139,C00951,,C00021,andrstndn/C00280,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179</t>
-  </si>
-  <si>
-    <t>16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Estradiol-17beta; beta-Estradiol; Estradiol$$S-Adenosyl-L-homocysteine$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol</t>
+    <t>,,,C00021,,,</t>
+  </si>
+  <si>
+    <t>$$$S-Adenosyl-L-homocysteine$$$</t>
   </si>
   <si>
     <t>Prostaglandin formation from arachidonate</t>
@@ -1141,7 +1123,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>0.01356279726391153</v>
+        <v>0.01406699047074839</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1164,7 +1146,7 @@
         <v>120</v>
       </c>
       <c r="D3">
-        <v>0.01830221340817801</v>
+        <v>0.01922656762071226</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1187,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>0.03374733197761382</v>
+        <v>0.03339439673282802</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1210,7 +1192,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.03979765045965614</v>
+        <v>0.03986487622056772</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1233,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>0.04682274247491638</v>
+        <v>0.04736054856220904</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1256,7 +1238,7 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>0.05399909245222769</v>
+        <v>0.05463773718088771</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1279,7 +1261,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.0600830238147258</v>
+        <v>0.05966286280902842</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1302,7 +1284,7 @@
         <v>43</v>
       </c>
       <c r="D9">
-        <v>0.06890640493437085</v>
+        <v>0.06843582460798978</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1325,7 +1307,7 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>0.073057595670661</v>
+        <v>0.07278869262701468</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1348,7 +1330,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.07499033629686896</v>
+        <v>0.07510798137846422</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1365,7 +1347,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>0.07499033629686896</v>
+        <v>0.07510798137846422</v>
       </c>
       <c r="E12" t="s">
         <v>46</v>
@@ -1388,7 +1370,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.08899010100670576</v>
+        <v>0.08937664913194736</v>
       </c>
       <c r="E13" t="s">
         <v>50</v>
@@ -1411,7 +1393,7 @@
         <v>37</v>
       </c>
       <c r="D14">
-        <v>0.09833448177341557</v>
+        <v>0.09813280449068083</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
@@ -1434,7 +1416,7 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>0.1173929849918489</v>
+        <v>0.1175778558343557</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
@@ -1457,7 +1439,7 @@
         <v>62</v>
       </c>
       <c r="D16">
-        <v>0.1361657787264079</v>
+        <v>0.135678391959799</v>
       </c>
       <c r="E16" t="s">
         <v>62</v>
@@ -1480,7 +1462,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>0.1428547419371103</v>
+        <v>0.1426866775348314</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
@@ -1549,7 +1531,7 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <v>0.1493756407455337</v>
+        <v>0.1495100922673568</v>
       </c>
       <c r="E20" t="s">
         <v>78</v>
@@ -1572,7 +1554,7 @@
         <v>2</v>
       </c>
       <c r="D21">
-        <v>0.1493756407455337</v>
+        <v>0.1495100922673568</v>
       </c>
       <c r="E21" t="s">
         <v>82</v>
@@ -1589,7 +1571,7 @@
         <v>11</v>
       </c>
       <c r="D22">
-        <v>0.1722492058956992</v>
+        <v>0.1736609468748424</v>
       </c>
       <c r="E22" t="s">
         <v>84</v>
@@ -1612,7 +1594,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>0.1943328683551537</v>
+        <v>0.1962824154215896</v>
       </c>
       <c r="E23" t="s">
         <v>86</v>
@@ -1635,7 +1617,7 @@
         <v>40</v>
       </c>
       <c r="D24">
-        <v>0.2194416900556293</v>
+        <v>0.219811431740643</v>
       </c>
       <c r="E24" t="s">
         <v>90</v>
@@ -1658,7 +1640,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>0.2261474597065596</v>
+        <v>0.2272398783213727</v>
       </c>
       <c r="E25" t="s">
         <v>78</v>
@@ -1681,7 +1663,7 @@
         <v>152</v>
       </c>
       <c r="D26">
-        <v>0.2261978790272432</v>
+        <v>0.2272902976420564</v>
       </c>
       <c r="E26" t="s">
         <v>95</v>
@@ -1704,7 +1686,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>0.2395085796877363</v>
+        <v>0.2421471908035159</v>
       </c>
       <c r="E27" t="s">
         <v>99</v>
@@ -1727,7 +1709,7 @@
         <v>8</v>
       </c>
       <c r="D28">
-        <v>0.2395085796877363</v>
+        <v>0.2421471908035159</v>
       </c>
       <c r="E28" t="s">
         <v>101</v>
@@ -1750,7 +1732,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>0.2404161274600427</v>
+        <v>0.2430547385758222</v>
       </c>
       <c r="E29" t="s">
         <v>103</v>
@@ -1773,7 +1755,7 @@
         <v>13</v>
       </c>
       <c r="D30">
-        <v>0.2469202198282382</v>
+        <v>0.2505840237979194</v>
       </c>
       <c r="E30" t="s">
         <v>107</v>
@@ -1796,7 +1778,7 @@
         <v>18</v>
       </c>
       <c r="D31">
-        <v>0.2558444395892506</v>
+        <v>0.2597267272818944</v>
       </c>
       <c r="E31" t="s">
         <v>111</v>
@@ -1819,7 +1801,7 @@
         <v>14</v>
       </c>
       <c r="D32">
-        <v>0.2938438009445219</v>
+        <v>0.2985327977681048</v>
       </c>
       <c r="E32" t="s">
         <v>115</v>
@@ -1842,7 +1824,7 @@
         <v>9</v>
       </c>
       <c r="D33">
-        <v>0.2939278331456614</v>
+        <v>0.2986168299692442</v>
       </c>
       <c r="E33" t="s">
         <v>70</v>
@@ -1865,7 +1847,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>0.2939278331456614</v>
+        <v>0.2986168299692442</v>
       </c>
       <c r="E34" t="s">
         <v>118</v>
@@ -1888,7 +1870,7 @@
         <v>4</v>
       </c>
       <c r="D35">
-        <v>0.3027512142653065</v>
+        <v>0.3090200164703114</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
@@ -1905,21 +1887,15 @@
         <v>4</v>
       </c>
       <c r="D36">
-        <v>0.3027512142653065</v>
+        <v>0.3090200164703114</v>
       </c>
       <c r="E36" t="s">
         <v>121</v>
       </c>
-      <c r="F36" t="s">
-        <v>122</v>
-      </c>
-      <c r="G36" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B37">
         <v>7</v>
@@ -1928,21 +1904,21 @@
         <v>35</v>
       </c>
       <c r="D37">
-        <v>0.320969395472345</v>
+        <v>0.3272045847968942</v>
       </c>
       <c r="E37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" t="s">
         <v>125</v>
-      </c>
-      <c r="F37" t="s">
-        <v>126</v>
-      </c>
-      <c r="G37" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -1951,21 +1927,21 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>0.3218601368044234</v>
+        <v>0.32819616477034</v>
       </c>
       <c r="E38" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" t="s">
+        <v>128</v>
+      </c>
+      <c r="G38" t="s">
         <v>129</v>
-      </c>
-      <c r="F38" t="s">
-        <v>130</v>
-      </c>
-      <c r="G38" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -1974,21 +1950,21 @@
         <v>10</v>
       </c>
       <c r="D39">
-        <v>0.3270029075141594</v>
+        <v>0.3333053225996202</v>
       </c>
       <c r="E39" t="s">
+        <v>131</v>
+      </c>
+      <c r="F39" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39" t="s">
         <v>133</v>
-      </c>
-      <c r="F39" t="s">
-        <v>134</v>
-      </c>
-      <c r="G39" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B40">
         <v>2</v>
@@ -1997,10 +1973,10 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>0.3270029075141594</v>
+        <v>0.3333053225996202</v>
       </c>
       <c r="E40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F40" t="s">
         <v>87</v>
@@ -2011,7 +1987,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -2020,15 +1996,15 @@
         <v>5</v>
       </c>
       <c r="D41">
-        <v>0.3454731853246164</v>
+        <v>0.3519268583721282</v>
       </c>
       <c r="E41" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -2037,15 +2013,15 @@
         <v>5</v>
       </c>
       <c r="D42">
-        <v>0.3454731853246164</v>
+        <v>0.3519268583721282</v>
       </c>
       <c r="E42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -2054,10 +2030,10 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>0.3575065965277894</v>
+        <v>0.3640106888959849</v>
       </c>
       <c r="E43" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F43" t="s">
         <v>87</v>
@@ -2068,7 +2044,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -2077,7 +2053,7 @@
         <v>11</v>
       </c>
       <c r="D44">
-        <v>0.3575065965277894</v>
+        <v>0.3640106888959849</v>
       </c>
       <c r="E44" t="s">
         <v>70</v>
@@ -2091,7 +2067,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -2100,21 +2076,21 @@
         <v>11</v>
       </c>
       <c r="D45">
-        <v>0.3575065965277894</v>
+        <v>0.3640106888959849</v>
       </c>
       <c r="E45" t="s">
+        <v>144</v>
+      </c>
+      <c r="F45" t="s">
+        <v>145</v>
+      </c>
+      <c r="G45" t="s">
         <v>146</v>
-      </c>
-      <c r="F45" t="s">
-        <v>147</v>
-      </c>
-      <c r="G45" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B46">
         <v>3</v>
@@ -2123,10 +2099,10 @@
         <v>17</v>
       </c>
       <c r="D46">
-        <v>0.372346683249021</v>
+        <v>0.3792373237424581</v>
       </c>
       <c r="E46" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F46" t="s">
         <v>67</v>
@@ -2137,7 +2113,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -2146,15 +2122,15 @@
         <v>6</v>
       </c>
       <c r="D47">
-        <v>0.391455605788138</v>
+        <v>0.3966992151392413</v>
       </c>
       <c r="E47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -2163,15 +2139,15 @@
         <v>6</v>
       </c>
       <c r="D48">
-        <v>0.391455605788138</v>
+        <v>0.3966992151392413</v>
       </c>
       <c r="E48" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -2180,15 +2156,15 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>0.4359254466311491</v>
+        <v>0.4413203139443034</v>
       </c>
       <c r="E49" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -2197,15 +2173,15 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>0.4359254466311491</v>
+        <v>0.4413203139443034</v>
       </c>
       <c r="E50" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -2214,21 +2190,21 @@
         <v>14</v>
       </c>
       <c r="D51">
-        <v>0.4567318196332835</v>
+        <v>0.4601435269995462</v>
       </c>
       <c r="E51" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F51" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B52">
         <v>2</v>
@@ -2237,21 +2213,21 @@
         <v>14</v>
       </c>
       <c r="D52">
-        <v>0.4567318196332835</v>
+        <v>0.4601435269995462</v>
       </c>
       <c r="E52" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F52" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G52" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -2260,10 +2236,10 @@
         <v>14</v>
       </c>
       <c r="D53">
-        <v>0.4567318196332835</v>
+        <v>0.4601435269995462</v>
       </c>
       <c r="E53" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F53" t="s">
         <v>87</v>
@@ -2274,7 +2250,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B54">
         <v>4</v>
@@ -2283,10 +2259,10 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>0.4817061898119359</v>
+        <v>0.4866472832389371</v>
       </c>
       <c r="E54" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F54" t="s">
         <v>112</v>
@@ -2297,7 +2273,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B55">
         <v>6</v>
@@ -2306,21 +2282,21 @@
         <v>41</v>
       </c>
       <c r="D55">
-        <v>0.5183946488294314</v>
+        <v>0.5219744205979732</v>
       </c>
       <c r="E55" t="s">
+        <v>166</v>
+      </c>
+      <c r="F55" t="s">
+        <v>167</v>
+      </c>
+      <c r="G55" t="s">
         <v>168</v>
-      </c>
-      <c r="F55" t="s">
-        <v>169</v>
-      </c>
-      <c r="G55" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -2329,21 +2305,21 @@
         <v>17</v>
       </c>
       <c r="D56">
-        <v>0.5204618409774625</v>
+        <v>0.5240584191862322</v>
       </c>
       <c r="E56" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F56" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="G56" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2352,15 +2328,15 @@
         <v>10</v>
       </c>
       <c r="D57">
-        <v>0.5222097107611636</v>
+        <v>0.5259239340515286</v>
       </c>
       <c r="E57" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -2369,10 +2345,10 @@
         <v>24</v>
       </c>
       <c r="D58">
-        <v>0.5272852557099881</v>
+        <v>0.5312179627233156</v>
       </c>
       <c r="E58" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F58" t="s">
         <v>67</v>
@@ -2383,7 +2359,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -2392,21 +2368,21 @@
         <v>18</v>
       </c>
       <c r="D59">
-        <v>0.5329658325070167</v>
+        <v>0.5375539906892322</v>
       </c>
       <c r="E59" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F59" t="s">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="G59" t="s">
-        <v>182</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -2415,15 +2391,15 @@
         <v>11</v>
       </c>
       <c r="D60">
-        <v>0.5374363456076369</v>
+        <v>0.5421589553116755</v>
       </c>
       <c r="E60" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -2432,15 +2408,15 @@
         <v>12</v>
       </c>
       <c r="D61">
-        <v>0.5527133997747937</v>
+        <v>0.5572679450765533</v>
       </c>
       <c r="E61" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B62">
         <v>7</v>
@@ -2449,21 +2425,21 @@
         <v>51</v>
       </c>
       <c r="D62">
-        <v>0.555234365808978</v>
+        <v>0.5600242012739282</v>
       </c>
       <c r="E62" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F62" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G62" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -2472,21 +2448,21 @@
         <v>29</v>
       </c>
       <c r="D63">
-        <v>0.577233996067293</v>
+        <v>0.5804944454715046</v>
       </c>
       <c r="E63" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F63" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G63" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -2495,10 +2471,10 @@
         <v>22</v>
       </c>
       <c r="D64">
-        <v>0.5776037377523067</v>
+        <v>0.5808305742760626</v>
       </c>
       <c r="E64" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F64" t="s">
         <v>87</v>
@@ -2509,7 +2485,7 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2518,12 +2494,12 @@
         <v>6</v>
       </c>
       <c r="D65">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2532,12 +2508,12 @@
         <v>10</v>
       </c>
       <c r="D66">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2546,12 +2522,12 @@
         <v>8</v>
       </c>
       <c r="D67">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2560,12 +2536,12 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2574,12 +2550,12 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2588,12 +2564,12 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2602,12 +2578,12 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2616,12 +2592,12 @@
         <v>4</v>
       </c>
       <c r="D72">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2630,12 +2606,12 @@
         <v>6</v>
       </c>
       <c r="D73">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2644,12 +2620,12 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2658,12 +2634,12 @@
         <v>9</v>
       </c>
       <c r="D75">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2672,12 +2648,12 @@
         <v>5</v>
       </c>
       <c r="D76">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2686,12 +2662,12 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2700,12 +2676,12 @@
         <v>3</v>
       </c>
       <c r="D78">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2714,12 +2690,12 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2728,12 +2704,12 @@
         <v>5</v>
       </c>
       <c r="D80">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2742,12 +2718,12 @@
         <v>3</v>
       </c>
       <c r="D81">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2756,12 +2732,12 @@
         <v>3</v>
       </c>
       <c r="D82">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2770,12 +2746,12 @@
         <v>5</v>
       </c>
       <c r="D83">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2784,12 +2760,12 @@
         <v>3</v>
       </c>
       <c r="D84">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2798,12 +2774,12 @@
         <v>6</v>
       </c>
       <c r="D85">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2812,12 +2788,12 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2826,12 +2802,12 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2840,12 +2816,12 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2854,12 +2830,12 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2868,12 +2844,12 @@
         <v>3</v>
       </c>
       <c r="D90">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2882,12 +2858,12 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2896,12 +2872,12 @@
         <v>2</v>
       </c>
       <c r="D92">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2910,12 +2886,12 @@
         <v>3</v>
       </c>
       <c r="D93">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2924,12 +2900,12 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2938,12 +2914,12 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2952,12 +2928,12 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2966,12 +2942,12 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2980,12 +2956,12 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2994,12 +2970,12 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -3008,12 +2984,12 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3022,12 +2998,12 @@
         <v>10</v>
       </c>
       <c r="D101">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3036,12 +3012,12 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3050,12 +3026,12 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3064,12 +3040,12 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3078,12 +3054,12 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3092,12 +3068,12 @@
         <v>1</v>
       </c>
       <c r="D106">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3106,12 +3082,12 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3120,12 +3096,12 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3134,12 +3110,12 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3148,12 +3124,12 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3162,12 +3138,12 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3176,12 +3152,12 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3190,12 +3166,12 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3204,12 +3180,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3218,12 +3194,12 @@
         <v>5</v>
       </c>
       <c r="D115">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3232,12 +3208,12 @@
         <v>3</v>
       </c>
       <c r="D116">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3246,12 +3222,12 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3260,12 +3236,12 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3274,12 +3250,12 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3288,7 +3264,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>0.6092670711416615</v>
+        <v>0.6128636493504311</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="253">
   <si>
     <t>pathway</t>
   </si>
@@ -103,10 +103,10 @@
     <t>E2796,E1844,E26,E29,E1345</t>
   </si>
   <si>
-    <t>C00021,,,,</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$$$$</t>
+    <t>C00021,C00212/C00330,,,</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$Adenosine/Deoxyguanosine$$$</t>
   </si>
   <si>
     <t>Heparan sulfate degradation</t>
@@ -127,10 +127,10 @@
     <t>E143,E148,E1634,E2796,E1411,E26,E412,E29,E1535,E471,E145,E413</t>
   </si>
   <si>
-    <t>,,,C00021,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$S-Adenosyl-L-homocysteine$$$$$$$$</t>
+    <t>CE5536/C01586,CE5536/C01586,,C00021,CE2934,,C05589/C00788,,C04692,,CE5536/C01586,C05589/C00788</t>
+  </si>
+  <si>
+    <t>adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$S-Adenosyl-L-homocysteine$o-methylhippurate$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
   </si>
   <si>
     <t>Biopterin metabolism</t>
@@ -139,10 +139,10 @@
     <t>E912,E1459,E1455,E1439,E1735,E288</t>
   </si>
   <si>
-    <t>,,,C00268/C02953/C04244,C15522/thbpt4acam,</t>
-  </si>
-  <si>
-    <t>$$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$</t>
+    <t>C00079,CE2705/CE5236,CE2705/CE5236,C00268/C02953/C04244,C15522/thbpt4acam,C00082</t>
+  </si>
+  <si>
+    <t>L-Phenylalanine$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tyrosine</t>
   </si>
   <si>
     <t>Saturated fatty acids beta-oxidation</t>
@@ -193,10 +193,10 @@
     <t>E1514,E1512,E1071,E445,E1039</t>
   </si>
   <si>
-    <t>,,,,</t>
-  </si>
-  <si>
-    <t>$$$$</t>
+    <t>C00475,C00475,C00299,C00526,C00214</t>
+  </si>
+  <si>
+    <t>Cytidine$Cytidine$Uridine$Deoxyuridine$Thymidine</t>
   </si>
   <si>
     <t>C21-steroid hormone biosynthesis and metabolism</t>
@@ -205,10 +205,10 @@
     <t>E2503,E2263,E2398,E1116,E1550,E1176,E1163,E1164,E2269,E2399,E1768,E1771,E1691,E2457,E2669</t>
   </si>
   <si>
-    <t>,,,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$</t>
+    <t>,C05139,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C00951,,C05487/C05475/C05478,C05487/C05475/C05478,andrstndn/C00280,17ahprgstrn/C03205/C05498/C01176,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,,,C05489</t>
+  </si>
+  <si>
+    <t>$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Estradiol-17beta; beta-Estradiol; Estradiol$$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$$$11beta,17alpha,21-Trihydroxypregnenolone</t>
   </si>
   <si>
     <t>De novo fatty acid biosynthesis</t>
@@ -289,10 +289,10 @@
     <t>E521,E179,E796,E522,E1274,E2308,E803,E801,E940</t>
   </si>
   <si>
-    <t>,,C05635/C16596,,,,,,</t>
-  </si>
-  <si>
-    <t>$$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$$$$$$</t>
+    <t>C16595/C16587,C16586/CE2173,C05635/C16596,C16595/C16587,,,C16591,C16591,</t>
+  </si>
+  <si>
+    <t>4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$2-Phenyl-1,3-propanediol monocarbamate/$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$$$3-Carbamoyl-2-phenylpropionic acid$3-Carbamoyl-2-phenylpropionic acid$</t>
   </si>
   <si>
     <t>Pentose and Glucuronate Interconversions</t>
@@ -304,10 +304,10 @@
     <t>E918,E143,E1598,E412,E1438,E190,E430,E1599,E158,E618,E145,E413,E192,E680,E2796,E1222,E288,E160,E220,E912,E148,E634,E914,E1735,E337,E831,E567,E179,E1439,E66,E569,E1436,E170</t>
   </si>
   <si>
-    <t>,,,,C04148/C05642,,,,,,,,,,C00021,,,,,,,CE1918/CE5629,,C15522/thbpt4acam,,,C02670/C00072/glac,,C00268/C02953/C04244,,C02670/C00072/glac,C04148/C05642,</t>
-  </si>
-  <si>
-    <t>$$$$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$$$$$$$$$$S-Adenosyl-L-homocysteine$$$$$$$5-hydroxytryptophol/1,2-dehydrosalsolinol$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$</t>
+    <t>CE2176,CE5536/C01586,,C05589/C00788,C04148/C05642,C09642,C05580,,C00355,,CE5536/C01586,C05589/C00788,C09642,,C00021,,C00082,C00355,C05576,C00079,CE5536/C01586,CE1918/CE5629,CE2176,C15522/thbpt4acam,C05583/C05582,C02763/C00166,C02670/C00072/glac,C16586/CE2173,C00268/C02953/C04244,C05587/C07453,C02670/C00072/glac,C04148/C05642,C05588</t>
+  </si>
+  <si>
+    <t>3-O-methyldopa$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3,4-Dihydroxymandelate$$3,4-Dihydroxy-L-phenylalanine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$$S-Adenosyl-L-homocysteine$$L-Tyrosine$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxyphenylethyleneglycol$L-Phenylalanine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$5-hydroxytryptophol/1,2-dehydrosalsolinol$3-O-methyldopa$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$enol-Phenylpyruvate/Phenylpyruvate$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$2-Phenyl-1,3-propanediol monocarbamate/$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$3-Methoxytyramine/Epinine; Deoxyepinephrine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$L-Metanephrine</t>
   </si>
   <si>
     <t>Vitamin B2 (riboflavin) metabolism</t>
@@ -382,16 +382,22 @@
     <t>E1844</t>
   </si>
   <si>
+    <t>C00212/C00330</t>
+  </si>
+  <si>
+    <t>Adenosine/Deoxyguanosine</t>
+  </si>
+  <si>
     <t>Purine metabolism</t>
   </si>
   <si>
     <t>E567,E933,E572,E116,E1844,E569,E1995</t>
   </si>
   <si>
-    <t>C02670/C00072/glac,,,,,C02670/C00072/glac,</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$</t>
+    <t>C02670/C00072/glac,,C00262,,C00212/C00330,C02670/C00072/glac,C01762</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$Hypoxanthine$$Adenosine/Deoxyguanosine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$Xanthosine</t>
   </si>
   <si>
     <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
@@ -412,10 +418,10 @@
     <t>E2570,E2796</t>
   </si>
   <si>
-    <t>,C00021</t>
-  </si>
-  <si>
-    <t>$S-Adenosyl-L-homocysteine</t>
+    <t>C01185,C00021</t>
+  </si>
+  <si>
+    <t>Nicotinate D-ribonucleotide$S-Adenosyl-L-homocysteine</t>
   </si>
   <si>
     <t>Arginine and Proline Metabolism</t>
@@ -529,6 +535,12 @@
     <t>E2796,E831</t>
   </si>
   <si>
+    <t>C00021,C02763/C00166</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$enol-Phenylpyruvate/Phenylpyruvate</t>
+  </si>
+  <si>
     <t>Butanoate metabolism</t>
   </si>
   <si>
@@ -547,6 +559,12 @@
     <t>E831,E784</t>
   </si>
   <si>
+    <t>C02763/C00166,</t>
+  </si>
+  <si>
+    <t>enol-Phenylpyruvate/Phenylpyruvate$</t>
+  </si>
+  <si>
     <t>Vitamin B9 (folate) metabolism</t>
   </si>
   <si>
@@ -565,10 +583,10 @@
     <t>E2263,E1550,E1176,E2796,E2269,E1768,E1771</t>
   </si>
   <si>
-    <t>,,,C00021,,,</t>
-  </si>
-  <si>
-    <t>$$$S-Adenosyl-L-homocysteine$$$</t>
+    <t>C05139,C00951,,C00021,andrstndn/C00280,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179</t>
+  </si>
+  <si>
+    <t>16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Estradiol-17beta; beta-Estradiol; Estradiol$$S-Adenosyl-L-homocysteine$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol</t>
   </si>
   <si>
     <t>Prostaglandin formation from arachidonate</t>
@@ -1123,7 +1141,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>0.01406699047074839</v>
+        <v>0.0140165711500647</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,7 +1164,7 @@
         <v>120</v>
       </c>
       <c r="D3">
-        <v>0.01922656762071226</v>
+        <v>0.01847027781045697</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1169,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>0.03339439673282802</v>
+        <v>0.03322633233054906</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1192,7 +1210,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.03986487622056772</v>
+        <v>0.03999932774239089</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1215,7 +1233,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>0.04736054856220904</v>
+        <v>0.04806641905178064</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1238,7 +1256,7 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>0.05463773718088771</v>
+        <v>0.05435202769701349</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1261,7 +1279,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.05966286280902842</v>
+        <v>0.05988134653199106</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1284,7 +1302,7 @@
         <v>43</v>
       </c>
       <c r="D9">
-        <v>0.06843582460798978</v>
+        <v>0.06897363069528244</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1307,7 +1325,7 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>0.07278869262701468</v>
+        <v>0.0733937244752189</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1330,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.07510798137846422</v>
+        <v>0.07569620678644057</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1347,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>0.07510798137846422</v>
+        <v>0.07569620678644057</v>
       </c>
       <c r="E12" t="s">
         <v>46</v>
@@ -1370,7 +1388,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.08937664913194736</v>
+        <v>0.08767919866892994</v>
       </c>
       <c r="E13" t="s">
         <v>50</v>
@@ -1393,7 +1411,7 @@
         <v>37</v>
       </c>
       <c r="D14">
-        <v>0.09813280449068083</v>
+        <v>0.09581351573923128</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
@@ -1416,7 +1434,7 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>0.1175778558343557</v>
+        <v>0.115292179963362</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
@@ -1439,7 +1457,7 @@
         <v>62</v>
       </c>
       <c r="D16">
-        <v>0.135678391959799</v>
+        <v>0.1343506831817953</v>
       </c>
       <c r="E16" t="s">
         <v>62</v>
@@ -1462,7 +1480,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>0.1426866775348314</v>
+        <v>0.141627871800474</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
@@ -1485,7 +1503,7 @@
         <v>6</v>
       </c>
       <c r="D18">
-        <v>0.1483336414514042</v>
+        <v>0.1470563519940841</v>
       </c>
       <c r="E18" t="s">
         <v>70</v>
@@ -1508,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>0.1483336414514042</v>
+        <v>0.1470563519940841</v>
       </c>
       <c r="E19" t="s">
         <v>74</v>
@@ -1531,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <v>0.1495100922673568</v>
+        <v>0.1477622224836557</v>
       </c>
       <c r="E20" t="s">
         <v>78</v>
@@ -1554,7 +1572,7 @@
         <v>2</v>
       </c>
       <c r="D21">
-        <v>0.1495100922673568</v>
+        <v>0.1477622224836557</v>
       </c>
       <c r="E21" t="s">
         <v>82</v>
@@ -1571,7 +1589,7 @@
         <v>11</v>
       </c>
       <c r="D22">
-        <v>0.1736609468748424</v>
+        <v>0.1716945933681787</v>
       </c>
       <c r="E22" t="s">
         <v>84</v>
@@ -1594,7 +1612,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>0.1962824154215896</v>
+        <v>0.1938790944690005</v>
       </c>
       <c r="E23" t="s">
         <v>86</v>
@@ -1617,7 +1635,7 @@
         <v>40</v>
       </c>
       <c r="D24">
-        <v>0.219811431740643</v>
+        <v>0.2195257222567688</v>
       </c>
       <c r="E24" t="s">
         <v>90</v>
@@ -1640,7 +1658,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>0.2272398783213727</v>
+        <v>0.2264835885111175</v>
       </c>
       <c r="E25" t="s">
         <v>78</v>
@@ -1663,7 +1681,7 @@
         <v>152</v>
       </c>
       <c r="D26">
-        <v>0.2272902976420564</v>
+        <v>0.2265003949513454</v>
       </c>
       <c r="E26" t="s">
         <v>95</v>
@@ -1686,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>0.2421471908035159</v>
+        <v>0.2402480630577637</v>
       </c>
       <c r="E27" t="s">
         <v>99</v>
@@ -1709,7 +1727,7 @@
         <v>8</v>
       </c>
       <c r="D28">
-        <v>0.2421471908035159</v>
+        <v>0.2402480630577637</v>
       </c>
       <c r="E28" t="s">
         <v>101</v>
@@ -1732,7 +1750,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>0.2430547385758222</v>
+        <v>0.2408362884657401</v>
       </c>
       <c r="E29" t="s">
         <v>103</v>
@@ -1755,7 +1773,7 @@
         <v>13</v>
       </c>
       <c r="D30">
-        <v>0.2505840237979194</v>
+        <v>0.2480966706441909</v>
       </c>
       <c r="E30" t="s">
         <v>107</v>
@@ -1778,7 +1796,7 @@
         <v>18</v>
       </c>
       <c r="D31">
-        <v>0.2597267272818944</v>
+        <v>0.2556931816271996</v>
       </c>
       <c r="E31" t="s">
         <v>111</v>
@@ -1801,7 +1819,7 @@
         <v>14</v>
       </c>
       <c r="D32">
-        <v>0.2985327977681048</v>
+        <v>0.2952387354834373</v>
       </c>
       <c r="E32" t="s">
         <v>115</v>
@@ -1824,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="D33">
-        <v>0.2986168299692442</v>
+        <v>0.2953563805650325</v>
       </c>
       <c r="E33" t="s">
         <v>70</v>
@@ -1847,7 +1865,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>0.2986168299692442</v>
+        <v>0.2953563805650325</v>
       </c>
       <c r="E34" t="s">
         <v>118</v>
@@ -1870,7 +1888,7 @@
         <v>4</v>
       </c>
       <c r="D35">
-        <v>0.3090200164703114</v>
+        <v>0.3047679870926539</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
@@ -1887,15 +1905,21 @@
         <v>4</v>
       </c>
       <c r="D36">
-        <v>0.3090200164703114</v>
+        <v>0.3047679870926539</v>
       </c>
       <c r="E36" t="s">
         <v>121</v>
       </c>
+      <c r="F36" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B37">
         <v>7</v>
@@ -1904,21 +1928,21 @@
         <v>35</v>
       </c>
       <c r="D37">
-        <v>0.3272045847968942</v>
+        <v>0.3250869733281794</v>
       </c>
       <c r="E37" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F37" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -1927,21 +1951,21 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>0.32819616477034</v>
+        <v>0.3259609082200299</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -1950,21 +1974,21 @@
         <v>10</v>
       </c>
       <c r="D39">
-        <v>0.3333053225996202</v>
+        <v>0.331406194853868</v>
       </c>
       <c r="E39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G39" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B40">
         <v>2</v>
@@ -1973,10 +1997,10 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>0.3333053225996202</v>
+        <v>0.331406194853868</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F40" t="s">
         <v>87</v>
@@ -1987,7 +2011,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -1996,15 +2020,15 @@
         <v>5</v>
       </c>
       <c r="D41">
-        <v>0.3519268583721282</v>
+        <v>0.3491033764138418</v>
       </c>
       <c r="E41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -2013,15 +2037,15 @@
         <v>5</v>
       </c>
       <c r="D42">
-        <v>0.3519268583721282</v>
+        <v>0.3491033764138418</v>
       </c>
       <c r="E42" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -2030,10 +2054,10 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>0.3640106888959849</v>
+        <v>0.3612376262583822</v>
       </c>
       <c r="E43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F43" t="s">
         <v>87</v>
@@ -2044,7 +2068,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -2053,7 +2077,7 @@
         <v>11</v>
       </c>
       <c r="D44">
-        <v>0.3640106888959849</v>
+        <v>0.3612376262583822</v>
       </c>
       <c r="E44" t="s">
         <v>70</v>
@@ -2067,7 +2091,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -2076,21 +2100,21 @@
         <v>11</v>
       </c>
       <c r="D45">
-        <v>0.3640106888959849</v>
+        <v>0.3612376262583822</v>
       </c>
       <c r="E45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B46">
         <v>3</v>
@@ -2099,10 +2123,10 @@
         <v>17</v>
       </c>
       <c r="D46">
-        <v>0.3792373237424581</v>
+        <v>0.375724777734828</v>
       </c>
       <c r="E46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F46" t="s">
         <v>67</v>
@@ -2113,7 +2137,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -2122,15 +2146,15 @@
         <v>6</v>
       </c>
       <c r="D47">
-        <v>0.3966992151392413</v>
+        <v>0.3936740558982202</v>
       </c>
       <c r="E47" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -2139,15 +2163,15 @@
         <v>6</v>
       </c>
       <c r="D48">
-        <v>0.3966992151392413</v>
+        <v>0.3936740558982202</v>
       </c>
       <c r="E48" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -2156,15 +2180,15 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>0.4413203139443034</v>
+        <v>0.4375724777734828</v>
       </c>
       <c r="E49" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -2173,15 +2197,15 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>0.4413203139443034</v>
+        <v>0.4375724777734828</v>
       </c>
       <c r="E50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -2190,21 +2214,21 @@
         <v>14</v>
       </c>
       <c r="D51">
-        <v>0.4601435269995462</v>
+        <v>0.4576561738458177</v>
       </c>
       <c r="E51" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F51" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G51" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B52">
         <v>2</v>
@@ -2213,21 +2237,21 @@
         <v>14</v>
       </c>
       <c r="D52">
-        <v>0.4601435269995462</v>
+        <v>0.4576561738458177</v>
       </c>
       <c r="E52" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F52" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G52" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -2236,10 +2260,10 @@
         <v>14</v>
       </c>
       <c r="D53">
-        <v>0.4601435269995462</v>
+        <v>0.4576561738458177</v>
       </c>
       <c r="E53" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F53" t="s">
         <v>87</v>
@@ -2250,7 +2274,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B54">
         <v>4</v>
@@ -2259,10 +2283,10 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>0.4866472832389371</v>
+        <v>0.4837061561990555</v>
       </c>
       <c r="E54" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F54" t="s">
         <v>112</v>
@@ -2273,7 +2297,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B55">
         <v>6</v>
@@ -2282,21 +2306,21 @@
         <v>41</v>
       </c>
       <c r="D55">
-        <v>0.5219744205979732</v>
+        <v>0.5216382917934153</v>
       </c>
       <c r="E55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F55" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G55" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -2305,21 +2329,21 @@
         <v>17</v>
       </c>
       <c r="D56">
-        <v>0.5240584191862322</v>
+        <v>0.523923967664409</v>
       </c>
       <c r="E56" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F56" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="G56" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2328,15 +2352,15 @@
         <v>10</v>
       </c>
       <c r="D57">
-        <v>0.5259239340515286</v>
+        <v>0.5255541923665148</v>
       </c>
       <c r="E57" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -2345,10 +2369,10 @@
         <v>24</v>
       </c>
       <c r="D58">
-        <v>0.5312179627233156</v>
+        <v>0.5309490596796692</v>
       </c>
       <c r="E58" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F58" t="s">
         <v>67</v>
@@ -2359,7 +2383,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -2368,21 +2392,21 @@
         <v>18</v>
       </c>
       <c r="D59">
-        <v>0.5375539906892322</v>
+        <v>0.5373187005260416</v>
       </c>
       <c r="E59" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F59" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="G59" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -2391,15 +2415,15 @@
         <v>11</v>
       </c>
       <c r="D60">
-        <v>0.5421589553116755</v>
+        <v>0.542226181072587</v>
       </c>
       <c r="E60" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -2408,15 +2432,15 @@
         <v>12</v>
       </c>
       <c r="D61">
-        <v>0.5572679450765533</v>
+        <v>0.5566124939076654</v>
       </c>
       <c r="E61" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B62">
         <v>7</v>
@@ -2425,21 +2449,21 @@
         <v>51</v>
       </c>
       <c r="D62">
-        <v>0.5600242012739282</v>
+        <v>0.559738491790054</v>
       </c>
       <c r="E62" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F62" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G62" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -2448,21 +2472,21 @@
         <v>29</v>
       </c>
       <c r="D63">
-        <v>0.5804944454715046</v>
+        <v>0.5802087359876305</v>
       </c>
       <c r="E63" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F63" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="G63" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -2471,10 +2495,10 @@
         <v>22</v>
       </c>
       <c r="D64">
-        <v>0.5808305742760626</v>
+        <v>0.5804776390312768</v>
       </c>
       <c r="E64" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F64" t="s">
         <v>87</v>
@@ -2485,7 +2509,7 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2494,12 +2518,12 @@
         <v>6</v>
       </c>
       <c r="D65">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2508,12 +2532,12 @@
         <v>10</v>
       </c>
       <c r="D66">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2522,12 +2546,12 @@
         <v>8</v>
       </c>
       <c r="D67">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2536,12 +2560,12 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2550,12 +2574,12 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2564,12 +2588,12 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2578,12 +2602,12 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2592,12 +2616,12 @@
         <v>4</v>
       </c>
       <c r="D72">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2606,12 +2630,12 @@
         <v>6</v>
       </c>
       <c r="D73">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2620,12 +2644,12 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2634,12 +2658,12 @@
         <v>9</v>
       </c>
       <c r="D75">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2648,12 +2672,12 @@
         <v>5</v>
       </c>
       <c r="D76">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2662,12 +2686,12 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2676,12 +2700,12 @@
         <v>3</v>
       </c>
       <c r="D78">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2690,12 +2714,12 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2704,12 +2728,12 @@
         <v>5</v>
       </c>
       <c r="D80">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2718,12 +2742,12 @@
         <v>3</v>
       </c>
       <c r="D81">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2732,12 +2756,12 @@
         <v>3</v>
       </c>
       <c r="D82">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2746,12 +2770,12 @@
         <v>5</v>
       </c>
       <c r="D83">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2760,12 +2784,12 @@
         <v>3</v>
       </c>
       <c r="D84">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2774,12 +2798,12 @@
         <v>6</v>
       </c>
       <c r="D85">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2788,12 +2812,12 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2802,12 +2826,12 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2816,12 +2840,12 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2830,12 +2854,12 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2844,12 +2868,12 @@
         <v>3</v>
       </c>
       <c r="D90">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2858,12 +2882,12 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2872,12 +2896,12 @@
         <v>2</v>
       </c>
       <c r="D92">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2886,12 +2910,12 @@
         <v>3</v>
       </c>
       <c r="D93">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2900,12 +2924,12 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2914,12 +2938,12 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2928,12 +2952,12 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2942,12 +2966,12 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2956,12 +2980,12 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2970,12 +2994,12 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2984,12 +3008,12 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2998,12 +3022,12 @@
         <v>10</v>
       </c>
       <c r="D101">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3012,12 +3036,12 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3026,12 +3050,12 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3040,12 +3064,12 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3054,12 +3078,12 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3068,12 +3092,12 @@
         <v>1</v>
       </c>
       <c r="D106">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3082,12 +3106,12 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3096,12 +3120,12 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3110,12 +3134,12 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3124,12 +3148,12 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3138,12 +3162,12 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3152,12 +3176,12 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3166,12 +3190,12 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3180,12 +3204,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3194,12 +3218,12 @@
         <v>5</v>
       </c>
       <c r="D115">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3208,12 +3232,12 @@
         <v>3</v>
       </c>
       <c r="D116">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3222,12 +3246,12 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3236,12 +3260,12 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3250,12 +3274,12 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3264,7 +3288,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>0.6128636493504311</v>
+        <v>0.6124939076654173</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
@@ -1141,7 +1141,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>0.0140165711500647</v>
+        <v>0.01287373321456782</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1164,7 +1164,7 @@
         <v>120</v>
       </c>
       <c r="D3">
-        <v>0.01847027781045697</v>
+        <v>0.017982891043848</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1187,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>0.03322633233054906</v>
+        <v>0.03302465504781432</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.03999932774239089</v>
+        <v>0.03863800608393136</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1233,7 +1233,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>0.04806641905178064</v>
+        <v>0.04630174282785163</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1256,7 +1256,7 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>0.05435202769701349</v>
+        <v>0.05341086704425136</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1279,7 +1279,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>0.05988134653199106</v>
+        <v>0.05877212147694997</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1302,7 +1302,7 @@
         <v>43</v>
       </c>
       <c r="D9">
-        <v>0.06897363069528244</v>
+        <v>0.06662072906337708</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1325,7 +1325,7 @@
         <v>19</v>
       </c>
       <c r="D10">
-        <v>0.0733937244752189</v>
+        <v>0.07115846792490882</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1348,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.07569620678644057</v>
+        <v>0.07367943395909313</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1365,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>0.07569620678644057</v>
+        <v>0.07367943395909313</v>
       </c>
       <c r="E12" t="s">
         <v>46</v>
@@ -1388,7 +1388,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0.08767919866892994</v>
+        <v>0.08688929597821886</v>
       </c>
       <c r="E13" t="s">
         <v>50</v>
@@ -1411,7 +1411,7 @@
         <v>37</v>
       </c>
       <c r="D14">
-        <v>0.09581351573923128</v>
+        <v>0.09451941984168333</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
@@ -1434,7 +1434,7 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>0.115292179963362</v>
+        <v>0.1132417942555587</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
@@ -1457,7 +1457,7 @@
         <v>62</v>
       </c>
       <c r="D16">
-        <v>0.1343506831817953</v>
+        <v>0.1318633300280667</v>
       </c>
       <c r="E16" t="s">
         <v>62</v>
@@ -1480,7 +1480,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>0.141627871800474</v>
+        <v>0.1389556478042386</v>
       </c>
       <c r="E17" t="s">
         <v>66</v>
@@ -1503,7 +1503,7 @@
         <v>6</v>
       </c>
       <c r="D18">
-        <v>0.1470563519940841</v>
+        <v>0.1444345473185325</v>
       </c>
       <c r="E18" t="s">
         <v>70</v>
@@ -1526,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>0.1470563519940841</v>
+        <v>0.1444345473185325</v>
       </c>
       <c r="E19" t="s">
         <v>74</v>
@@ -1549,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <v>0.1477622224836557</v>
+        <v>0.1454261272919783</v>
       </c>
       <c r="E20" t="s">
         <v>78</v>
@@ -1572,7 +1572,7 @@
         <v>2</v>
       </c>
       <c r="D21">
-        <v>0.1477622224836557</v>
+        <v>0.1454261272919783</v>
       </c>
       <c r="E21" t="s">
         <v>82</v>
@@ -1589,7 +1589,7 @@
         <v>11</v>
       </c>
       <c r="D22">
-        <v>0.1716945933681787</v>
+        <v>0.1687870792087528</v>
       </c>
       <c r="E22" t="s">
         <v>84</v>
@@ -1612,7 +1612,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>0.1938790944690005</v>
+        <v>0.1898623552545335</v>
       </c>
       <c r="E23" t="s">
         <v>86</v>
@@ -1635,7 +1635,7 @@
         <v>40</v>
       </c>
       <c r="D24">
-        <v>0.2195257222567688</v>
+        <v>0.2149207576343255</v>
       </c>
       <c r="E24" t="s">
         <v>90</v>
@@ -1658,7 +1658,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>0.2264835885111175</v>
+        <v>0.2222651720139157</v>
       </c>
       <c r="E25" t="s">
         <v>78</v>
@@ -1681,7 +1681,7 @@
         <v>152</v>
       </c>
       <c r="D26">
-        <v>0.2265003949513454</v>
+        <v>0.2223155913345994</v>
       </c>
       <c r="E26" t="s">
         <v>95</v>
@@ -1704,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>0.2402480630577637</v>
+        <v>0.2354246147123578</v>
       </c>
       <c r="E27" t="s">
         <v>99</v>
@@ -1727,7 +1727,7 @@
         <v>8</v>
       </c>
       <c r="D28">
-        <v>0.2402480630577637</v>
+        <v>0.2354246147123578</v>
       </c>
       <c r="E28" t="s">
         <v>101</v>
@@ -1750,7 +1750,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>0.2408362884657401</v>
+        <v>0.2360464530007899</v>
       </c>
       <c r="E29" t="s">
         <v>103</v>
@@ -1773,7 +1773,7 @@
         <v>13</v>
       </c>
       <c r="D30">
-        <v>0.2480966706441909</v>
+        <v>0.2435589317826591</v>
       </c>
       <c r="E30" t="s">
         <v>107</v>
@@ -1796,7 +1796,7 @@
         <v>18</v>
       </c>
       <c r="D31">
-        <v>0.2556931816271996</v>
+        <v>0.2514075393690862</v>
       </c>
       <c r="E31" t="s">
         <v>111</v>
@@ -1819,7 +1819,7 @@
         <v>14</v>
       </c>
       <c r="D32">
-        <v>0.2952387354834373</v>
+        <v>0.2892892556427623</v>
       </c>
       <c r="E32" t="s">
         <v>115</v>
@@ -1842,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="D33">
-        <v>0.2953563805650325</v>
+        <v>0.2894237071645855</v>
       </c>
       <c r="E33" t="s">
         <v>70</v>
@@ -1865,7 +1865,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>0.2953563805650325</v>
+        <v>0.2894237071645855</v>
       </c>
       <c r="E34" t="s">
         <v>118</v>
@@ -1888,7 +1888,7 @@
         <v>4</v>
       </c>
       <c r="D35">
-        <v>0.3047679870926539</v>
+        <v>0.2996420228231458</v>
       </c>
       <c r="E35" t="s">
         <v>44</v>
@@ -1905,7 +1905,7 @@
         <v>4</v>
       </c>
       <c r="D36">
-        <v>0.3047679870926539</v>
+        <v>0.2996420228231458</v>
       </c>
       <c r="E36" t="s">
         <v>121</v>
@@ -1928,7 +1928,7 @@
         <v>35</v>
       </c>
       <c r="D37">
-        <v>0.3250869733281794</v>
+        <v>0.3191374934875044</v>
       </c>
       <c r="E37" t="s">
         <v>125</v>
@@ -1951,7 +1951,7 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>0.3259609082200299</v>
+        <v>0.3199442026184434</v>
       </c>
       <c r="E38" t="s">
         <v>129</v>
@@ -1974,7 +1974,7 @@
         <v>10</v>
       </c>
       <c r="D39">
-        <v>0.331406194853868</v>
+        <v>0.3256415858556999</v>
       </c>
       <c r="E39" t="s">
         <v>133</v>
@@ -1997,7 +1997,7 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>0.331406194853868</v>
+        <v>0.3256415858556999</v>
       </c>
       <c r="E40" t="s">
         <v>137</v>
@@ -2020,7 +2020,7 @@
         <v>5</v>
       </c>
       <c r="D41">
-        <v>0.3491033764138418</v>
+        <v>0.3447168955143611</v>
       </c>
       <c r="E41" t="s">
         <v>139</v>
@@ -2037,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="D42">
-        <v>0.3491033764138418</v>
+        <v>0.3447168955143611</v>
       </c>
       <c r="E42" t="s">
         <v>141</v>
@@ -2054,7 +2054,7 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>0.3612376262583822</v>
+        <v>0.3569519840002689</v>
       </c>
       <c r="E43" t="s">
         <v>143</v>
@@ -2077,7 +2077,7 @@
         <v>11</v>
       </c>
       <c r="D44">
-        <v>0.3612376262583822</v>
+        <v>0.3569519840002689</v>
       </c>
       <c r="E44" t="s">
         <v>70</v>
@@ -2100,7 +2100,7 @@
         <v>11</v>
       </c>
       <c r="D45">
-        <v>0.3612376262583822</v>
+        <v>0.3569519840002689</v>
       </c>
       <c r="E45" t="s">
         <v>146</v>
@@ -2123,7 +2123,7 @@
         <v>17</v>
       </c>
       <c r="D46">
-        <v>0.375724777734828</v>
+        <v>0.3707332649871431</v>
       </c>
       <c r="E46" t="s">
         <v>150</v>
@@ -2146,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="D47">
-        <v>0.3936740558982202</v>
+        <v>0.3891531234769163</v>
       </c>
       <c r="E47" t="s">
         <v>152</v>
@@ -2163,7 +2163,7 @@
         <v>6</v>
       </c>
       <c r="D48">
-        <v>0.3936740558982202</v>
+        <v>0.3891531234769163</v>
       </c>
       <c r="E48" t="s">
         <v>154</v>
@@ -2180,7 +2180,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>0.4375724777734828</v>
+        <v>0.433034738911951</v>
       </c>
       <c r="E49" t="s">
         <v>156</v>
@@ -2197,7 +2197,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>0.4375724777734828</v>
+        <v>0.433034738911951</v>
       </c>
       <c r="E50" t="s">
         <v>158</v>
@@ -2214,7 +2214,7 @@
         <v>14</v>
       </c>
       <c r="D51">
-        <v>0.4576561738458177</v>
+        <v>0.4533705315877044</v>
       </c>
       <c r="E51" t="s">
         <v>160</v>
@@ -2237,7 +2237,7 @@
         <v>14</v>
       </c>
       <c r="D52">
-        <v>0.4576561738458177</v>
+        <v>0.4533705315877044</v>
       </c>
       <c r="E52" t="s">
         <v>162</v>
@@ -2260,7 +2260,7 @@
         <v>14</v>
       </c>
       <c r="D53">
-        <v>0.4576561738458177</v>
+        <v>0.4533705315877044</v>
       </c>
       <c r="E53" t="s">
         <v>164</v>
@@ -2283,7 +2283,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>0.4837061561990555</v>
+        <v>0.4795381590225374</v>
       </c>
       <c r="E54" t="s">
         <v>166</v>
@@ -2306,7 +2306,7 @@
         <v>41</v>
       </c>
       <c r="D55">
-        <v>0.5216382917934153</v>
+        <v>0.5164451017629956</v>
       </c>
       <c r="E55" t="s">
         <v>168</v>
@@ -2329,7 +2329,7 @@
         <v>17</v>
       </c>
       <c r="D56">
-        <v>0.523923967664409</v>
+        <v>0.5188148098351288</v>
       </c>
       <c r="E56" t="s">
         <v>172</v>
@@ -2352,7 +2352,7 @@
         <v>10</v>
       </c>
       <c r="D57">
-        <v>0.5255541923665148</v>
+        <v>0.5206467118199695</v>
       </c>
       <c r="E57" t="s">
         <v>176</v>
@@ -2369,7 +2369,7 @@
         <v>24</v>
       </c>
       <c r="D58">
-        <v>0.5309490596796692</v>
+        <v>0.5256718374481101</v>
       </c>
       <c r="E58" t="s">
         <v>178</v>
@@ -2392,7 +2392,7 @@
         <v>18</v>
       </c>
       <c r="D59">
-        <v>0.5373187005260416</v>
+        <v>0.5322431555772172</v>
       </c>
       <c r="E59" t="s">
         <v>180</v>
@@ -2415,7 +2415,7 @@
         <v>11</v>
       </c>
       <c r="D60">
-        <v>0.542226181072587</v>
+        <v>0.5373523134064974</v>
       </c>
       <c r="E60" t="s">
         <v>184</v>
@@ -2432,7 +2432,7 @@
         <v>12</v>
       </c>
       <c r="D61">
-        <v>0.5566124939076654</v>
+        <v>0.5524949160518311</v>
       </c>
       <c r="E61" t="s">
         <v>186</v>
@@ -2449,7 +2449,7 @@
         <v>51</v>
       </c>
       <c r="D62">
-        <v>0.559738491790054</v>
+        <v>0.5556545268146754</v>
       </c>
       <c r="E62" t="s">
         <v>188</v>
@@ -2472,7 +2472,7 @@
         <v>29</v>
       </c>
       <c r="D63">
-        <v>0.5802087359876305</v>
+        <v>0.5757046100065545</v>
       </c>
       <c r="E63" t="s">
         <v>192</v>
@@ -2495,7 +2495,7 @@
         <v>22</v>
       </c>
       <c r="D64">
-        <v>0.5804776390312768</v>
+        <v>0.5762424160938472</v>
       </c>
       <c r="E64" t="s">
         <v>196</v>
@@ -2518,7 +2518,7 @@
         <v>6</v>
       </c>
       <c r="D65">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2532,7 +2532,7 @@
         <v>10</v>
       </c>
       <c r="D66">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2546,7 +2546,7 @@
         <v>8</v>
       </c>
       <c r="D67">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2560,7 +2560,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2574,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2588,7 +2588,7 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2602,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2616,7 +2616,7 @@
         <v>4</v>
       </c>
       <c r="D72">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2630,7 +2630,7 @@
         <v>6</v>
       </c>
       <c r="D73">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="D75">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2672,7 +2672,7 @@
         <v>5</v>
       </c>
       <c r="D76">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2700,7 +2700,7 @@
         <v>3</v>
       </c>
       <c r="D78">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2728,7 +2728,7 @@
         <v>5</v>
       </c>
       <c r="D80">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2742,7 +2742,7 @@
         <v>3</v>
       </c>
       <c r="D81">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2756,7 +2756,7 @@
         <v>3</v>
       </c>
       <c r="D82">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2770,7 +2770,7 @@
         <v>5</v>
       </c>
       <c r="D83">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2784,7 +2784,7 @@
         <v>3</v>
       </c>
       <c r="D84">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2798,7 +2798,7 @@
         <v>6</v>
       </c>
       <c r="D85">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2826,7 +2826,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2840,7 +2840,7 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2868,7 +2868,7 @@
         <v>3</v>
       </c>
       <c r="D90">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2896,7 +2896,7 @@
         <v>2</v>
       </c>
       <c r="D92">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2910,7 +2910,7 @@
         <v>3</v>
       </c>
       <c r="D93">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2952,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2966,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2994,7 +2994,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3008,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3022,7 +3022,7 @@
         <v>10</v>
       </c>
       <c r="D101">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3078,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3092,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="D106">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3106,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3120,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3190,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3218,7 +3218,7 @@
         <v>5</v>
       </c>
       <c r="D115">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3232,7 +3232,7 @@
         <v>3</v>
       </c>
       <c r="D116">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3246,7 +3246,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3260,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3274,7 +3274,7 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3288,7 +3288,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>0.6124939076654173</v>
+        <v>0.6086284264130014</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="231">
   <si>
     <t>pathway</t>
   </si>
@@ -37,709 +37,643 @@
     <t>overlap_features (name)</t>
   </si>
   <si>
+    <t>Tryptophan metabolism</t>
+  </si>
+  <si>
+    <t>E2752,E796,E823,E1154,E877,E123,E1438,E640,E760,E691,E2796,E647,E1186,E527,E1138,E1187,E693,E649,E737,E738,E601,E2748,E1735,E634,E651,E696,E705,E2750,E1439,E767,E706,E1436</t>
+  </si>
+  <si>
+    <t>CE3140,C05635/C16596,CE6205,C00978,CE5860,C05645,C04148/C05642,C00637,C05638,C05639,C00021,C05660,CE2119/C05643,C00954/C05634,C00643,CE2119/C05643,C05639,C05660,CE2122,CE2122,C00780,CE3140,C15522/thbpt4acam,CE1918/CE5629,C05660,C05639,C01252,CE3140,C00268/C02953/C04244,C00328/C05647,C01252,C04148/C05642</t>
+  </si>
+  <si>
+    <t>$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$5-methoxytryptophol$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$$4-(2-Amino-3-hydroxyphenyl)-2,4-dioxobutanoate$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$Indole-3-acetaldehyde$5-Hydroxykynurenamine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$S-Adenosyl-L-homocysteine$5-Methoxyindoleacetate$/6-Hydroxymelatonin$Indole-3-acetate/5-Hydroxyindoleacetaldehyde$5-Hydroxy-L-tryptophan$/6-Hydroxymelatonin$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Methoxyindoleacetate$methyl indole-3-acetate$methyl indole-3-acetate$Serotonin$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$5-hydroxytryptophol/1,2-dehydrosalsolinol$5-Methoxyindoleacetate$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$4-(2-Aminophenyl)-2,4-dioxobutanoate$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$L-Kynurenine/Formyl-5-hydroxykynurenamine$4-(2-Aminophenyl)-2,4-dioxobutanoate$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine</t>
+  </si>
+  <si>
+    <t>D4&amp;E4-neuroprostanes formation</t>
+  </si>
+  <si>
+    <t>E2895,E570,E1408,E569</t>
+  </si>
+  <si>
+    <t>CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,C02670/C00072/glac,CE6429/CE6423/CE6420/CE6426/CE6438/CE6432/CE6435,C02670/C00072/glac</t>
+  </si>
+  <si>
+    <t>///////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$//////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
+  </si>
+  <si>
+    <t>C21-steroid hormone biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2503,E2263,E1116,E1550,E1176,E423,E1163,E1164,E2269,E2399,E1526,E1768,E1771,E2264,E2457,E1691,E2669</t>
+  </si>
+  <si>
+    <t>CE2211/C05480,C18045/C14497/C18075/C05294/C05139,C05488/C05497/C05477/C02140,C00951,C02538,dhea/C03772/C01227/C00674/C00535,C05487/C05475/C05478,C05487/C05475/C05478,andrstndn/C00280,17ahprgstrn/C03205/C05498/C01176,C00468,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,C18045/C14497/C18075/C05294/C05139,C05472,CE1352,C05489/C05471/C05474</t>
+  </si>
+  <si>
+    <t>allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Estradiol-17beta; beta-Estradiol; Estradiol$Estrone 3-sulfate$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$17alpha-hydroxypregnenolone sulfate$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al</t>
+  </si>
+  <si>
+    <t>Porphyrin metabolism</t>
+  </si>
+  <si>
+    <t>E570,E2728,E354,E1520,E569</t>
+  </si>
+  <si>
+    <t>C02670/C00072/glac,C05769/C05770,C00931,C05791,C02670/C00072/glac</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$/$Porphobilinogen$D-Urobilinogen$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>E26,E2796,E1844,E29,E1345</t>
+  </si>
+  <si>
+    <t>C00170,C00021,C00212/C00330,C00170,C02291/C00542</t>
+  </si>
+  <si>
+    <t>5-Methylthioadenosine$S-Adenosyl-L-homocysteine$Adenosine/Deoxyguanosine$5-Methylthioadenosine$L-Cystathionine/Cystathionine</t>
+  </si>
+  <si>
+    <t>Saturated fatty acids beta-oxidation</t>
+  </si>
+  <si>
+    <t>E2345</t>
+  </si>
+  <si>
+    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2796</t>
+  </si>
+  <si>
+    <t>C00021</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Urea cycle/amino group metabolism</t>
+  </si>
+  <si>
+    <t>E143,E26,E148,E1634,E2796,E1411,E412,E29,E1535,E471,E145</t>
+  </si>
+  <si>
+    <t>CE5536/C01586,C00170,CE5536/C01586,,C00021,CE2934,C05589/C00788,C00170,C04692,,CE5536/C01586</t>
+  </si>
+  <si>
+    <t>adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$5-Methylthioadenosine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$S-Adenosyl-L-homocysteine$o-methylhippurate$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Methylthioadenosine$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>E1514,E1512,E1071,E445,E1039</t>
+  </si>
+  <si>
+    <t>C00475,C00475,C00299,C00526,C00214</t>
+  </si>
+  <si>
+    <t>Cytidine$Cytidine$Uridine$Deoxyuridine$Thymidine</t>
+  </si>
+  <si>
+    <t>Drug metabolism - cytochrome P450</t>
+  </si>
+  <si>
+    <t>E179,E796,E522,E1274,E2308,E800,E803,E2568,E801,E940</t>
+  </si>
+  <si>
+    <t>C16586/CE2173,C05635/C16596,C16595/C16587,,,C16591,C16591,C07572,C16591,</t>
+  </si>
+  <si>
+    <t>2-Phenyl-1,3-propanediol monocarbamate/$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$$$3-Carbamoyl-2-phenylpropionic acid$3-Carbamoyl-2-phenylpropionic acid$Citalopram$3-Carbamoyl-2-phenylpropionic acid$</t>
+  </si>
+  <si>
+    <t>Linoleate metabolism</t>
+  </si>
+  <si>
+    <t>E570,E92,E113,E2350,E2348,E2738,E2639,E569,E479</t>
+  </si>
+  <si>
+    <t>C02670/C00072/glac,,,,,,,C02670/C00072/glac,</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$$$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$</t>
+  </si>
+  <si>
+    <t>De novo fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E2345,E92,E2166</t>
+  </si>
+  <si>
+    <t>,,</t>
+  </si>
+  <si>
+    <t>$$</t>
+  </si>
+  <si>
+    <t>Limonene and pinene degradation</t>
+  </si>
+  <si>
+    <t>E262,E261,E264</t>
+  </si>
+  <si>
+    <t>Biopterin metabolism</t>
+  </si>
+  <si>
+    <t>E1459,E1439,E1455,E1735,E288</t>
+  </si>
+  <si>
+    <t>CE2705/CE5236,C00268/C02953/C04244,CE2705/CE5236,C15522/thbpt4acam,C00082</t>
+  </si>
+  <si>
+    <t>quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tyrosine</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E1074</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
+  </si>
+  <si>
+    <t>E2345,E2119,E2409</t>
+  </si>
+  <si>
     <t>Hyaluronan Metabolism</t>
   </si>
   <si>
-    <t>E2845,E35,E33,E57</t>
-  </si>
-  <si>
-    <t>C00518,C01074/C00645/C00140,C01074/C00645/C00140,C00618/C06472/C00191</t>
-  </si>
-  <si>
-    <t>Hyaluronate; Hyaluronic acid; [beta-N-Acetyl-D-glucosaminyl(1,4)beta-D-glucuronosyl(1,3)]n$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
-  </si>
-  <si>
-    <t>Tryptophan metabolism</t>
-  </si>
-  <si>
-    <t>E2752,E796,E823,E1154,E877,E123,E1438,E640,E760,E691,E2796,E647,E1186,E527,E1138,E1187,E693,E737,E846,E738,E601,E2748,E1735,E634,E651,E696,E705,E2750,E1439,E767,E1142,E706,E1436</t>
-  </si>
-  <si>
-    <t>CE3140,C05635/C16596,CE6205,C00978,CE5860,C05645,C04148/C05642,C00637,C05638,C05639,C00021,C05660,CE2119/C05643,C00954/C05634,C00643,CE2119/C05643,C05639,CE2122,C02406/C02700,CE2122,C00780,CE3140,C15522/thbpt4acam,CE1918/CE5629,C05660,C05639,C01252,CE3140,C00268/C02953/C04244,C00328/C05647,C00643,C01252,C04148/C05642</t>
-  </si>
-  <si>
-    <t>$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$5-methoxytryptophol$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$$4-(2-Amino-3-hydroxyphenyl)-2,4-dioxobutanoate$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$Indole-3-acetaldehyde$5-Hydroxykynurenamine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$S-Adenosyl-L-homocysteine$5-Methoxyindoleacetate$/6-Hydroxymelatonin$Indole-3-acetate/5-Hydroxyindoleacetaldehyde$5-Hydroxy-L-tryptophan$/6-Hydroxymelatonin$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$methyl indole-3-acetate$Formylkynurenine/L-Formylkynurenine$methyl indole-3-acetate$Serotonin$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$5-hydroxytryptophol/1,2-dehydrosalsolinol$5-Methoxyindoleacetate$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$4-(2-Aminophenyl)-2,4-dioxobutanoate$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$L-Kynurenine/Formyl-5-hydroxykynurenamine$5-Hydroxy-L-tryptophan$4-(2-Aminophenyl)-2,4-dioxobutanoate$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine</t>
-  </si>
-  <si>
-    <t>D4&amp;E4-neuroprostanes formation</t>
-  </si>
-  <si>
-    <t>E2895,E1408,E567,E569</t>
-  </si>
-  <si>
-    <t>CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,CE6429/CE6423/CE6420/CE6426/CE6438/CE6432/CE6435,C02670/C00072/glac,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>///////$//////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Porphyrin metabolism</t>
-  </si>
-  <si>
-    <t>E567,E57,E354,E1520,E569</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,C00618/C06472/C00191,C00931,C05791,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate$Porphobilinogen$D-Urobilinogen$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Limonene and pinene degradation</t>
-  </si>
-  <si>
-    <t>E262,E257,E261,E264</t>
-  </si>
-  <si>
-    <t>C02452/C11409/C02759/C00964,C02452/C11409/C02759/C00964,C02452/C11409/C02759/C00964,C02452/C11409/C02759/C00964</t>
-  </si>
-  <si>
-    <t>Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol$Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol$Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol$Perillyl alcohol; (-)-Perillyl alcohol; p-Mentha-1,8-dien-7-ol; (-)-Perillylalcohol/(+)-trans-Carveol; (4S,6R)-trans-Carveol//(-)-trans-Carveol</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E2796,E1844,E26,E29,E1345</t>
-  </si>
-  <si>
-    <t>C00021,C00212/C00330,,,</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$Adenosine/Deoxyguanosine$$$</t>
+    <t>E2845,E33</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
+  </si>
+  <si>
+    <t>E975,E2549</t>
+  </si>
+  <si>
+    <t>Vitamin B2 (riboflavin) metabolism</t>
+  </si>
+  <si>
+    <t>E276,E3036</t>
+  </si>
+  <si>
+    <t>Fatty acid activation</t>
+  </si>
+  <si>
+    <t>E2345,E92</t>
+  </si>
+  <si>
+    <t>Vitamin A (retinol) metabolism</t>
+  </si>
+  <si>
+    <t>E2485,E2166,E2012,E2513</t>
+  </si>
+  <si>
+    <t>,,,</t>
+  </si>
+  <si>
+    <t>$$$</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>E2345,E3164,E2383</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>E855,E853</t>
+  </si>
+  <si>
+    <t>Tyrosine metabolism</t>
+  </si>
+  <si>
+    <t>E570,E918,E143,E1598,E412,E1438,E190,E1599,E158,E618,E145,E192,E2796,E1222,E288,E160,E220,E148,E336,E830,E634,E1735,E337,E831,E179,E1439,E66,E569,E1436,E170</t>
+  </si>
+  <si>
+    <t>C02670/C00072/glac,CE2176,CE5536/C01586,,C05589/C00788,C04148/C05642,C09642,,C00355,,CE5536/C01586,C09642,C00021,,C00082,C00355,C05576,CE5536/C01586,C05583/C05582,C02763/C00166,CE1918/CE5629,C15522/thbpt4acam,C05583/C05582,C02763/C00166,C16586/CE2173,C00268/C02953/C04244,C05587/C07453,C02670/C00072/glac,C04148/C05642,C05588</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$3-O-methyldopa$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$$3,4-Dihydroxy-L-phenylalanine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$S-Adenosyl-L-homocysteine$$L-Tyrosine$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxyphenylethyleneglycol$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$enol-Phenylpyruvate/Phenylpyruvate$5-hydroxytryptophol/1,2-dehydrosalsolinol$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$enol-Phenylpyruvate/Phenylpyruvate$2-Phenyl-1,3-propanediol monocarbamate/$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$3-Methoxytyramine/Epinine; Deoxyepinephrine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$L-Metanephrine</t>
+  </si>
+  <si>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2263,E1550,E1176,E423,E2796,E2269,E1526,E1768,E1771,E2264</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,C00951,C02538,dhea/C03772/C01227/C00674/C00535,C00021,andrstndn/C00280,C00468,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,C18045/C14497/C18075/C05294/C05139</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Estradiol-17beta; beta-Estradiol; Estradiol$Estrone 3-sulfate$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$S-Adenosyl-L-homocysteine$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one</t>
+  </si>
+  <si>
+    <t>Fatty Acid Metabolism</t>
+  </si>
+  <si>
+    <t>Selenoamino acid metabolism</t>
+  </si>
+  <si>
+    <t>E1844</t>
+  </si>
+  <si>
+    <t>C00212/C00330</t>
+  </si>
+  <si>
+    <t>Adenosine/Deoxyguanosine</t>
+  </si>
+  <si>
+    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
+  </si>
+  <si>
+    <t>E2570,E2796</t>
+  </si>
+  <si>
+    <t>C01185,C00021</t>
+  </si>
+  <si>
+    <t>Nicotinate D-ribonucleotide$S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Arginine and Proline Metabolism</t>
+  </si>
+  <si>
+    <t>E29,E26</t>
+  </si>
+  <si>
+    <t>C00170,C00170</t>
+  </si>
+  <si>
+    <t>5-Methylthioadenosine$5-Methylthioadenosine</t>
+  </si>
+  <si>
+    <t>Glycerophospholipid metabolism</t>
+  </si>
+  <si>
+    <t>E2383,E92,E2796,E2985,E2513</t>
+  </si>
+  <si>
+    <t>,,C00021,,</t>
+  </si>
+  <si>
+    <t>$$S-Adenosyl-L-homocysteine$$</t>
+  </si>
+  <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2505</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
+    <t>E2192,E3007</t>
+  </si>
+  <si>
+    <t>Lysine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1926</t>
+  </si>
+  <si>
+    <t>C00021,</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E2796,E831,E830</t>
+  </si>
+  <si>
+    <t>C00021,C02763/C00166,C02763/C00166</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$enol-Phenylpyruvate/Phenylpyruvate$enol-Phenylpyruvate/Phenylpyruvate</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E471,E1473,E1074</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>E2839,E33</t>
+  </si>
+  <si>
+    <t>Hexose phosphorylation</t>
+  </si>
+  <si>
+    <t>E830,E831,E784</t>
+  </si>
+  <si>
+    <t>C02763/C00166,C02763/C00166,</t>
+  </si>
+  <si>
+    <t>enol-Phenylpyruvate/Phenylpyruvate$enol-Phenylpyruvate/Phenylpyruvate$</t>
+  </si>
+  <si>
+    <t>Purine metabolism</t>
+  </si>
+  <si>
+    <t>E570,E572,E116,E1844,E573,E569</t>
+  </si>
+  <si>
+    <t>C02670/C00072/glac,C00262,,C00212/C00330,C00262,C02670/C00072/glac</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$Hypoxanthine$$Adenosine/Deoxyguanosine$Hypoxanthine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
+  </si>
+  <si>
+    <t>Keratan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E33</t>
+  </si>
+  <si>
+    <t>Omega-3 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E92</t>
+  </si>
+  <si>
+    <t>Phosphatidylinositol phosphate metabolism</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E1403</t>
+  </si>
+  <si>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>CoA Catabolism</t>
+  </si>
+  <si>
+    <t>E2192</t>
   </si>
   <si>
     <t>Heparan sulfate degradation</t>
   </si>
   <si>
-    <t>E35,E33,E57</t>
-  </si>
-  <si>
-    <t>C01074/C00645/C00140,C01074/C00645/C00140,C00618/C06472/C00191</t>
-  </si>
-  <si>
-    <t>N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
-  </si>
-  <si>
-    <t>Urea cycle/amino group metabolism</t>
-  </si>
-  <si>
-    <t>E143,E148,E1634,E2796,E1411,E26,E412,E29,E1535,E471,E145,E413</t>
-  </si>
-  <si>
-    <t>CE5536/C01586,CE5536/C01586,,C00021,CE2934,,C05589/C00788,,C04692,,CE5536/C01586,C05589/C00788</t>
-  </si>
-  <si>
-    <t>adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$S-Adenosyl-L-homocysteine$o-methylhippurate$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
-  </si>
-  <si>
-    <t>Biopterin metabolism</t>
-  </si>
-  <si>
-    <t>E912,E1459,E1455,E1439,E1735,E288</t>
-  </si>
-  <si>
-    <t>C00079,CE2705/CE5236,CE2705/CE5236,C00268/C02953/C04244,C15522/thbpt4acam,C00082</t>
-  </si>
-  <si>
-    <t>L-Phenylalanine$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tyrosine</t>
-  </si>
-  <si>
-    <t>Saturated fatty acids beta-oxidation</t>
-  </si>
-  <si>
-    <t>E2345</t>
-  </si>
-  <si>
-    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
-  </si>
-  <si>
-    <t>E2796</t>
-  </si>
-  <si>
-    <t>C00021</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E2839,E35,E33,E2970</t>
-  </si>
-  <si>
-    <t>,C01074/C00645/C00140,C01074/C00645/C00140,</t>
-  </si>
-  <si>
-    <t>$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$</t>
-  </si>
-  <si>
-    <t>Linoleate metabolism</t>
-  </si>
-  <si>
-    <t>E567,E92,E2348,E113,E2350,E2738,E2084,E2639,E569,E479</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,,,,,,,,C02670/C00072/glac,</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$$$$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>E1514,E1512,E1071,E445,E1039</t>
-  </si>
-  <si>
-    <t>C00475,C00475,C00299,C00526,C00214</t>
-  </si>
-  <si>
-    <t>Cytidine$Cytidine$Uridine$Deoxyuridine$Thymidine</t>
-  </si>
-  <si>
-    <t>C21-steroid hormone biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2503,E2263,E2398,E1116,E1550,E1176,E1163,E1164,E2269,E2399,E1768,E1771,E1691,E2457,E2669</t>
-  </si>
-  <si>
-    <t>,C05139,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C00951,,C05487/C05475/C05478,C05487/C05475/C05478,andrstndn/C00280,17ahprgstrn/C03205/C05498/C01176,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,,,C05489</t>
-  </si>
-  <si>
-    <t>$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Estradiol-17beta; beta-Estradiol; Estradiol$$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$$$11beta,17alpha,21-Trihydroxypregnenolone</t>
-  </si>
-  <si>
-    <t>De novo fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E2345,E92,E2166</t>
-  </si>
-  <si>
-    <t>,,</t>
-  </si>
-  <si>
-    <t>$$</t>
-  </si>
-  <si>
-    <t>Keratan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E35,E33</t>
-  </si>
-  <si>
-    <t>C01074/C00645/C00140,C01074/C00645/C00140</t>
-  </si>
-  <si>
-    <t>N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol phosphate metabolism</t>
-  </si>
-  <si>
-    <t>E2345,E57</t>
-  </si>
-  <si>
-    <t>,C00618/C06472/C00191</t>
-  </si>
-  <si>
-    <t>$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
+    <t>Histidine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1403</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1714</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E2442,E1452</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>E2859,E3025,E3062,E3005</t>
+  </si>
+  <si>
+    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
+  </si>
+  <si>
+    <t>E570,E569</t>
+  </si>
+  <si>
+    <t>C02670/C00072/glac,C02670/C00072/glac</t>
+  </si>
+  <si>
+    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E975,E989,E1301,E1286,E2899,E1899</t>
+  </si>
+  <si>
+    <t>,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E975,E92,E2513</t>
+  </si>
+  <si>
+    <t>Vitamin B9 (folate) metabolism</t>
+  </si>
+  <si>
+    <t>E1823</t>
+  </si>
+  <si>
+    <t>Aminosugars metabolism</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E975,E570,E569</t>
+  </si>
+  <si>
+    <t>,C02670/C00072/glac,C02670/C00072/glac</t>
+  </si>
+  <si>
+    <t>$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
+  </si>
+  <si>
+    <t>Bile acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E2942,E2940</t>
+  </si>
+  <si>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycolysis and Gluconeogenesis</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+  </si>
+  <si>
+    <t>R Group Synthesis</t>
+  </si>
+  <si>
+    <t>C5-Branched dibasic acid metabolism</t>
+  </si>
+  <si>
+    <t>Pyruvate Metabolism</t>
   </si>
   <si>
     <t>Chondroitin sulfate degradation</t>
   </si>
   <si>
-    <t>E57</t>
-  </si>
-  <si>
-    <t>C00618/C06472/C00191</t>
-  </si>
-  <si>
-    <t>3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>E1074</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>E2345,E2119,E2409</t>
-  </si>
-  <si>
-    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
-  </si>
-  <si>
-    <t>E975,E2549</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>Drug metabolism - cytochrome P450</t>
-  </si>
-  <si>
-    <t>E521,E179,E796,E522,E1274,E2308,E803,E801,E940</t>
-  </si>
-  <si>
-    <t>C16595/C16587,C16586/CE2173,C05635/C16596,C16595/C16587,,,C16591,C16591,</t>
-  </si>
-  <si>
-    <t>4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$2-Phenyl-1,3-propanediol monocarbamate/$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$$$3-Carbamoyl-2-phenylpropionic acid$3-Carbamoyl-2-phenylpropionic acid$</t>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycerolipid metabolism</t>
+  </si>
+  <si>
+    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
+  </si>
+  <si>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - globoseries</t>
+  </si>
+  <si>
+    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - lactoseries</t>
+  </si>
+  <si>
+    <t>Parathio degradation</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>Blood Group Biosynthesis</t>
+  </si>
+  <si>
+    <t>Electron transport chain</t>
+  </si>
+  <si>
+    <t>Vitamin H (biotin) metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
+  </si>
+  <si>
+    <t>Caffeine metabolism</t>
+  </si>
+  <si>
+    <t>Lipoate metabolism</t>
+  </si>
+  <si>
+    <t>Heparan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>Glyoxylate and Dicarboxylate Metabolism</t>
+  </si>
+  <si>
+    <t>Valine, leucine and isoleucine degradation</t>
+  </si>
+  <si>
+    <t>Glycosaminoglycan degradation</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation</t>
+  </si>
+  <si>
+    <t>ROS Detoxification</t>
+  </si>
+  <si>
+    <t>Butanoate metabolism</t>
+  </si>
+  <si>
+    <t>Mono-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
+  </si>
+  <si>
+    <t>Geraniol degradation</t>
+  </si>
+  <si>
+    <t>Vitamin D</t>
+  </si>
+  <si>
+    <t>Dynorphin metabolism</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation, peroxisome</t>
+  </si>
+  <si>
+    <t>Polyunsaturated fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>Alanine and Aspartate Metabolism</t>
+  </si>
+  <si>
+    <t>Keratan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>TCA cycle</t>
+  </si>
+  <si>
+    <t>3-Chloroacrylic acid degradation</t>
+  </si>
+  <si>
+    <t>Sphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>O-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Proteoglycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin K metabolism</t>
+  </si>
+  <si>
+    <t>Glutamate metabolism</t>
+  </si>
+  <si>
+    <t>Benzoate degradation via CoA ligation</t>
+  </si>
+  <si>
+    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
+  </si>
+  <si>
+    <t>Vitamin B6 (pyridoxine) metabolism</t>
   </si>
   <si>
     <t>Pentose and Glucuronate Interconversions</t>
-  </si>
-  <si>
-    <t>Tyrosine metabolism</t>
-  </si>
-  <si>
-    <t>E918,E143,E1598,E412,E1438,E190,E430,E1599,E158,E618,E145,E413,E192,E680,E2796,E1222,E288,E160,E220,E912,E148,E634,E914,E1735,E337,E831,E567,E179,E1439,E66,E569,E1436,E170</t>
-  </si>
-  <si>
-    <t>CE2176,CE5536/C01586,,C05589/C00788,C04148/C05642,C09642,C05580,,C00355,,CE5536/C01586,C05589/C00788,C09642,,C00021,,C00082,C00355,C05576,C00079,CE5536/C01586,CE1918/CE5629,CE2176,C15522/thbpt4acam,C05583/C05582,C02763/C00166,C02670/C00072/glac,C16586/CE2173,C00268/C02953/C04244,C05587/C07453,C02670/C00072/glac,C04148/C05642,C05588</t>
-  </si>
-  <si>
-    <t>3-O-methyldopa$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3,4-Dihydroxymandelate$$3,4-Dihydroxy-L-phenylalanine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$$S-Adenosyl-L-homocysteine$$L-Tyrosine$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxyphenylethyleneglycol$L-Phenylalanine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$5-hydroxytryptophol/1,2-dehydrosalsolinol$3-O-methyldopa$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$enol-Phenylpyruvate/Phenylpyruvate$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$2-Phenyl-1,3-propanediol monocarbamate/$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$3-Methoxytyramine/Epinine; Deoxyepinephrine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$L-Metanephrine</t>
-  </si>
-  <si>
-    <t>Vitamin B2 (riboflavin) metabolism</t>
-  </si>
-  <si>
-    <t>E276,E3036</t>
-  </si>
-  <si>
-    <t>Fatty acid activation</t>
-  </si>
-  <si>
-    <t>E2345,E92</t>
-  </si>
-  <si>
-    <t>Glycerophospholipid metabolism</t>
-  </si>
-  <si>
-    <t>E92,E2383,E2796,E1351,E2985,E2513</t>
-  </si>
-  <si>
-    <t>,,C00021,,,</t>
-  </si>
-  <si>
-    <t>$$S-Adenosyl-L-homocysteine$$$</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>E2839,E35,E33</t>
-  </si>
-  <si>
-    <t>,C01074/C00645/C00140,C01074/C00645/C00140</t>
-  </si>
-  <si>
-    <t>$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine$N-Acetylgalactosamine; N-Acetylchondrosamine; 2-Acetamido-2-deoxygalactose; GalNAc/N-Acetyl-D-mannosamine; 2-Acetamido-2-deoxy-D-mannose/N-Acetyl-D-glucosamine</t>
-  </si>
-  <si>
-    <t>Vitamin A (retinol) metabolism</t>
-  </si>
-  <si>
-    <t>E2485,E2166,E2012,E2513</t>
-  </si>
-  <si>
-    <t>,,,</t>
-  </si>
-  <si>
-    <t>$$$</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>E2345,E3164,E2383</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
-  </si>
-  <si>
-    <t>E855,E853</t>
-  </si>
-  <si>
-    <t>Fatty Acid Metabolism</t>
-  </si>
-  <si>
-    <t>Selenoamino acid metabolism</t>
-  </si>
-  <si>
-    <t>E1844</t>
-  </si>
-  <si>
-    <t>C00212/C00330</t>
-  </si>
-  <si>
-    <t>Adenosine/Deoxyguanosine</t>
-  </si>
-  <si>
-    <t>Purine metabolism</t>
-  </si>
-  <si>
-    <t>E567,E933,E572,E116,E1844,E569,E1995</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,,C00262,,C00212/C00330,C02670/C00072/glac,C01762</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$Hypoxanthine$$Adenosine/Deoxyguanosine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$Xanthosine</t>
-  </si>
-  <si>
-    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
-  </si>
-  <si>
-    <t>E567,E57,E569</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,C00618/C06472/C00191,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$3-Dehydro-L-gulonate/L-Iduronic acid/D-Glucuronate$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
-  </si>
-  <si>
-    <t>E2570,E2796</t>
-  </si>
-  <si>
-    <t>C01185,C00021</t>
-  </si>
-  <si>
-    <t>Nicotinate D-ribonucleotide$S-Adenosyl-L-homocysteine</t>
-  </si>
-  <si>
-    <t>Arginine and Proline Metabolism</t>
-  </si>
-  <si>
-    <t>E26,E29</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>E2505</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
-  </si>
-  <si>
-    <t>E2183</t>
-  </si>
-  <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>E2192,E3007</t>
-  </si>
-  <si>
-    <t>Aminosugars metabolism</t>
-  </si>
-  <si>
-    <t>Lysine metabolism</t>
-  </si>
-  <si>
-    <t>E2796,E1926</t>
-  </si>
-  <si>
-    <t>C00021,</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E471,E1473,E1074</t>
-  </si>
-  <si>
-    <t>Omega-3 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E92</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E1403</t>
-  </si>
-  <si>
-    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
-  </si>
-  <si>
-    <t>E1990</t>
-  </si>
-  <si>
-    <t>CoA Catabolism</t>
-  </si>
-  <si>
-    <t>E2192</t>
-  </si>
-  <si>
-    <t>Histidine metabolism</t>
-  </si>
-  <si>
-    <t>E2796,E1403</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>E2796,E1714</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E2442,E1452</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E2859,E3025,E3062,E3005</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E975,E989,E1301,E1286,E2899,E1899</t>
-  </si>
-  <si>
-    <t>,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$</t>
-  </si>
-  <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E2796,E831</t>
-  </si>
-  <si>
-    <t>C00021,C02763/C00166</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$enol-Phenylpyruvate/Phenylpyruvate</t>
-  </si>
-  <si>
-    <t>Butanoate metabolism</t>
-  </si>
-  <si>
-    <t>E1044</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E975,E92,E2513</t>
-  </si>
-  <si>
-    <t>Hexose phosphorylation</t>
-  </si>
-  <si>
-    <t>E831,E784</t>
-  </si>
-  <si>
-    <t>C02763/C00166,</t>
-  </si>
-  <si>
-    <t>enol-Phenylpyruvate/Phenylpyruvate$</t>
-  </si>
-  <si>
-    <t>Vitamin B9 (folate) metabolism</t>
-  </si>
-  <si>
-    <t>E1823</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (pyridoxine) metabolism</t>
-  </si>
-  <si>
-    <t>E383</t>
-  </si>
-  <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2263,E1550,E1176,E2796,E2269,E1768,E1771</t>
-  </si>
-  <si>
-    <t>C05139,C00951,,C00021,andrstndn/C00280,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179</t>
-  </si>
-  <si>
-    <t>16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Estradiol-17beta; beta-Estradiol; Estradiol$$S-Adenosyl-L-homocysteine$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E975,E567,E569</t>
-  </si>
-  <si>
-    <t>,C02670/C00072/glac,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Bile acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E2942,E2940</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
-  </si>
-  <si>
-    <t>R Group Synthesis</t>
-  </si>
-  <si>
-    <t>C5-Branched dibasic acid metabolism</t>
-  </si>
-  <si>
-    <t>Pyruvate Metabolism</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycerolipid metabolism</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - globoseries</t>
-  </si>
-  <si>
-    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - lactoseries</t>
-  </si>
-  <si>
-    <t>Parathio degradation</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>Blood Group Biosynthesis</t>
-  </si>
-  <si>
-    <t>Electron transport chain</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Caffeine metabolism</t>
-  </si>
-  <si>
-    <t>Lipoate metabolism</t>
-  </si>
-  <si>
-    <t>Heparan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>Glyoxylate and Dicarboxylate Metabolism</t>
-  </si>
-  <si>
-    <t>Valine, leucine and isoleucine degradation</t>
-  </si>
-  <si>
-    <t>Glycosaminoglycan degradation</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation</t>
-  </si>
-  <si>
-    <t>ROS Detoxification</t>
-  </si>
-  <si>
-    <t>Mono-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
-  </si>
-  <si>
-    <t>Geraniol degradation</t>
-  </si>
-  <si>
-    <t>Vitamin D</t>
-  </si>
-  <si>
-    <t>Dynorphin metabolism</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation, peroxisome</t>
-  </si>
-  <si>
-    <t>Polyunsaturated fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>Alanine and Aspartate Metabolism</t>
-  </si>
-  <si>
-    <t>Keratan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>TCA cycle</t>
-  </si>
-  <si>
-    <t>3-Chloroacrylic acid degradation</t>
-  </si>
-  <si>
-    <t>Sphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>O-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Proteoglycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin K metabolism</t>
-  </si>
-  <si>
-    <t>Glutamate metabolism</t>
-  </si>
-  <si>
-    <t>Benzoate degradation via CoA ligation</t>
-  </si>
-  <si>
-    <t>Dimethyl-branched-chain fatty acid mitochondrial beta-oxidation</t>
   </si>
   <si>
     <t>Atrazine degradation</t>
@@ -1135,13 +1069,13 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="D2">
-        <v>0.01287373321456782</v>
+        <v>0.01241995932841465</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,13 +1092,13 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0.017982891043848</v>
+        <v>0.02744491689215307</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1181,13 +1115,13 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="D4">
-        <v>0.03302465504781432</v>
+        <v>0.02978101208383052</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1210,7 +1144,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.03863800608393136</v>
+        <v>0.03184820423186165</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1227,13 +1161,13 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>0.04630174282785163</v>
+        <v>0.04189845548814305</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1250,107 +1184,107 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0.05341086704425136</v>
+        <v>0.07107443572376936</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0.07107443572376936</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
         <v>31</v>
       </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8">
-        <v>0.05877212147694997</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>32</v>
-      </c>
-      <c r="F8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>43</v>
       </c>
       <c r="D9">
-        <v>0.06662072906337708</v>
+        <v>0.08127594494210182</v>
       </c>
       <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
         <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>0.0878136501907531</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
         <v>39</v>
       </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>19</v>
-      </c>
-      <c r="D10">
-        <v>0.07115846792490882</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>40</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>0.1034268331624679</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
         <v>43</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.07367943395909313</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1359,13 +1293,13 @@
         <v>45</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D12">
-        <v>0.07367943395909313</v>
+        <v>0.1261491403505823</v>
       </c>
       <c r="E12" t="s">
         <v>46</v>
@@ -1382,13 +1316,13 @@
         <v>49</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>0.08688929597821886</v>
+        <v>0.1287541385859061</v>
       </c>
       <c r="E13" t="s">
         <v>50</v>
@@ -1405,1167 +1339,1107 @@
         <v>53</v>
       </c>
       <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
         <v>10</v>
       </c>
-      <c r="C14">
-        <v>37</v>
-      </c>
       <c r="D14">
-        <v>0.09451941984168333</v>
+        <v>0.1287541385859061</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
       <c r="C15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D15">
-        <v>0.1132417942555587</v>
+        <v>0.1306196534512025</v>
       </c>
       <c r="E15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" t="s">
         <v>58</v>
-      </c>
-      <c r="F15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>0.1318633300280667</v>
+        <v>0.1421824843279945</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>0.1389556478042386</v>
+        <v>0.1519974454210854</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>0.1444345473185325</v>
+        <v>0.1711735937211139</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>0.1444345473185325</v>
+        <v>0.1711735937211139</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>0.1454261272919783</v>
+        <v>0.2227189459000689</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>0.1454261272919783</v>
+        <v>0.2227189459000689</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>72</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D22">
-        <v>0.1687870792087528</v>
+        <v>0.2250046217710627</v>
       </c>
       <c r="E22" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D23">
-        <v>0.1898623552545335</v>
+        <v>0.2568696324431522</v>
       </c>
       <c r="E23" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
         <v>9</v>
       </c>
-      <c r="C24">
-        <v>40</v>
-      </c>
       <c r="D24">
-        <v>0.2149207576343255</v>
+        <v>0.265407304078923</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="D25">
-        <v>0.2222651720139157</v>
+        <v>0.2782138115325793</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B26">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="D26">
-        <v>0.2223155913345994</v>
+        <v>0.2871884506142754</v>
       </c>
       <c r="E26" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>0.2354246147123578</v>
+        <v>0.2871884506142754</v>
       </c>
       <c r="E27" t="s">
-        <v>99</v>
-      </c>
-      <c r="F27" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>0.2354246147123578</v>
+        <v>0.2871884506142754</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D29">
-        <v>0.2360464530007899</v>
+        <v>0.3175408816658544</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F29" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>0.2435589317826591</v>
+        <v>0.3175408816658544</v>
       </c>
       <c r="E30" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D31">
-        <v>0.2514075393690862</v>
+        <v>0.332532226349137</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F31" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G31" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>0.2892892556427623</v>
+        <v>0.3404648661367036</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
-      </c>
-      <c r="F32" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D33">
-        <v>0.2894237071645855</v>
+        <v>0.3438765735029664</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="F33" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G33" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D34">
-        <v>0.2894237071645855</v>
+        <v>0.3438765735029664</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F34" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D35">
-        <v>0.2996420228231458</v>
+        <v>0.3516243424480261</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>115</v>
+      </c>
+      <c r="F35" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D36">
-        <v>0.2996420228231458</v>
+        <v>0.3516243424480261</v>
       </c>
       <c r="E36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F36" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="G36" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B37">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D37">
-        <v>0.3191374934875044</v>
+        <v>0.3731197794995042</v>
       </c>
       <c r="E37" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F37" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="G37" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D38">
-        <v>0.3199442026184434</v>
+        <v>0.3759936807784743</v>
       </c>
       <c r="E38" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F38" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G38" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D39">
-        <v>0.3256415858556999</v>
+        <v>0.3779432278449102</v>
       </c>
       <c r="E39" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F39" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>0.3256415858556999</v>
+        <v>0.3799936135527134</v>
       </c>
       <c r="E40" t="s">
-        <v>137</v>
-      </c>
-      <c r="F40" t="s">
-        <v>87</v>
-      </c>
-      <c r="G40" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>0.3447168955143611</v>
+        <v>0.3799936135527134</v>
       </c>
       <c r="E41" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42">
-        <v>0.3447168955143611</v>
+        <v>0.3799936135527134</v>
       </c>
       <c r="E42" t="s">
-        <v>141</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>0.3569519840002689</v>
+        <v>0.3799936135527134</v>
       </c>
       <c r="E43" t="s">
-        <v>143</v>
-      </c>
-      <c r="F43" t="s">
-        <v>87</v>
-      </c>
-      <c r="G43" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D44">
-        <v>0.3569519840002689</v>
+        <v>0.4030520495453858</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="F44" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G44" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D45">
-        <v>0.3569519840002689</v>
+        <v>0.4223290364867817</v>
       </c>
       <c r="E45" t="s">
-        <v>146</v>
-      </c>
-      <c r="F45" t="s">
-        <v>147</v>
-      </c>
-      <c r="G45" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>0.3707332649871431</v>
+        <v>0.4223290364867817</v>
       </c>
       <c r="E46" t="s">
-        <v>150</v>
-      </c>
-      <c r="F46" t="s">
-        <v>67</v>
-      </c>
-      <c r="G46" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D47">
-        <v>0.3891531234769163</v>
+        <v>0.4350010924186148</v>
       </c>
       <c r="E47" t="s">
-        <v>152</v>
+        <v>142</v>
+      </c>
+      <c r="F47" t="s">
+        <v>112</v>
+      </c>
+      <c r="G47" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D48">
-        <v>0.3891531234769163</v>
+        <v>0.4350010924186148</v>
       </c>
       <c r="E48" t="s">
-        <v>154</v>
+        <v>144</v>
+      </c>
+      <c r="F48" t="s">
+        <v>112</v>
+      </c>
+      <c r="G48" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>0.433034738911951</v>
+        <v>0.4350010924186148</v>
       </c>
       <c r="E49" t="s">
-        <v>156</v>
+        <v>146</v>
+      </c>
+      <c r="F49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G49" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D50">
-        <v>0.433034738911951</v>
+        <v>0.4498579855800743</v>
       </c>
       <c r="E50" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="F50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D51">
-        <v>0.4533705315877044</v>
+        <v>0.4605973008856994</v>
       </c>
       <c r="E51" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F51" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G51" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D52">
-        <v>0.4533705315877044</v>
+        <v>0.4862607351136956</v>
       </c>
       <c r="E52" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F52" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G52" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D53">
-        <v>0.4533705315877044</v>
+        <v>0.4898405068822373</v>
       </c>
       <c r="E53" t="s">
-        <v>164</v>
-      </c>
-      <c r="F53" t="s">
-        <v>87</v>
-      </c>
-      <c r="G53" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D54">
-        <v>0.4795381590225374</v>
+        <v>0.5111342666509806</v>
       </c>
       <c r="E54" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F54" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="G54" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D55">
-        <v>0.5164451017629956</v>
+        <v>0.534999411774592</v>
       </c>
       <c r="E55" t="s">
-        <v>168</v>
-      </c>
-      <c r="F55" t="s">
-        <v>169</v>
-      </c>
-      <c r="G55" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D56">
-        <v>0.5188148098351288</v>
+        <v>0.534999411774592</v>
       </c>
       <c r="E56" t="s">
-        <v>172</v>
-      </c>
-      <c r="F56" t="s">
-        <v>173</v>
-      </c>
-      <c r="G56" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D57">
-        <v>0.5206467118199695</v>
+        <v>0.5673854220937463</v>
       </c>
       <c r="E57" t="s">
-        <v>176</v>
+        <v>164</v>
+      </c>
+      <c r="F57" t="s">
+        <v>165</v>
+      </c>
+      <c r="G57" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D58">
-        <v>0.5256718374481101</v>
+        <v>0.5701248718508932</v>
       </c>
       <c r="E58" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F58" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G58" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D59">
-        <v>0.5322431555772172</v>
-      </c>
-      <c r="E59" t="s">
-        <v>180</v>
-      </c>
-      <c r="F59" t="s">
-        <v>181</v>
-      </c>
-      <c r="G59" t="s">
-        <v>182</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D60">
-        <v>0.5373523134064974</v>
-      </c>
-      <c r="E60" t="s">
-        <v>184</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D61">
-        <v>0.5524949160518311</v>
-      </c>
-      <c r="E61" t="s">
-        <v>186</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
         <v>7</v>
       </c>
-      <c r="C62">
-        <v>51</v>
-      </c>
       <c r="D62">
-        <v>0.5556545268146754</v>
-      </c>
-      <c r="E62" t="s">
-        <v>188</v>
-      </c>
-      <c r="F62" t="s">
-        <v>189</v>
-      </c>
-      <c r="G62" t="s">
-        <v>190</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>0.5757046100065545</v>
-      </c>
-      <c r="E63" t="s">
-        <v>192</v>
-      </c>
-      <c r="F63" t="s">
-        <v>193</v>
-      </c>
-      <c r="G63" t="s">
-        <v>194</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
         <v>2</v>
       </c>
-      <c r="C64">
-        <v>22</v>
-      </c>
       <c r="D64">
-        <v>0.5762424160938472</v>
-      </c>
-      <c r="E64" t="s">
-        <v>196</v>
-      </c>
-      <c r="F64" t="s">
-        <v>87</v>
-      </c>
-      <c r="G64" t="s">
-        <v>88</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
       <c r="C65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D66">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D67">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D68">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2574,96 +2448,96 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D70">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D71">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D72">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D74">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2672,26 +2546,26 @@
         <v>5</v>
       </c>
       <c r="D76">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D77">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2700,26 +2574,26 @@
         <v>3</v>
       </c>
       <c r="D78">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D79">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2728,12 +2602,12 @@
         <v>5</v>
       </c>
       <c r="D80">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2742,68 +2616,68 @@
         <v>3</v>
       </c>
       <c r="D81">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D82">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D85">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2812,110 +2686,110 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D89">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2924,12 +2798,12 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2938,12 +2812,12 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2952,96 +2826,96 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D97">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D99">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3050,12 +2924,12 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3064,82 +2938,82 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D108">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D109">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3148,12 +3022,12 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3162,12 +3036,12 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3176,12 +3050,12 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3190,12 +3064,12 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3204,12 +3078,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3218,12 +3092,12 @@
         <v>5</v>
       </c>
       <c r="D115">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3232,12 +3106,12 @@
         <v>3</v>
       </c>
       <c r="D116">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3246,12 +3120,12 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3260,12 +3134,12 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3274,12 +3148,12 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3288,7 +3162,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>0.6086284264130014</v>
+        <v>0.6167123241626191</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_pathwayanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="216">
   <si>
     <t>pathway</t>
   </si>
@@ -37,567 +37,525 @@
     <t>overlap_features (name)</t>
   </si>
   <si>
+    <t>C21-steroid hormone biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2503,E2263,E2398,E1116,E1163,E423,E422,E1164,E2269,E2399,E1526,E1768,E1771,E1691,E2457,E2669</t>
+  </si>
+  <si>
+    <t>CE2211/C05480,C18045/C14497/C18075/C05294/C05139,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C05487/C05475/C05478,dhea/C03772/C01227/C00674/C00535,dhea/C03772/C01227/C00674/C00535,C05487/C05475/C05478,andrstndn/C00280,17ahprgstrn/C03205/C05498/C01176,C00468,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,CE1352,C05472,C05489/C05471/C05474</t>
+  </si>
+  <si>
+    <t>allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$17alpha-hydroxypregnenolone sulfate$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>E26,E29,E2796,E1844,E1345</t>
+  </si>
+  <si>
+    <t>C00170,C00170,C00021,C00212/C00330,C02291/C00542</t>
+  </si>
+  <si>
+    <t>5-Methylthioadenosine$5-Methylthioadenosine$S-Adenosyl-L-homocysteine$Adenosine/Deoxyguanosine$L-Cystathionine/Cystathionine</t>
+  </si>
+  <si>
     <t>Tryptophan metabolism</t>
   </si>
   <si>
-    <t>E2752,E796,E823,E1154,E877,E123,E1438,E640,E760,E691,E2796,E647,E1186,E527,E1138,E1187,E693,E649,E737,E738,E601,E2748,E1735,E634,E651,E696,E705,E2750,E1439,E767,E706,E1436</t>
-  </si>
-  <si>
-    <t>CE3140,C05635/C16596,CE6205,C00978,CE5860,C05645,C04148/C05642,C00637,C05638,C05639,C00021,C05660,CE2119/C05643,C00954/C05634,C00643,CE2119/C05643,C05639,C05660,CE2122,CE2122,C00780,CE3140,C15522/thbpt4acam,CE1918/CE5629,C05660,C05639,C01252,CE3140,C00268/C02953/C04244,C00328/C05647,C01252,C04148/C05642</t>
-  </si>
-  <si>
-    <t>$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$5-methoxytryptophol$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$$4-(2-Amino-3-hydroxyphenyl)-2,4-dioxobutanoate$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$Indole-3-acetaldehyde$5-Hydroxykynurenamine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$S-Adenosyl-L-homocysteine$5-Methoxyindoleacetate$/6-Hydroxymelatonin$Indole-3-acetate/5-Hydroxyindoleacetaldehyde$5-Hydroxy-L-tryptophan$/6-Hydroxymelatonin$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Methoxyindoleacetate$methyl indole-3-acetate$methyl indole-3-acetate$Serotonin$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$5-hydroxytryptophol/1,2-dehydrosalsolinol$5-Methoxyindoleacetate$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$4-(2-Aminophenyl)-2,4-dioxobutanoate$$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$L-Kynurenine/Formyl-5-hydroxykynurenamine$4-(2-Aminophenyl)-2,4-dioxobutanoate$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine</t>
+    <t>E2752,E823,E1154,E877,E123,E1438,E760,E691,E2796,E647,E1186,E527,E1138,E1187,E693,E737,E738,E2748,E1735,E651,E696,E705,E2750,E1439,E767,E706,E1436</t>
+  </si>
+  <si>
+    <t>,,,,,,,,C00021,,,,,,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$S-Adenosyl-L-homocysteine$$$$$$$$$$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Urea cycle/amino group metabolism</t>
+  </si>
+  <si>
+    <t>E143,E26,E148,E29,E1634,E2796,E1411,E412,E1535,E471,E145</t>
+  </si>
+  <si>
+    <t>,C00170,,C00170,,C00021,,,,,</t>
+  </si>
+  <si>
+    <t>$5-Methylthioadenosine$$5-Methylthioadenosine$$S-Adenosyl-L-homocysteine$$$$$</t>
+  </si>
+  <si>
+    <t>Saturated fatty acids beta-oxidation</t>
+  </si>
+  <si>
+    <t>E2345</t>
+  </si>
+  <si>
+    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2796</t>
+  </si>
+  <si>
+    <t>C00021</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>E1514,E1512,E1071,E445,E1039</t>
+  </si>
+  <si>
+    <t>,,,,</t>
+  </si>
+  <si>
+    <t>$$$$</t>
   </si>
   <si>
     <t>D4&amp;E4-neuroprostanes formation</t>
   </si>
   <si>
-    <t>E2895,E570,E1408,E569</t>
-  </si>
-  <si>
-    <t>CE6444/CE6445/CE6446/CE6448/CE6451/CE6450/CE6447/CE6449,C02670/C00072/glac,CE6429/CE6423/CE6420/CE6426/CE6438/CE6432/CE6435,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>///////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$//////$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>C21-steroid hormone biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2503,E2263,E1116,E1550,E1176,E423,E1163,E1164,E2269,E2399,E1526,E1768,E1771,E2264,E2457,E1691,E2669</t>
-  </si>
-  <si>
-    <t>CE2211/C05480,C18045/C14497/C18075/C05294/C05139,C05488/C05497/C05477/C02140,C00951,C02538,dhea/C03772/C01227/C00674/C00535,C05487/C05475/C05478,C05487/C05475/C05478,andrstndn/C00280,17ahprgstrn/C03205/C05498/C01176,C00468,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,C18045/C14497/C18075/C05294/C05139,C05472,CE1352,C05489/C05471/C05474</t>
-  </si>
-  <si>
-    <t>allopregnanolone/3alpha-Hydroxy-5beta-pregnane-20-one$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Estradiol-17beta; beta-Estradiol; Estradiol$Estrone 3-sulfate$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$17alpha-hydroxypregnenolone sulfate$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al</t>
+    <t>E2895,E1408,E569</t>
+  </si>
+  <si>
+    <t>,,</t>
+  </si>
+  <si>
+    <t>$$</t>
+  </si>
+  <si>
+    <t>Linoleate metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2348,E113,E2350,E2738,E2084,E2639,E569,E479</t>
+  </si>
+  <si>
+    <t>,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Biopterin metabolism</t>
+  </si>
+  <si>
+    <t>E1459,E1455,E1439,E1735,E288</t>
+  </si>
+  <si>
+    <t>De novo fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E2345,E92,E2166</t>
+  </si>
+  <si>
+    <t>Limonene and pinene degradation</t>
+  </si>
+  <si>
+    <t>E262,E261,E264</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E1074</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
+  </si>
+  <si>
+    <t>E2345,E2119,E2409</t>
+  </si>
+  <si>
+    <t>Hyaluronan Metabolism</t>
+  </si>
+  <si>
+    <t>E2845,E33</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
+  </si>
+  <si>
+    <t>E975,E2549</t>
+  </si>
+  <si>
+    <t>Vitamin A (retinol) metabolism</t>
+  </si>
+  <si>
+    <t>E2485,E2166,E2012,E2513</t>
+  </si>
+  <si>
+    <t>,,,</t>
+  </si>
+  <si>
+    <t>$$$</t>
   </si>
   <si>
     <t>Porphyrin metabolism</t>
   </si>
   <si>
-    <t>E570,E2728,E354,E1520,E569</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,C05769/C05770,C00931,C05791,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$/$Porphobilinogen$D-Urobilinogen$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E26,E2796,E1844,E29,E1345</t>
-  </si>
-  <si>
-    <t>C00170,C00021,C00212/C00330,C00170,C02291/C00542</t>
-  </si>
-  <si>
-    <t>5-Methylthioadenosine$S-Adenosyl-L-homocysteine$Adenosine/Deoxyguanosine$5-Methylthioadenosine$L-Cystathionine/Cystathionine</t>
-  </si>
-  <si>
-    <t>Saturated fatty acids beta-oxidation</t>
-  </si>
-  <si>
-    <t>E2345</t>
-  </si>
-  <si>
-    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
-  </si>
-  <si>
-    <t>E2796</t>
-  </si>
-  <si>
-    <t>C00021</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine</t>
-  </si>
-  <si>
-    <t>Urea cycle/amino group metabolism</t>
-  </si>
-  <si>
-    <t>E143,E26,E148,E1634,E2796,E1411,E412,E29,E1535,E471,E145</t>
-  </si>
-  <si>
-    <t>CE5536/C01586,C00170,CE5536/C01586,,C00021,CE2934,C05589/C00788,C00170,C04692,,CE5536/C01586</t>
-  </si>
-  <si>
-    <t>adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$5-Methylthioadenosine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$S-Adenosyl-L-homocysteine$o-methylhippurate$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Methylthioadenosine$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>E1514,E1512,E1071,E445,E1039</t>
-  </si>
-  <si>
-    <t>C00475,C00475,C00299,C00526,C00214</t>
-  </si>
-  <si>
-    <t>Cytidine$Cytidine$Uridine$Deoxyuridine$Thymidine</t>
+    <t>E569,E2728,E354</t>
+  </si>
+  <si>
+    <t>Vitamin B2 (riboflavin) metabolism</t>
+  </si>
+  <si>
+    <t>E276,E3036</t>
+  </si>
+  <si>
+    <t>Fatty acid activation</t>
+  </si>
+  <si>
+    <t>E2345,E92</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1714,E1239</t>
+  </si>
+  <si>
+    <t>C00021,,</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$$</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>E2345,E3164,E2383</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>E855,E853</t>
+  </si>
+  <si>
+    <t>Fatty Acid Metabolism</t>
+  </si>
+  <si>
+    <t>Selenoamino acid metabolism</t>
+  </si>
+  <si>
+    <t>E1844</t>
+  </si>
+  <si>
+    <t>C00212/C00330</t>
+  </si>
+  <si>
+    <t>Adenosine/Deoxyguanosine</t>
+  </si>
+  <si>
+    <t>Arginine and Proline Metabolism</t>
+  </si>
+  <si>
+    <t>E26,E29</t>
+  </si>
+  <si>
+    <t>C00170,C00170</t>
+  </si>
+  <si>
+    <t>5-Methylthioadenosine$5-Methylthioadenosine</t>
+  </si>
+  <si>
+    <t>Glycerophospholipid metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2383,E2796,E2985,E2513</t>
+  </si>
+  <si>
+    <t>,,C00021,,</t>
+  </si>
+  <si>
+    <t>$$S-Adenosyl-L-homocysteine$$</t>
+  </si>
+  <si>
+    <t>Tyrosine metabolism</t>
+  </si>
+  <si>
+    <t>E918,E143,E66,E1598,E412,E1438,E190,E158,E1599,E618,E145,E192,E680,E2796,E1222,E288,E160,E220,E148,E336,E830,E1735,E337,E831,E1439,E569,E1436,E170</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,C00021,,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$S-Adenosyl-L-homocysteine$$$$$$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
+    <t>E2192,E3007</t>
+  </si>
+  <si>
+    <t>Lysine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1926</t>
+  </si>
+  <si>
+    <t>C00021,</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$</t>
+  </si>
+  <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2505</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E2796,E831,E830</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E471,E1473,E1074</t>
+  </si>
+  <si>
+    <t>Hexose phosphorylation</t>
+  </si>
+  <si>
+    <t>E830,E831,E784</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>E2839,E33</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>E2047</t>
+  </si>
+  <si>
+    <t>Keratan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E33</t>
+  </si>
+  <si>
+    <t>Omega-3 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E92</t>
+  </si>
+  <si>
+    <t>Phosphatidylinositol phosphate metabolism</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E1403</t>
+  </si>
+  <si>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+  </si>
+  <si>
+    <t>E2765</t>
+  </si>
+  <si>
+    <t>CoA Catabolism</t>
+  </si>
+  <si>
+    <t>E2192</t>
+  </si>
+  <si>
+    <t>Heparan sulfate degradation</t>
+  </si>
+  <si>
+    <t>Histidine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1403</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E2442,E1452</t>
+  </si>
+  <si>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2263,E2796,E423,E2269,E1526,E1768,E1771,E422</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,C00021,dhea/C03772/C01227/C00674/C00535,andrstndn/C00280,C00468,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,dhea/C03772/C01227/C00674/C00535</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$S-Adenosyl-L-homocysteine$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>E2859,E3025,E3062,E3005</t>
   </si>
   <si>
     <t>Drug metabolism - cytochrome P450</t>
   </si>
   <si>
-    <t>E179,E796,E522,E1274,E2308,E800,E803,E2568,E801,E940</t>
-  </si>
-  <si>
-    <t>C16586/CE2173,C05635/C16596,C16595/C16587,,,C16591,C16591,C07572,C16591,</t>
-  </si>
-  <si>
-    <t>2-Phenyl-1,3-propanediol monocarbamate/$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one/3-Carbamoyl-2-phenylpropionaldehyde$$$3-Carbamoyl-2-phenylpropionic acid$3-Carbamoyl-2-phenylpropionic acid$Citalopram$3-Carbamoyl-2-phenylpropionic acid$</t>
-  </si>
-  <si>
-    <t>Linoleate metabolism</t>
-  </si>
-  <si>
-    <t>E570,E92,E113,E2350,E2348,E2738,E2639,E569,E479</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,,,,,,,C02670/C00072/glac,</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$$$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$</t>
-  </si>
-  <si>
-    <t>De novo fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E2345,E92,E2166</t>
-  </si>
-  <si>
-    <t>,,</t>
-  </si>
-  <si>
-    <t>$$</t>
-  </si>
-  <si>
-    <t>Limonene and pinene degradation</t>
-  </si>
-  <si>
-    <t>E262,E261,E264</t>
-  </si>
-  <si>
-    <t>Biopterin metabolism</t>
-  </si>
-  <si>
-    <t>E1459,E1439,E1455,E1735,E288</t>
-  </si>
-  <si>
-    <t>CE2705/CE5236,C00268/C02953/C04244,CE2705/CE5236,C15522/thbpt4acam,C00082</t>
-  </si>
-  <si>
-    <t>quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tyrosine</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>E1074</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>E2345,E2119,E2409</t>
-  </si>
-  <si>
-    <t>Hyaluronan Metabolism</t>
-  </si>
-  <si>
-    <t>E2845,E33</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
-  </si>
-  <si>
-    <t>E975,E2549</t>
-  </si>
-  <si>
-    <t>Vitamin B2 (riboflavin) metabolism</t>
-  </si>
-  <si>
-    <t>E276,E3036</t>
-  </si>
-  <si>
-    <t>Fatty acid activation</t>
-  </si>
-  <si>
-    <t>E2345,E92</t>
-  </si>
-  <si>
-    <t>Vitamin A (retinol) metabolism</t>
-  </si>
-  <si>
-    <t>E2485,E2166,E2012,E2513</t>
-  </si>
-  <si>
-    <t>,,,</t>
-  </si>
-  <si>
-    <t>$$$</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>E2345,E3164,E2383</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
-  </si>
-  <si>
-    <t>E855,E853</t>
-  </si>
-  <si>
-    <t>Tyrosine metabolism</t>
-  </si>
-  <si>
-    <t>E570,E918,E143,E1598,E412,E1438,E190,E1599,E158,E618,E145,E192,E2796,E1222,E288,E160,E220,E148,E336,E830,E634,E1735,E337,E831,E179,E1439,E66,E569,E1436,E170</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,CE2176,CE5536/C01586,,C05589/C00788,C04148/C05642,C09642,,C00355,,CE5536/C01586,C09642,C00021,,C00082,C00355,C05576,CE5536/C01586,C05583/C05582,C02763/C00166,CE1918/CE5629,C15522/thbpt4acam,C05583/C05582,C02763/C00166,C16586/CE2173,C00268/C02953/C04244,C05587/C07453,C02670/C00072/glac,C04148/C05642,C05588</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$3-O-methyldopa$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$$3,4-Dihydroxy-L-phenylalanine$$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$S-Adenosyl-L-homocysteine$$L-Tyrosine$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxyphenylethyleneglycol$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$enol-Phenylpyruvate/Phenylpyruvate$5-hydroxytryptophol/1,2-dehydrosalsolinol$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$enol-Phenylpyruvate/Phenylpyruvate$2-Phenyl-1,3-propanediol monocarbamate/$6,7-Dihydrobiopterin/7,8-Dihydrobiopterin/6-Lactoyl-5,6,7,8-tetrahydropterin$3-Methoxytyramine/Epinine; Deoxyepinephrine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$alpha-N-Phenylacetyl-L-glutamine/Formyl-N-acetyl-5-methoxykynurenamine$L-Metanephrine</t>
-  </si>
-  <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2263,E1550,E1176,E423,E2796,E2269,E1526,E1768,E1771,E2264</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,C00951,C02538,dhea/C03772/C01227/C00674/C00535,C00021,andrstndn/C00280,C00468,C05301/hestratriol/C05141/CE2179,C05301/hestratriol/C05141/CE2179,C18045/C14497/C18075/C05294/C05139</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Estradiol-17beta; beta-Estradiol; Estradiol$Estrone 3-sulfate$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$S-Adenosyl-L-homocysteine$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$2-Hydroxyestradiol-17beta; 2-OH-Estradiol/4,17 dihydroxy estradiol/Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol/4-hydroxy-17beta-estradiol$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one</t>
-  </si>
-  <si>
-    <t>Fatty Acid Metabolism</t>
-  </si>
-  <si>
-    <t>Selenoamino acid metabolism</t>
-  </si>
-  <si>
-    <t>E1844</t>
-  </si>
-  <si>
-    <t>C00212/C00330</t>
-  </si>
-  <si>
-    <t>Adenosine/Deoxyguanosine</t>
+    <t>E522,E1274,E2308,E2568,E801,E940</t>
+  </si>
+  <si>
+    <t>,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$</t>
+  </si>
+  <si>
+    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
+  </si>
+  <si>
+    <t>E569,E1132</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E975,E989,E1301,E1286,E2899,E1899</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E975,E92,E2513</t>
   </si>
   <si>
     <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
   </si>
   <si>
-    <t>E2570,E2796</t>
-  </si>
-  <si>
-    <t>C01185,C00021</t>
-  </si>
-  <si>
-    <t>Nicotinate D-ribonucleotide$S-Adenosyl-L-homocysteine</t>
-  </si>
-  <si>
-    <t>Arginine and Proline Metabolism</t>
-  </si>
-  <si>
-    <t>E29,E26</t>
-  </si>
-  <si>
-    <t>C00170,C00170</t>
-  </si>
-  <si>
-    <t>5-Methylthioadenosine$5-Methylthioadenosine</t>
-  </si>
-  <si>
-    <t>Glycerophospholipid metabolism</t>
-  </si>
-  <si>
-    <t>E2383,E92,E2796,E2985,E2513</t>
-  </si>
-  <si>
-    <t>,,C00021,,</t>
-  </si>
-  <si>
-    <t>$$S-Adenosyl-L-homocysteine$$</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>E2505</t>
-  </si>
-  <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>E2192,E3007</t>
-  </si>
-  <si>
-    <t>Lysine metabolism</t>
-  </si>
-  <si>
-    <t>E2796,E1926</t>
-  </si>
-  <si>
-    <t>C00021,</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$</t>
-  </si>
-  <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E2796,E831,E830</t>
-  </si>
-  <si>
-    <t>C00021,C02763/C00166,C02763/C00166</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$enol-Phenylpyruvate/Phenylpyruvate$enol-Phenylpyruvate/Phenylpyruvate</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E471,E1473,E1074</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E2839,E33</t>
-  </si>
-  <si>
-    <t>Hexose phosphorylation</t>
-  </si>
-  <si>
-    <t>E830,E831,E784</t>
-  </si>
-  <si>
-    <t>C02763/C00166,C02763/C00166,</t>
-  </si>
-  <si>
-    <t>enol-Phenylpyruvate/Phenylpyruvate$enol-Phenylpyruvate/Phenylpyruvate$</t>
+    <t>TCA cycle</t>
+  </si>
+  <si>
+    <t>E1132</t>
+  </si>
+  <si>
+    <t>Aminosugars metabolism</t>
   </si>
   <si>
     <t>Purine metabolism</t>
   </si>
   <si>
-    <t>E570,E572,E116,E1844,E573,E569</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,C00262,,C00212/C00330,C00262,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$Hypoxanthine$$Adenosine/Deoxyguanosine$Hypoxanthine$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Keratan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E33</t>
-  </si>
-  <si>
-    <t>Omega-3 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E92</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol phosphate metabolism</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E1403</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>CoA Catabolism</t>
-  </si>
-  <si>
-    <t>E2192</t>
-  </si>
-  <si>
-    <t>Heparan sulfate degradation</t>
-  </si>
-  <si>
-    <t>Histidine metabolism</t>
-  </si>
-  <si>
-    <t>E2796,E1403</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>E2796,E1714</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E2442,E1452</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E2859,E3025,E3062,E3005</t>
-  </si>
-  <si>
-    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
-  </si>
-  <si>
-    <t>E570,E569</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E975,E989,E1301,E1286,E2899,E1899</t>
-  </si>
-  <si>
-    <t>,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E975,E92,E2513</t>
+    <t>E1844,E572,E569</t>
+  </si>
+  <si>
+    <t>C00212/C00330,,</t>
+  </si>
+  <si>
+    <t>Adenosine/Deoxyguanosine$$</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E975,E569</t>
+  </si>
+  <si>
+    <t>Bile acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E2942</t>
+  </si>
+  <si>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycolysis and Gluconeogenesis</t>
+  </si>
+  <si>
+    <t>R Group Synthesis</t>
+  </si>
+  <si>
+    <t>C5-Branched dibasic acid metabolism</t>
+  </si>
+  <si>
+    <t>Pyruvate Metabolism</t>
+  </si>
+  <si>
+    <t>Chondroitin sulfate degradation</t>
+  </si>
+  <si>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycerolipid metabolism</t>
+  </si>
+  <si>
+    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
+  </si>
+  <si>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - globoseries</t>
+  </si>
+  <si>
+    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - lactoseries</t>
+  </si>
+  <si>
+    <t>Parathio degradation</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>Blood Group Biosynthesis</t>
+  </si>
+  <si>
+    <t>Electron transport chain</t>
+  </si>
+  <si>
+    <t>Vitamin H (biotin) metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
+  </si>
+  <si>
+    <t>Caffeine metabolism</t>
+  </si>
+  <si>
+    <t>Lipoate metabolism</t>
+  </si>
+  <si>
+    <t>Heparan sulfate biosynthesis</t>
   </si>
   <si>
     <t>Vitamin B9 (folate) metabolism</t>
   </si>
   <si>
-    <t>E1823</t>
-  </si>
-  <si>
-    <t>Aminosugars metabolism</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E975,E570,E569</t>
-  </si>
-  <si>
-    <t>,C02670/C00072/glac,C02670/C00072/glac</t>
-  </si>
-  <si>
-    <t>$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone</t>
-  </si>
-  <si>
-    <t>Bile acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E2942,E2940</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
-  </si>
-  <si>
-    <t>R Group Synthesis</t>
-  </si>
-  <si>
-    <t>C5-Branched dibasic acid metabolism</t>
-  </si>
-  <si>
-    <t>Pyruvate Metabolism</t>
-  </si>
-  <si>
-    <t>Chondroitin sulfate degradation</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycerolipid metabolism</t>
-  </si>
-  <si>
-    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - globoseries</t>
-  </si>
-  <si>
-    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - lactoseries</t>
-  </si>
-  <si>
-    <t>Parathio degradation</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>Blood Group Biosynthesis</t>
-  </si>
-  <si>
-    <t>Electron transport chain</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
-  </si>
-  <si>
-    <t>Caffeine metabolism</t>
-  </si>
-  <si>
-    <t>Lipoate metabolism</t>
-  </si>
-  <si>
-    <t>Heparan sulfate biosynthesis</t>
-  </si>
-  <si>
     <t>Glyoxylate and Dicarboxylate Metabolism</t>
   </si>
   <si>
@@ -641,9 +599,6 @@
   </si>
   <si>
     <t>Keratan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>TCA cycle</t>
   </si>
   <si>
     <t>3-Chloroacrylic acid degradation</t>
@@ -1069,13 +1024,13 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="D2">
-        <v>0.01241995932841465</v>
+        <v>0.03225155879733114</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1092,13 +1047,13 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>0.02744491689215307</v>
+        <v>0.03257088116166115</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1115,13 +1070,13 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C4">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="D4">
-        <v>0.02978101208383052</v>
+        <v>0.05683938085074201</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1138,13 +1093,13 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>0.03184820423186165</v>
+        <v>0.05752844490008571</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1161,27 +1116,21 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0.04189845548814305</v>
+        <v>0.06603250365540075</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1190,9 +1139,15 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0.07107443572376936</v>
+        <v>0.06603250365540075</v>
       </c>
       <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1201,13 +1156,13 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>0.07107443572376936</v>
+        <v>0.0719987899363036</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -1224,13 +1179,13 @@
         <v>33</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>0.08127594494210182</v>
+        <v>0.08186417035007815</v>
       </c>
       <c r="E9" t="s">
         <v>34</v>
@@ -1247,13 +1202,13 @@
         <v>37</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D10">
-        <v>0.0878136501907531</v>
+        <v>0.09194803448681535</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -1270,50 +1225,50 @@
         <v>41</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D11">
-        <v>0.1034268331624679</v>
+        <v>0.1098636997697518</v>
       </c>
       <c r="E11" t="s">
         <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>0.1261491403505823</v>
+        <v>0.1137964067830793</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -1322,153 +1277,153 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>0.1287541385859061</v>
+        <v>0.1137964067830793</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>0.1287541385859061</v>
+        <v>0.1327204584796894</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>0.1306196534512025</v>
+        <v>0.1337120384531352</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>0.1421824843279945</v>
+        <v>0.1527705416715685</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>52</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>0.1519974454210854</v>
+        <v>0.1527705416715685</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D18">
-        <v>0.1711735937211139</v>
+        <v>0.1864002285675871</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D19">
-        <v>0.1711735937211139</v>
+        <v>0.1915093863968673</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -1477,21 +1432,21 @@
         <v>8</v>
       </c>
       <c r="D20">
-        <v>0.2227189459000689</v>
+        <v>0.1959967059377153</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -1500,44 +1455,44 @@
         <v>8</v>
       </c>
       <c r="D21">
-        <v>0.2227189459000689</v>
+        <v>0.1959967059377153</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D22">
-        <v>0.2250046217710627</v>
+        <v>0.2241138804389842</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -1546,21 +1501,21 @@
         <v>14</v>
       </c>
       <c r="D23">
-        <v>0.2568696324431522</v>
+        <v>0.2241138804389842</v>
       </c>
       <c r="E23" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G23" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -1569,176 +1524,176 @@
         <v>9</v>
       </c>
       <c r="D24">
-        <v>0.265407304078923</v>
+        <v>0.2356262919950925</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B25">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>0.2782138115325793</v>
+        <v>0.259306566276197</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
-      </c>
-      <c r="F25" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>0.2871884506142754</v>
+        <v>0.259306566276197</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>0.2871884506142754</v>
+        <v>0.280986874170182</v>
       </c>
       <c r="E27" t="s">
-        <v>28</v>
+        <v>81</v>
+      </c>
+      <c r="F27" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D28">
-        <v>0.2871884506142754</v>
+        <v>0.2891548041209391</v>
       </c>
       <c r="E28" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="D29">
-        <v>0.3175408816658544</v>
+        <v>0.2944824456731819</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30">
-        <v>0.3175408816658544</v>
+        <v>0.3196752995747971</v>
       </c>
       <c r="E30" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F30" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="G30" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D31">
-        <v>0.332532226349137</v>
+        <v>0.3196752995747971</v>
       </c>
       <c r="E31" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F31" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1747,176 +1702,158 @@
         <v>5</v>
       </c>
       <c r="D32">
-        <v>0.3404648661367036</v>
+        <v>0.3215240079998655</v>
       </c>
       <c r="E32" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D33">
-        <v>0.3438765735029664</v>
+        <v>0.3221626527285256</v>
       </c>
       <c r="E33" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D34">
-        <v>0.3438765735029664</v>
+        <v>0.3221626527285256</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F34" t="s">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="G34" t="s">
-        <v>113</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B35">
         <v>3</v>
       </c>
       <c r="C35">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D35">
-        <v>0.3516243424480261</v>
+        <v>0.3421959294801768</v>
       </c>
       <c r="E35" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F35" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="G35" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D36">
-        <v>0.3516243424480261</v>
+        <v>0.3438093477420547</v>
       </c>
       <c r="E36" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G36" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>0.3731197794995042</v>
+        <v>0.3573385321255105</v>
       </c>
       <c r="E37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G37" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D38">
-        <v>0.3759936807784743</v>
+        <v>0.3573385321255105</v>
       </c>
       <c r="E38" t="s">
-        <v>123</v>
-      </c>
-      <c r="F38" t="s">
-        <v>124</v>
-      </c>
-      <c r="G38" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
         <v>6</v>
       </c>
-      <c r="C39">
-        <v>35</v>
-      </c>
       <c r="D39">
-        <v>0.3779432278449102</v>
+        <v>0.3573385321255105</v>
       </c>
       <c r="E39" t="s">
-        <v>127</v>
-      </c>
-      <c r="F39" t="s">
-        <v>128</v>
-      </c>
-      <c r="G39" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -1925,15 +1862,15 @@
         <v>6</v>
       </c>
       <c r="D40">
-        <v>0.3799936135527134</v>
+        <v>0.3573385321255105</v>
       </c>
       <c r="E40" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -1942,72 +1879,72 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <v>0.3799936135527134</v>
+        <v>0.3573385321255105</v>
       </c>
       <c r="E41" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D42">
-        <v>0.3799936135527134</v>
+        <v>0.3706324263457757</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>107</v>
+      </c>
+      <c r="F42" t="s">
+        <v>53</v>
+      </c>
+      <c r="G42" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43">
-        <v>0.3799936135527134</v>
+        <v>0.3973714727483572</v>
       </c>
       <c r="E43" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D44">
-        <v>0.4030520495453858</v>
+        <v>0.3973714727483572</v>
       </c>
       <c r="E44" t="s">
         <v>121</v>
       </c>
-      <c r="F44" t="s">
-        <v>65</v>
-      </c>
-      <c r="G44" t="s">
-        <v>66</v>
-      </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -2016,32 +1953,38 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>0.4223290364867817</v>
+        <v>0.3973714727483572</v>
       </c>
       <c r="E45" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D46">
-        <v>0.4223290364867817</v>
+        <v>0.4014722441639637</v>
       </c>
       <c r="E46" t="s">
-        <v>131</v>
+        <v>124</v>
+      </c>
+      <c r="F46" t="s">
+        <v>96</v>
+      </c>
+      <c r="G46" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="B47">
         <v>2</v>
@@ -2050,90 +1993,90 @@
         <v>14</v>
       </c>
       <c r="D47">
-        <v>0.4350010924186148</v>
+        <v>0.4014722441639637</v>
       </c>
       <c r="E47" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="F47" t="s">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="G47" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C48">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D48">
-        <v>0.4350010924186148</v>
+        <v>0.4067830792759786</v>
       </c>
       <c r="E48" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="F48" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="G48" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D49">
-        <v>0.4350010924186148</v>
+        <v>0.4083796910976286</v>
       </c>
       <c r="E49" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F49" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G49" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C50">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D50">
-        <v>0.4498579855800743</v>
+        <v>0.4223458429270096</v>
       </c>
       <c r="E50" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F50" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="G50" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -2142,21 +2085,21 @@
         <v>15</v>
       </c>
       <c r="D51">
-        <v>0.4605973008856994</v>
+        <v>0.4297406766272836</v>
       </c>
       <c r="E51" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="F51" t="s">
-        <v>151</v>
+        <v>53</v>
       </c>
       <c r="G51" t="s">
-        <v>152</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="B52">
         <v>6</v>
@@ -2165,21 +2108,21 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.4862607351136956</v>
+        <v>0.4408665400581503</v>
       </c>
       <c r="E52" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="F52" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="G52" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -2188,15 +2131,15 @@
         <v>9</v>
       </c>
       <c r="D53">
-        <v>0.4898405068822373</v>
+        <v>0.4675215542595923</v>
       </c>
       <c r="E53" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="B54">
         <v>3</v>
@@ -2205,241 +2148,253 @@
         <v>24</v>
       </c>
       <c r="D54">
-        <v>0.5111342666509806</v>
+        <v>0.4799751264684627</v>
       </c>
       <c r="E54" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="F54" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G54" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D55">
-        <v>0.534999411774592</v>
+        <v>0.495184954874708</v>
       </c>
       <c r="E55" t="s">
-        <v>161</v>
+        <v>26</v>
+      </c>
+      <c r="F55" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D56">
-        <v>0.534999411774592</v>
+        <v>0.495184954874708</v>
       </c>
       <c r="E56" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D57">
-        <v>0.5673854220937463</v>
+        <v>0.5180417135846457</v>
       </c>
       <c r="E57" t="s">
-        <v>164</v>
-      </c>
-      <c r="F57" t="s">
-        <v>165</v>
-      </c>
-      <c r="G57" t="s">
-        <v>166</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D58">
-        <v>0.5701248718508932</v>
+        <v>0.5885111174602108</v>
       </c>
       <c r="E58" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="F58" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="G58" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D59">
-        <v>0.6167123241626191</v>
+        <v>0.5960908220029916</v>
+      </c>
+      <c r="E59" t="s">
+        <v>153</v>
+      </c>
+      <c r="F59" t="s">
+        <v>53</v>
+      </c>
+      <c r="G59" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D60">
-        <v>0.6167123241626191</v>
+        <v>0.603889010268735</v>
+      </c>
+      <c r="E60" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D61">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D62">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D63">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D68">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2448,12 +2403,12 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2462,12 +2417,12 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2476,12 +2431,12 @@
         <v>9</v>
       </c>
       <c r="D71">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2490,12 +2445,12 @@
         <v>5</v>
       </c>
       <c r="D72">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2504,12 +2459,12 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2518,12 +2473,12 @@
         <v>3</v>
       </c>
       <c r="D74">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2532,12 +2487,12 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2546,12 +2501,12 @@
         <v>5</v>
       </c>
       <c r="D76">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2560,12 +2515,12 @@
         <v>3</v>
       </c>
       <c r="D77">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2574,12 +2529,12 @@
         <v>3</v>
       </c>
       <c r="D78">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2588,12 +2543,12 @@
         <v>5</v>
       </c>
       <c r="D79">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2602,12 +2557,12 @@
         <v>5</v>
       </c>
       <c r="D80">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2616,12 +2571,12 @@
         <v>3</v>
       </c>
       <c r="D81">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2630,12 +2585,12 @@
         <v>6</v>
       </c>
       <c r="D82">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2644,138 +2599,138 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D84">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D88">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D90">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D92">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2784,12 +2739,12 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2798,12 +2753,12 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2812,12 +2767,12 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2826,54 +2781,54 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D98">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D99">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2882,12 +2837,12 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2896,12 +2851,12 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2910,12 +2865,12 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2924,12 +2879,12 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2938,12 +2893,12 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2952,12 +2907,12 @@
         <v>1</v>
       </c>
       <c r="D105">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2966,12 +2921,12 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2980,12 +2935,12 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2994,12 +2949,12 @@
         <v>12</v>
       </c>
       <c r="D108">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3008,12 +2963,12 @@
         <v>3</v>
       </c>
       <c r="D109">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3022,12 +2977,12 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3036,12 +2991,12 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3050,12 +3005,12 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3064,12 +3019,12 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3078,12 +3033,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3092,12 +3047,12 @@
         <v>5</v>
       </c>
       <c r="D115">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3106,12 +3061,12 @@
         <v>3</v>
       </c>
       <c r="D116">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3120,12 +3075,12 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3134,12 +3089,12 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3148,12 +3103,12 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3162,7 +3117,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>0.6167123241626191</v>
+        <v>0.6130821330733938</v>
       </c>
     </row>
   </sheetData>
